--- a/actividades MIR 2026/IPPI SDTI - Calendario Actividades.xlsx
+++ b/actividades MIR 2026/IPPI SDTI - Calendario Actividades.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="24334"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="26327"/>
   <workbookPr codeName="ThisWorkbook" autoCompressPictures="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\IPPI 11\Documents\GitHub\proyecto-ippi\actividades MIR 2026\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\MTGH\Documents\GitHub\proyecto-ippi\actividades MIR 2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{925A3F42-8760-456C-9BE6-1EC98A112663}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2BB2C3C0-2EDD-428C-A516-64F587783FBC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="16440" tabRatio="788" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" tabRatio="788" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Calendario" sheetId="15" r:id="rId1"/>
@@ -144,8 +144,17 @@
     <definedName name="ValorDeInicioDeSemana" localSheetId="3">IF('Calendario Detallado 2026'!InicioDeSemana="LUNES",2,1)</definedName>
     <definedName name="ValorDeInicioDeSemana">IF(InicioDeSemana="LUNES",2,1)</definedName>
   </definedNames>
-  <calcPr calcId="181029"/>
+  <calcPr calcId="191029"/>
   <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
     <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
       <xlwcv:version setVersion="1"/>
     </ext>
@@ -1081,7 +1090,7 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="80">
+  <cellXfs count="72">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="7" fillId="6" borderId="0" xfId="9">
       <alignment horizontal="center"/>
@@ -1097,7 +1106,7 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="2">
       <alignment horizontal="left" indent="3"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="7" borderId="3" xfId="10" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="7" borderId="3" xfId="10">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="6" borderId="3" xfId="11" applyAlignment="1">
@@ -1129,7 +1138,7 @@
     <xf numFmtId="0" fontId="19" fillId="0" borderId="11" xfId="13" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="12" xfId="13" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="13" xfId="13" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="13" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="13" applyFont="1"/>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="16" xfId="13" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="17" xfId="13" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="18" xfId="13" applyFont="1" applyBorder="1"/>
@@ -1139,25 +1148,12 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="13" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="13" applyFont="1"/>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="24" xfId="13" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="25" xfId="13" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="26" xfId="13" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="13" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="13" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="13" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="13" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="13" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="13" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="13" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="13" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="20" fillId="8" borderId="15" xfId="13" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1165,49 +1161,49 @@
     <xf numFmtId="0" fontId="21" fillId="8" borderId="21" xfId="13" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="15" xfId="13" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="15" xfId="13" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="20" xfId="13" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="20" xfId="13" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="20" xfId="13" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="20" xfId="13" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="8" borderId="19" xfId="13" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="21" xfId="13" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="21" xfId="13" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="31" xfId="13" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="19" xfId="13" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="19" xfId="13" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="21" xfId="13" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="21" xfId="13" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="20" xfId="13" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="20" xfId="13" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="8" borderId="20" xfId="13" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="29" xfId="13" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="29" xfId="13" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="30" xfId="13" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="30" xfId="13" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="16" xfId="13" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="17" xfId="13" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="17" xfId="13" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="18" xfId="13" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="18" xfId="13" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="13" applyBorder="1" applyAlignment="1">
@@ -1222,7 +1218,7 @@
     <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="2" applyFont="1">
       <alignment horizontal="left" indent="3"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="12" borderId="3" xfId="10" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="12" borderId="3" xfId="10" applyFill="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="13" borderId="3" xfId="11" applyFill="1" applyAlignment="1">
@@ -1237,16 +1233,16 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="14" xfId="13" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="9" borderId="0" xfId="13" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="9" borderId="0" xfId="13" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="10" borderId="0" xfId="13" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="8" xfId="8" applyFont="1" applyBorder="1">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="8" xfId="8" applyFont="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
-    <xf numFmtId="164" fontId="12" fillId="0" borderId="8" xfId="8" applyBorder="1">
+    <xf numFmtId="164" fontId="12" fillId="0" borderId="8" xfId="8">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="7" applyNumberFormat="1">
@@ -1259,9 +1255,6 @@
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="28" xfId="8" applyNumberFormat="1" applyBorder="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="12" fillId="0" borderId="8" xfId="8">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="14" borderId="32" xfId="6" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1789,10 +1782,10 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A2:AH74"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="5.625" style="14" customWidth="1"/>
-    <col min="2" max="2" width="10.625" style="14" customWidth="1"/>
+    <col min="1" max="1" width="5.6640625" style="14" customWidth="1"/>
+    <col min="2" max="2" width="10.6640625" style="14" customWidth="1"/>
     <col min="3" max="8" width="12" style="14" customWidth="1"/>
     <col min="9" max="9" width="11" style="14"/>
     <col min="10" max="10" width="0" style="14" hidden="1" customWidth="1"/>
@@ -1804,65 +1797,65 @@
     <col min="33" max="16384" width="11" style="14"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:34" ht="28.5" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A2" s="67"/>
-      <c r="B2" s="67"/>
-      <c r="C2" s="68" t="s">
+    <row r="2" spans="1:34" ht="28.5" customHeight="1" x14ac:dyDescent="0.5">
+      <c r="A2" s="60"/>
+      <c r="B2" s="60"/>
+      <c r="C2" s="61" t="s">
         <v>4</v>
       </c>
-      <c r="D2" s="68"/>
-      <c r="E2" s="68"/>
-      <c r="F2" s="68"/>
-      <c r="G2" s="68"/>
-      <c r="H2" s="68"/>
-      <c r="K2" s="64" t="s">
+      <c r="D2" s="61"/>
+      <c r="E2" s="61"/>
+      <c r="F2" s="61"/>
+      <c r="G2" s="61"/>
+      <c r="H2" s="61"/>
+      <c r="K2" s="57" t="s">
         <v>5</v>
       </c>
-      <c r="L2" s="64"/>
-      <c r="M2" s="64"/>
-      <c r="N2" s="64"/>
-      <c r="O2" s="64"/>
-      <c r="P2" s="64"/>
-      <c r="S2" s="64" t="s">
+      <c r="L2" s="57"/>
+      <c r="M2" s="57"/>
+      <c r="N2" s="57"/>
+      <c r="O2" s="57"/>
+      <c r="P2" s="57"/>
+      <c r="S2" s="57" t="s">
         <v>6</v>
       </c>
-      <c r="T2" s="64"/>
-      <c r="U2" s="64"/>
-      <c r="V2" s="64"/>
-      <c r="W2" s="64"/>
-      <c r="X2" s="64"/>
-      <c r="AA2" s="64" t="s">
+      <c r="T2" s="57"/>
+      <c r="U2" s="57"/>
+      <c r="V2" s="57"/>
+      <c r="W2" s="57"/>
+      <c r="X2" s="57"/>
+      <c r="AA2" s="57" t="s">
         <v>7</v>
       </c>
-      <c r="AB2" s="64"/>
-      <c r="AC2" s="64"/>
-      <c r="AD2" s="64"/>
-      <c r="AE2" s="64"/>
-      <c r="AF2" s="64"/>
+      <c r="AB2" s="57"/>
+      <c r="AC2" s="57"/>
+      <c r="AD2" s="57"/>
+      <c r="AE2" s="57"/>
+      <c r="AF2" s="57"/>
     </row>
     <row r="3" spans="1:34" x14ac:dyDescent="0.3">
-      <c r="A3" s="67"/>
-      <c r="B3" s="67"/>
-    </row>
-    <row r="4" spans="1:34" s="16" customFormat="1" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A4" s="67"/>
-      <c r="B4" s="67"/>
-      <c r="C4" s="58" t="s">
+      <c r="A3" s="60"/>
+      <c r="B3" s="60"/>
+    </row>
+    <row r="4" spans="1:34" s="16" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A4" s="60"/>
+      <c r="B4" s="60"/>
+      <c r="C4" s="51" t="s">
         <v>0</v>
       </c>
-      <c r="D4" s="58" t="s">
+      <c r="D4" s="51" t="s">
         <v>8</v>
       </c>
-      <c r="E4" s="58" t="s">
+      <c r="E4" s="51" t="s">
         <v>9</v>
       </c>
-      <c r="F4" s="58" t="s">
+      <c r="F4" s="51" t="s">
         <v>10</v>
       </c>
-      <c r="G4" s="58" t="s">
+      <c r="G4" s="51" t="s">
         <v>11</v>
       </c>
-      <c r="H4" s="58" t="s">
+      <c r="H4" s="51" t="s">
         <v>12</v>
       </c>
       <c r="J4" s="16" t="s">
@@ -1929,8 +1922,8 @@
         <v>12</v>
       </c>
     </row>
-    <row r="5" spans="1:34" ht="15.75" customHeight="1" thickTop="1" x14ac:dyDescent="0.35">
-      <c r="A5" s="65" t="s">
+    <row r="5" spans="1:34" ht="15.75" customHeight="1" thickTop="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="58" t="s">
         <v>16</v>
       </c>
       <c r="B5" s="17"/>
@@ -1940,7 +1933,7 @@
       <c r="F5" s="19"/>
       <c r="G5" s="19"/>
       <c r="H5" s="20"/>
-      <c r="J5" s="65" t="s">
+      <c r="J5" s="58" t="s">
         <v>16</v>
       </c>
       <c r="K5" s="18" t="s">
@@ -1961,7 +1954,7 @@
       <c r="P5" s="20" t="s">
         <v>17</v>
       </c>
-      <c r="R5" s="65" t="s">
+      <c r="R5" s="58" t="s">
         <v>16</v>
       </c>
       <c r="S5" s="18" t="s">
@@ -1982,7 +1975,7 @@
       <c r="X5" s="20" t="s">
         <v>17</v>
       </c>
-      <c r="Z5" s="65" t="s">
+      <c r="Z5" s="58" t="s">
         <v>16</v>
       </c>
       <c r="AA5" s="18" t="s">
@@ -2005,24 +1998,24 @@
       </c>
       <c r="AH5" s="21"/>
     </row>
-    <row r="6" spans="1:34" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A6" s="65"/>
-      <c r="B6" s="66" t="s">
+    <row r="6" spans="1:34" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="58"/>
+      <c r="B6" s="59" t="s">
         <v>18</v>
       </c>
-      <c r="C6" s="40" t="s">
+      <c r="C6" s="33" t="s">
         <v>19</v>
       </c>
-      <c r="D6" s="43"/>
-      <c r="E6" s="40" t="s">
+      <c r="D6" s="36"/>
+      <c r="E6" s="33" t="s">
         <v>19</v>
       </c>
-      <c r="F6" s="43"/>
-      <c r="G6" s="40" t="s">
+      <c r="F6" s="36"/>
+      <c r="G6" s="33" t="s">
         <v>19</v>
       </c>
-      <c r="H6" s="43"/>
-      <c r="J6" s="65"/>
+      <c r="H6" s="36"/>
+      <c r="J6" s="58"/>
       <c r="K6" s="22" t="s">
         <v>20</v>
       </c>
@@ -2041,7 +2034,7 @@
       <c r="P6" s="24" t="s">
         <v>21</v>
       </c>
-      <c r="R6" s="65"/>
+      <c r="R6" s="58"/>
       <c r="S6" s="22" t="s">
         <v>21</v>
       </c>
@@ -2060,7 +2053,7 @@
       <c r="X6" s="24" t="s">
         <v>21</v>
       </c>
-      <c r="Z6" s="65"/>
+      <c r="Z6" s="58"/>
       <c r="AA6" s="22" t="s">
         <v>20</v>
       </c>
@@ -2080,16 +2073,16 @@
         <v>21</v>
       </c>
     </row>
-    <row r="7" spans="1:34" ht="8.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A7" s="65"/>
-      <c r="B7" s="66"/>
-      <c r="C7" s="46"/>
-      <c r="D7" s="49"/>
-      <c r="E7" s="46"/>
-      <c r="F7" s="49"/>
-      <c r="G7" s="46"/>
-      <c r="H7" s="49"/>
-      <c r="J7" s="65"/>
+    <row r="7" spans="1:34" ht="8.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A7" s="58"/>
+      <c r="B7" s="59"/>
+      <c r="C7" s="39"/>
+      <c r="D7" s="42"/>
+      <c r="E7" s="39"/>
+      <c r="F7" s="42"/>
+      <c r="G7" s="39"/>
+      <c r="H7" s="42"/>
+      <c r="J7" s="58"/>
       <c r="K7" s="22" t="s">
         <v>22</v>
       </c>
@@ -2108,7 +2101,7 @@
       <c r="P7" s="24" t="s">
         <v>23</v>
       </c>
-      <c r="R7" s="65"/>
+      <c r="R7" s="58"/>
       <c r="S7" s="22" t="s">
         <v>23</v>
       </c>
@@ -2127,7 +2120,7 @@
       <c r="X7" s="24" t="s">
         <v>23</v>
       </c>
-      <c r="Z7" s="65"/>
+      <c r="Z7" s="58"/>
       <c r="AA7" s="22" t="s">
         <v>21</v>
       </c>
@@ -2147,22 +2140,22 @@
         <v>23</v>
       </c>
     </row>
-    <row r="8" spans="1:34" ht="27.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A8" s="65"/>
-      <c r="B8" s="66"/>
-      <c r="C8" s="42" t="s">
+    <row r="8" spans="1:34" ht="27.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="58"/>
+      <c r="B8" s="59"/>
+      <c r="C8" s="35" t="s">
         <v>2</v>
       </c>
-      <c r="D8" s="50"/>
-      <c r="E8" s="42" t="s">
+      <c r="D8" s="43"/>
+      <c r="E8" s="35" t="s">
         <v>2</v>
       </c>
-      <c r="F8" s="50"/>
-      <c r="G8" s="42" t="s">
+      <c r="F8" s="43"/>
+      <c r="G8" s="35" t="s">
         <v>2</v>
       </c>
-      <c r="H8" s="51"/>
-      <c r="J8" s="65"/>
+      <c r="H8" s="44"/>
+      <c r="J8" s="58"/>
       <c r="K8" s="22" t="s">
         <v>21</v>
       </c>
@@ -2181,7 +2174,7 @@
       <c r="P8" s="24" t="s">
         <v>24</v>
       </c>
-      <c r="R8" s="65"/>
+      <c r="R8" s="58"/>
       <c r="S8" s="22" t="s">
         <v>25</v>
       </c>
@@ -2200,7 +2193,7 @@
       <c r="X8" s="24" t="s">
         <v>24</v>
       </c>
-      <c r="Z8" s="65"/>
+      <c r="Z8" s="58"/>
       <c r="AA8" s="22" t="s">
         <v>23</v>
       </c>
@@ -2220,30 +2213,30 @@
         <v>24</v>
       </c>
     </row>
-    <row r="9" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A9" s="65"/>
+    <row r="9" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A9" s="58"/>
       <c r="B9" s="16"/>
-      <c r="C9" s="55"/>
-      <c r="D9" s="44"/>
-      <c r="E9" s="55"/>
-      <c r="F9" s="45"/>
-      <c r="G9" s="55"/>
-      <c r="H9" s="47"/>
-      <c r="J9" s="65"/>
+      <c r="C9" s="48"/>
+      <c r="D9" s="37"/>
+      <c r="E9" s="48"/>
+      <c r="F9" s="38"/>
+      <c r="G9" s="48"/>
+      <c r="H9" s="40"/>
+      <c r="J9" s="58"/>
       <c r="K9" s="22"/>
       <c r="L9" s="23"/>
       <c r="M9" s="23"/>
       <c r="N9" s="23"/>
       <c r="O9" s="23"/>
       <c r="P9" s="24"/>
-      <c r="R9" s="65"/>
+      <c r="R9" s="58"/>
       <c r="S9" s="22"/>
       <c r="T9" s="23"/>
       <c r="U9" s="23"/>
       <c r="V9" s="23"/>
       <c r="W9" s="23"/>
       <c r="X9" s="24"/>
-      <c r="Z9" s="65"/>
+      <c r="Z9" s="58"/>
       <c r="AA9" s="22"/>
       <c r="AB9" s="23"/>
       <c r="AC9" s="23"/>
@@ -2251,24 +2244,24 @@
       <c r="AE9" s="23"/>
       <c r="AF9" s="24"/>
     </row>
-    <row r="10" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A10" s="65"/>
-      <c r="B10" s="66" t="s">
+    <row r="10" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A10" s="58"/>
+      <c r="B10" s="59" t="s">
         <v>27</v>
       </c>
-      <c r="C10" s="40" t="s">
+      <c r="C10" s="33" t="s">
         <v>19</v>
       </c>
-      <c r="D10" s="43"/>
-      <c r="E10" s="40" t="s">
+      <c r="D10" s="36"/>
+      <c r="E10" s="33" t="s">
         <v>19</v>
       </c>
-      <c r="F10" s="43"/>
-      <c r="G10" s="40" t="s">
+      <c r="F10" s="36"/>
+      <c r="G10" s="33" t="s">
         <v>19</v>
       </c>
-      <c r="H10" s="43"/>
-      <c r="J10" s="65"/>
+      <c r="H10" s="36"/>
+      <c r="J10" s="58"/>
       <c r="K10" s="22" t="s">
         <v>24</v>
       </c>
@@ -2287,7 +2280,7 @@
       <c r="P10" s="24" t="s">
         <v>26</v>
       </c>
-      <c r="R10" s="65"/>
+      <c r="R10" s="58"/>
       <c r="S10" s="22" t="s">
         <v>28</v>
       </c>
@@ -2306,7 +2299,7 @@
       <c r="X10" s="24" t="s">
         <v>26</v>
       </c>
-      <c r="Z10" s="65"/>
+      <c r="Z10" s="58"/>
       <c r="AA10" s="22" t="s">
         <v>25</v>
       </c>
@@ -2326,16 +2319,16 @@
         <v>26</v>
       </c>
     </row>
-    <row r="11" spans="1:34" ht="6.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A11" s="65"/>
-      <c r="B11" s="66"/>
-      <c r="C11" s="46"/>
-      <c r="D11" s="49"/>
-      <c r="E11" s="46"/>
-      <c r="F11" s="49"/>
-      <c r="G11" s="46"/>
-      <c r="H11" s="49"/>
-      <c r="J11" s="65"/>
+    <row r="11" spans="1:34" ht="6.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A11" s="58"/>
+      <c r="B11" s="59"/>
+      <c r="C11" s="39"/>
+      <c r="D11" s="42"/>
+      <c r="E11" s="39"/>
+      <c r="F11" s="42"/>
+      <c r="G11" s="39"/>
+      <c r="H11" s="42"/>
+      <c r="J11" s="58"/>
       <c r="K11" s="22" t="s">
         <v>25</v>
       </c>
@@ -2354,7 +2347,7 @@
       <c r="P11" s="24" t="s">
         <v>28</v>
       </c>
-      <c r="R11" s="65"/>
+      <c r="R11" s="58"/>
       <c r="S11" s="22" t="s">
         <v>30</v>
       </c>
@@ -2373,7 +2366,7 @@
       <c r="X11" s="24" t="s">
         <v>30</v>
       </c>
-      <c r="Z11" s="65"/>
+      <c r="Z11" s="58"/>
       <c r="AA11" s="22" t="s">
         <v>26</v>
       </c>
@@ -2393,22 +2386,22 @@
         <v>30</v>
       </c>
     </row>
-    <row r="12" spans="1:34" ht="24.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A12" s="65"/>
-      <c r="B12" s="66"/>
-      <c r="C12" s="52" t="s">
+    <row r="12" spans="1:34" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A12" s="58"/>
+      <c r="B12" s="59"/>
+      <c r="C12" s="45" t="s">
         <v>2</v>
       </c>
-      <c r="D12" s="53"/>
-      <c r="E12" s="42" t="s">
+      <c r="D12" s="46"/>
+      <c r="E12" s="35" t="s">
         <v>2</v>
       </c>
-      <c r="F12" s="51"/>
-      <c r="G12" s="42" t="s">
+      <c r="F12" s="44"/>
+      <c r="G12" s="35" t="s">
         <v>2</v>
       </c>
-      <c r="H12" s="51"/>
-      <c r="J12" s="65"/>
+      <c r="H12" s="44"/>
+      <c r="J12" s="58"/>
       <c r="K12" s="22" t="s">
         <v>26</v>
       </c>
@@ -2427,7 +2420,7 @@
       <c r="P12" s="24" t="s">
         <v>30</v>
       </c>
-      <c r="R12" s="65"/>
+      <c r="R12" s="58"/>
       <c r="S12" s="22" t="s">
         <v>33</v>
       </c>
@@ -2446,7 +2439,7 @@
       <c r="X12" s="24" t="s">
         <v>29</v>
       </c>
-      <c r="Z12" s="65"/>
+      <c r="Z12" s="58"/>
       <c r="AA12" s="22" t="s">
         <v>28</v>
       </c>
@@ -2466,16 +2459,16 @@
         <v>29</v>
       </c>
     </row>
-    <row r="13" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A13" s="65"/>
+    <row r="13" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A13" s="58"/>
       <c r="B13" s="16"/>
-      <c r="C13" s="55"/>
-      <c r="D13" s="56"/>
-      <c r="E13" s="55"/>
-      <c r="F13" s="56"/>
-      <c r="G13" s="55"/>
-      <c r="H13" s="57"/>
-      <c r="J13" s="65"/>
+      <c r="C13" s="48"/>
+      <c r="D13" s="49"/>
+      <c r="E13" s="48"/>
+      <c r="F13" s="49"/>
+      <c r="G13" s="48"/>
+      <c r="H13" s="50"/>
+      <c r="J13" s="58"/>
       <c r="K13" s="22" t="s">
         <v>28</v>
       </c>
@@ -2494,7 +2487,7 @@
       <c r="P13" s="24" t="s">
         <v>29</v>
       </c>
-      <c r="R13" s="65"/>
+      <c r="R13" s="58"/>
       <c r="S13" s="22" t="s">
         <v>36</v>
       </c>
@@ -2513,7 +2506,7 @@
       <c r="X13" s="24" t="s">
         <v>38</v>
       </c>
-      <c r="Z13" s="65"/>
+      <c r="Z13" s="58"/>
       <c r="AA13" s="22" t="s">
         <v>30</v>
       </c>
@@ -2533,24 +2526,24 @@
         <v>38</v>
       </c>
     </row>
-    <row r="14" spans="1:34" ht="18" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A14" s="65"/>
-      <c r="B14" s="66" t="s">
+    <row r="14" spans="1:34" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A14" s="58"/>
+      <c r="B14" s="59" t="s">
         <v>40</v>
       </c>
-      <c r="C14" s="40" t="s">
+      <c r="C14" s="33" t="s">
         <v>19</v>
       </c>
-      <c r="D14" s="43"/>
-      <c r="E14" s="40" t="s">
+      <c r="D14" s="36"/>
+      <c r="E14" s="33" t="s">
         <v>19</v>
       </c>
-      <c r="F14" s="43"/>
-      <c r="G14" s="40" t="s">
+      <c r="F14" s="36"/>
+      <c r="G14" s="33" t="s">
         <v>19</v>
       </c>
-      <c r="H14" s="43"/>
-      <c r="J14" s="65"/>
+      <c r="H14" s="36"/>
+      <c r="J14" s="58"/>
       <c r="K14" s="22" t="s">
         <v>30</v>
       </c>
@@ -2569,7 +2562,7 @@
       <c r="P14" s="24" t="s">
         <v>38</v>
       </c>
-      <c r="R14" s="65"/>
+      <c r="R14" s="58"/>
       <c r="S14" s="22" t="s">
         <v>39</v>
       </c>
@@ -2586,7 +2579,7 @@
       <c r="X14" s="24" t="s">
         <v>33</v>
       </c>
-      <c r="Z14" s="65"/>
+      <c r="Z14" s="58"/>
       <c r="AA14" s="22" t="s">
         <v>38</v>
       </c>
@@ -2606,16 +2599,16 @@
         <v>33</v>
       </c>
     </row>
-    <row r="15" spans="1:34" ht="8.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A15" s="65"/>
-      <c r="B15" s="66"/>
-      <c r="C15" s="46"/>
-      <c r="D15" s="49"/>
-      <c r="E15" s="46"/>
-      <c r="F15" s="49"/>
-      <c r="G15" s="46"/>
-      <c r="H15" s="49"/>
-      <c r="J15" s="65"/>
+    <row r="15" spans="1:34" ht="8.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A15" s="58"/>
+      <c r="B15" s="59"/>
+      <c r="C15" s="39"/>
+      <c r="D15" s="42"/>
+      <c r="E15" s="39"/>
+      <c r="F15" s="42"/>
+      <c r="G15" s="39"/>
+      <c r="H15" s="42"/>
+      <c r="J15" s="58"/>
       <c r="K15" s="22" t="s">
         <v>38</v>
       </c>
@@ -2634,7 +2627,7 @@
       <c r="P15" s="24" t="s">
         <v>33</v>
       </c>
-      <c r="R15" s="65"/>
+      <c r="R15" s="58"/>
       <c r="S15" s="22" t="s">
         <v>42</v>
       </c>
@@ -2649,7 +2642,7 @@
       <c r="X15" s="24" t="s">
         <v>36</v>
       </c>
-      <c r="Z15" s="65"/>
+      <c r="Z15" s="58"/>
       <c r="AA15" s="22" t="s">
         <v>33</v>
       </c>
@@ -2669,22 +2662,22 @@
         <v>36</v>
       </c>
     </row>
-    <row r="16" spans="1:34" ht="23.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A16" s="65"/>
-      <c r="B16" s="66"/>
-      <c r="C16" s="52" t="s">
+    <row r="16" spans="1:34" ht="23.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A16" s="58"/>
+      <c r="B16" s="59"/>
+      <c r="C16" s="45" t="s">
         <v>2</v>
       </c>
-      <c r="D16" s="53"/>
-      <c r="E16" s="42" t="s">
+      <c r="D16" s="46"/>
+      <c r="E16" s="35" t="s">
         <v>2</v>
       </c>
-      <c r="F16" s="53"/>
-      <c r="G16" s="42" t="s">
+      <c r="F16" s="46"/>
+      <c r="G16" s="35" t="s">
         <v>2</v>
       </c>
-      <c r="H16" s="51"/>
-      <c r="J16" s="65"/>
+      <c r="H16" s="44"/>
+      <c r="J16" s="58"/>
       <c r="K16" s="22" t="s">
         <v>33</v>
       </c>
@@ -2703,7 +2696,7 @@
       <c r="P16" s="24" t="s">
         <v>36</v>
       </c>
-      <c r="R16" s="65"/>
+      <c r="R16" s="58"/>
       <c r="S16" s="22"/>
       <c r="T16" s="23" t="s">
         <v>36</v>
@@ -2714,7 +2707,7 @@
       <c r="X16" s="24" t="s">
         <v>41</v>
       </c>
-      <c r="Z16" s="65"/>
+      <c r="Z16" s="58"/>
       <c r="AA16" s="22" t="s">
         <v>37</v>
       </c>
@@ -2730,16 +2723,16 @@
         <v>41</v>
       </c>
     </row>
-    <row r="17" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A17" s="65"/>
+    <row r="17" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A17" s="58"/>
       <c r="B17" s="16"/>
-      <c r="C17" s="55"/>
-      <c r="D17" s="56"/>
-      <c r="E17" s="55"/>
-      <c r="F17" s="56"/>
-      <c r="G17" s="55"/>
-      <c r="H17" s="57"/>
-      <c r="J17" s="65"/>
+      <c r="C17" s="48"/>
+      <c r="D17" s="49"/>
+      <c r="E17" s="48"/>
+      <c r="F17" s="49"/>
+      <c r="G17" s="48"/>
+      <c r="H17" s="50"/>
+      <c r="J17" s="58"/>
       <c r="K17" s="22" t="s">
         <v>37</v>
       </c>
@@ -2758,7 +2751,7 @@
       <c r="P17" s="24" t="s">
         <v>39</v>
       </c>
-      <c r="R17" s="65"/>
+      <c r="R17" s="58"/>
       <c r="S17" s="25"/>
       <c r="T17" s="26" t="s">
         <v>42</v>
@@ -2767,7 +2760,7 @@
       <c r="V17" s="26"/>
       <c r="W17" s="26"/>
       <c r="X17" s="27"/>
-      <c r="Z17" s="65"/>
+      <c r="Z17" s="58"/>
       <c r="AA17" s="22" t="s">
         <v>36</v>
       </c>
@@ -2781,24 +2774,24 @@
       <c r="AE17" s="23"/>
       <c r="AF17" s="24"/>
     </row>
-    <row r="18" spans="1:32" ht="18" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A18" s="65"/>
-      <c r="B18" s="66" t="s">
+    <row r="18" spans="1:32" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A18" s="58"/>
+      <c r="B18" s="59" t="s">
         <v>43</v>
       </c>
-      <c r="C18" s="40" t="s">
+      <c r="C18" s="33" t="s">
         <v>19</v>
       </c>
-      <c r="D18" s="43"/>
-      <c r="E18" s="40" t="s">
+      <c r="D18" s="36"/>
+      <c r="E18" s="33" t="s">
         <v>19</v>
       </c>
-      <c r="F18" s="43"/>
-      <c r="G18" s="40" t="s">
+      <c r="F18" s="36"/>
+      <c r="G18" s="33" t="s">
         <v>19</v>
       </c>
-      <c r="H18" s="43"/>
-      <c r="J18" s="65"/>
+      <c r="H18" s="36"/>
+      <c r="J18" s="58"/>
       <c r="K18" s="22" t="s">
         <v>36</v>
       </c>
@@ -2816,13 +2809,13 @@
         <v>42</v>
       </c>
       <c r="R18" s="28"/>
-      <c r="S18" s="29"/>
-      <c r="T18" s="29"/>
-      <c r="U18" s="29"/>
-      <c r="V18" s="29"/>
-      <c r="W18" s="29"/>
-      <c r="X18" s="29"/>
-      <c r="Z18" s="65"/>
+      <c r="S18" s="21"/>
+      <c r="T18" s="21"/>
+      <c r="U18" s="21"/>
+      <c r="V18" s="21"/>
+      <c r="W18" s="21"/>
+      <c r="X18" s="21"/>
+      <c r="Z18" s="58"/>
       <c r="AA18" s="25" t="s">
         <v>39</v>
       </c>
@@ -2834,16 +2827,16 @@
       <c r="AE18" s="26"/>
       <c r="AF18" s="27"/>
     </row>
-    <row r="19" spans="1:32" ht="6.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A19" s="65"/>
-      <c r="B19" s="66"/>
-      <c r="C19" s="46"/>
-      <c r="D19" s="49"/>
-      <c r="E19" s="46"/>
-      <c r="F19" s="49"/>
-      <c r="G19" s="46"/>
-      <c r="H19" s="49"/>
-      <c r="J19" s="65"/>
+    <row r="19" spans="1:32" ht="6.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A19" s="58"/>
+      <c r="B19" s="59"/>
+      <c r="C19" s="39"/>
+      <c r="D19" s="42"/>
+      <c r="E19" s="39"/>
+      <c r="F19" s="42"/>
+      <c r="G19" s="39"/>
+      <c r="H19" s="42"/>
+      <c r="J19" s="58"/>
       <c r="K19" s="22" t="s">
         <v>39</v>
       </c>
@@ -2861,36 +2854,36 @@
         <v>41</v>
       </c>
       <c r="R19" s="28"/>
-      <c r="S19" s="29"/>
-      <c r="T19" s="29"/>
-      <c r="U19" s="29"/>
-      <c r="V19" s="29"/>
-      <c r="W19" s="29"/>
-      <c r="X19" s="29"/>
+      <c r="S19" s="21"/>
+      <c r="T19" s="21"/>
+      <c r="U19" s="21"/>
+      <c r="V19" s="21"/>
+      <c r="W19" s="21"/>
+      <c r="X19" s="21"/>
       <c r="Z19" s="28"/>
-      <c r="AA19" s="29"/>
-      <c r="AB19" s="29"/>
-      <c r="AC19" s="29"/>
-      <c r="AD19" s="29"/>
-      <c r="AE19" s="29"/>
-      <c r="AF19" s="29"/>
-    </row>
-    <row r="20" spans="1:32" ht="28.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A20" s="65"/>
-      <c r="B20" s="66"/>
-      <c r="C20" s="52" t="s">
+      <c r="AA19" s="21"/>
+      <c r="AB19" s="21"/>
+      <c r="AC19" s="21"/>
+      <c r="AD19" s="21"/>
+      <c r="AE19" s="21"/>
+      <c r="AF19" s="21"/>
+    </row>
+    <row r="20" spans="1:32" ht="28.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A20" s="58"/>
+      <c r="B20" s="59"/>
+      <c r="C20" s="45" t="s">
         <v>2</v>
       </c>
-      <c r="D20" s="53"/>
-      <c r="E20" s="42" t="s">
+      <c r="D20" s="46"/>
+      <c r="E20" s="35" t="s">
         <v>2</v>
       </c>
-      <c r="F20" s="53"/>
-      <c r="G20" s="42" t="s">
+      <c r="F20" s="46"/>
+      <c r="G20" s="35" t="s">
         <v>2</v>
       </c>
-      <c r="H20" s="54"/>
-      <c r="J20" s="65"/>
+      <c r="H20" s="47"/>
+      <c r="J20" s="58"/>
       <c r="K20" s="22" t="s">
         <v>42</v>
       </c>
@@ -2904,40 +2897,40 @@
       <c r="O20" s="23"/>
       <c r="P20" s="24"/>
       <c r="R20" s="28"/>
-      <c r="S20" s="29"/>
-      <c r="T20" s="29"/>
-      <c r="U20" s="29"/>
-      <c r="V20" s="29"/>
-      <c r="W20" s="29"/>
-      <c r="X20" s="29"/>
+      <c r="S20" s="21"/>
+      <c r="T20" s="21"/>
+      <c r="U20" s="21"/>
+      <c r="V20" s="21"/>
+      <c r="W20" s="21"/>
+      <c r="X20" s="21"/>
       <c r="Z20" s="28"/>
-      <c r="AA20" s="29"/>
-      <c r="AB20" s="29"/>
-      <c r="AC20" s="29"/>
-      <c r="AD20" s="29"/>
-      <c r="AE20" s="29"/>
-      <c r="AF20" s="29"/>
-    </row>
-    <row r="21" spans="1:32" s="16" customFormat="1" ht="17.25" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="AA20" s="21"/>
+      <c r="AB20" s="21"/>
+      <c r="AC20" s="21"/>
+      <c r="AD20" s="21"/>
+      <c r="AE20" s="21"/>
+      <c r="AF20" s="21"/>
+    </row>
+    <row r="21" spans="1:32" s="16" customFormat="1" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A21" s="16" t="s">
         <v>27</v>
       </c>
-      <c r="C21" s="48" t="s">
+      <c r="C21" s="41" t="s">
         <v>0</v>
       </c>
-      <c r="D21" s="48" t="s">
+      <c r="D21" s="41" t="s">
         <v>8</v>
       </c>
-      <c r="E21" s="48" t="s">
+      <c r="E21" s="41" t="s">
         <v>9</v>
       </c>
-      <c r="F21" s="48" t="s">
+      <c r="F21" s="41" t="s">
         <v>10</v>
       </c>
-      <c r="G21" s="48" t="s">
+      <c r="G21" s="41" t="s">
         <v>11</v>
       </c>
-      <c r="H21" s="48" t="s">
+      <c r="H21" s="41" t="s">
         <v>12</v>
       </c>
       <c r="J21" s="16" t="s">
@@ -3004,8 +2997,8 @@
         <v>12</v>
       </c>
     </row>
-    <row r="22" spans="1:32" ht="15.75" hidden="1" customHeight="1" thickTop="1" x14ac:dyDescent="0.35">
-      <c r="A22" s="65" t="s">
+    <row r="22" spans="1:32" ht="15.75" hidden="1" customHeight="1" thickTop="1" x14ac:dyDescent="0.3">
+      <c r="A22" s="58" t="s">
         <v>16</v>
       </c>
       <c r="B22" s="17"/>
@@ -3027,7 +3020,7 @@
       <c r="H22" s="20" t="s">
         <v>17</v>
       </c>
-      <c r="J22" s="65" t="s">
+      <c r="J22" s="58" t="s">
         <v>16</v>
       </c>
       <c r="K22" s="18" t="s">
@@ -3048,7 +3041,7 @@
       <c r="P22" s="20" t="s">
         <v>20</v>
       </c>
-      <c r="R22" s="65" t="s">
+      <c r="R22" s="58" t="s">
         <v>16</v>
       </c>
       <c r="S22" s="18" t="s">
@@ -3069,20 +3062,20 @@
       <c r="X22" s="20" t="s">
         <v>20</v>
       </c>
-      <c r="Z22" s="65" t="s">
+      <c r="Z22" s="58" t="s">
         <v>16</v>
       </c>
-      <c r="AA22" s="30" t="s">
+      <c r="AA22" s="29" t="s">
         <v>24</v>
       </c>
-      <c r="AB22" s="29"/>
-      <c r="AC22" s="29"/>
-      <c r="AD22" s="29"/>
-      <c r="AE22" s="29"/>
-      <c r="AF22" s="29"/>
-    </row>
-    <row r="23" spans="1:32" ht="17.25" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A23" s="65"/>
+      <c r="AB22" s="21"/>
+      <c r="AC22" s="21"/>
+      <c r="AD22" s="21"/>
+      <c r="AE22" s="21"/>
+      <c r="AF22" s="21"/>
+    </row>
+    <row r="23" spans="1:32" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A23" s="58"/>
       <c r="B23" s="17"/>
       <c r="C23" s="22" t="s">
         <v>21</v>
@@ -3102,7 +3095,7 @@
       <c r="H23" s="24" t="s">
         <v>20</v>
       </c>
-      <c r="J23" s="65"/>
+      <c r="J23" s="58"/>
       <c r="K23" s="22" t="s">
         <v>20</v>
       </c>
@@ -3121,7 +3114,7 @@
       <c r="P23" s="24" t="s">
         <v>24</v>
       </c>
-      <c r="R23" s="65"/>
+      <c r="R23" s="58"/>
       <c r="S23" s="22" t="s">
         <v>22</v>
       </c>
@@ -3140,18 +3133,18 @@
       <c r="X23" s="24" t="s">
         <v>24</v>
       </c>
-      <c r="Z23" s="65"/>
-      <c r="AA23" s="31" t="s">
+      <c r="Z23" s="58"/>
+      <c r="AA23" s="30" t="s">
         <v>25</v>
       </c>
-      <c r="AB23" s="29"/>
-      <c r="AC23" s="29"/>
-      <c r="AD23" s="29"/>
-      <c r="AE23" s="29"/>
-      <c r="AF23" s="29"/>
-    </row>
-    <row r="24" spans="1:32" ht="17.25" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A24" s="65"/>
+      <c r="AB23" s="21"/>
+      <c r="AC23" s="21"/>
+      <c r="AD23" s="21"/>
+      <c r="AE23" s="21"/>
+      <c r="AF23" s="21"/>
+    </row>
+    <row r="24" spans="1:32" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A24" s="58"/>
       <c r="B24" s="17"/>
       <c r="C24" s="22" t="s">
         <v>23</v>
@@ -3171,7 +3164,7 @@
       <c r="H24" s="24" t="s">
         <v>21</v>
       </c>
-      <c r="J24" s="65"/>
+      <c r="J24" s="58"/>
       <c r="K24" s="22" t="s">
         <v>23</v>
       </c>
@@ -3190,7 +3183,7 @@
       <c r="P24" s="24" t="s">
         <v>25</v>
       </c>
-      <c r="R24" s="65"/>
+      <c r="R24" s="58"/>
       <c r="S24" s="22" t="s">
         <v>23</v>
       </c>
@@ -3209,18 +3202,18 @@
       <c r="X24" s="24" t="s">
         <v>25</v>
       </c>
-      <c r="Z24" s="65"/>
-      <c r="AA24" s="31" t="s">
+      <c r="Z24" s="58"/>
+      <c r="AA24" s="30" t="s">
         <v>26</v>
       </c>
-      <c r="AB24" s="29"/>
-      <c r="AC24" s="29"/>
-      <c r="AD24" s="29"/>
-      <c r="AE24" s="29"/>
-      <c r="AF24" s="29"/>
-    </row>
-    <row r="25" spans="1:32" ht="17.25" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A25" s="65"/>
+      <c r="AB24" s="21"/>
+      <c r="AC24" s="21"/>
+      <c r="AD24" s="21"/>
+      <c r="AE24" s="21"/>
+      <c r="AF24" s="21"/>
+    </row>
+    <row r="25" spans="1:32" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A25" s="58"/>
       <c r="B25" s="17"/>
       <c r="C25" s="22" t="s">
         <v>25</v>
@@ -3240,7 +3233,7 @@
       <c r="H25" s="24" t="s">
         <v>48</v>
       </c>
-      <c r="J25" s="65"/>
+      <c r="J25" s="58"/>
       <c r="K25" s="22" t="s">
         <v>24</v>
       </c>
@@ -3259,7 +3252,7 @@
       <c r="P25" s="24" t="s">
         <v>26</v>
       </c>
-      <c r="R25" s="65"/>
+      <c r="R25" s="58"/>
       <c r="S25" s="22" t="s">
         <v>25</v>
       </c>
@@ -3278,18 +3271,18 @@
       <c r="X25" s="24" t="s">
         <v>26</v>
       </c>
-      <c r="Z25" s="65"/>
-      <c r="AA25" s="31" t="s">
+      <c r="Z25" s="58"/>
+      <c r="AA25" s="30" t="s">
         <v>30</v>
       </c>
-      <c r="AB25" s="29"/>
-      <c r="AC25" s="29"/>
-      <c r="AD25" s="29"/>
-      <c r="AE25" s="29"/>
-      <c r="AF25" s="29"/>
-    </row>
-    <row r="26" spans="1:32" ht="17.25" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A26" s="65"/>
+      <c r="AB25" s="21"/>
+      <c r="AC25" s="21"/>
+      <c r="AD25" s="21"/>
+      <c r="AE25" s="21"/>
+      <c r="AF25" s="21"/>
+    </row>
+    <row r="26" spans="1:32" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A26" s="58"/>
       <c r="B26" s="17"/>
       <c r="C26" s="22" t="s">
         <v>26</v>
@@ -3309,7 +3302,7 @@
       <c r="H26" s="24" t="s">
         <v>24</v>
       </c>
-      <c r="J26" s="65"/>
+      <c r="J26" s="58"/>
       <c r="K26" s="22" t="s">
         <v>25</v>
       </c>
@@ -3328,7 +3321,7 @@
       <c r="P26" s="24" t="s">
         <v>32</v>
       </c>
-      <c r="R26" s="65"/>
+      <c r="R26" s="58"/>
       <c r="S26" s="22" t="s">
         <v>26</v>
       </c>
@@ -3347,18 +3340,18 @@
       <c r="X26" s="24" t="s">
         <v>28</v>
       </c>
-      <c r="Z26" s="65"/>
-      <c r="AA26" s="31" t="s">
+      <c r="Z26" s="58"/>
+      <c r="AA26" s="30" t="s">
         <v>29</v>
       </c>
-      <c r="AB26" s="29"/>
-      <c r="AC26" s="29"/>
-      <c r="AD26" s="29"/>
-      <c r="AE26" s="29"/>
-      <c r="AF26" s="29"/>
-    </row>
-    <row r="27" spans="1:32" ht="17.25" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A27" s="65"/>
+      <c r="AB26" s="21"/>
+      <c r="AC26" s="21"/>
+      <c r="AD26" s="21"/>
+      <c r="AE26" s="21"/>
+      <c r="AF26" s="21"/>
+    </row>
+    <row r="27" spans="1:32" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A27" s="58"/>
       <c r="B27" s="17"/>
       <c r="C27" s="22" t="s">
         <v>49</v>
@@ -3378,7 +3371,7 @@
       <c r="H27" s="24" t="s">
         <v>25</v>
       </c>
-      <c r="J27" s="65"/>
+      <c r="J27" s="58"/>
       <c r="K27" s="22" t="s">
         <v>26</v>
       </c>
@@ -3397,7 +3390,7 @@
       <c r="P27" s="24" t="s">
         <v>33</v>
       </c>
-      <c r="R27" s="65"/>
+      <c r="R27" s="58"/>
       <c r="S27" s="22" t="s">
         <v>32</v>
       </c>
@@ -3416,18 +3409,18 @@
       <c r="X27" s="24" t="s">
         <v>32</v>
       </c>
-      <c r="Z27" s="65"/>
-      <c r="AA27" s="31" t="s">
+      <c r="Z27" s="58"/>
+      <c r="AA27" s="30" t="s">
         <v>36</v>
       </c>
-      <c r="AB27" s="29"/>
-      <c r="AC27" s="29"/>
-      <c r="AD27" s="29"/>
-      <c r="AE27" s="29"/>
-      <c r="AF27" s="29"/>
-    </row>
-    <row r="28" spans="1:32" ht="17.25" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A28" s="65"/>
+      <c r="AB27" s="21"/>
+      <c r="AC27" s="21"/>
+      <c r="AD27" s="21"/>
+      <c r="AE27" s="21"/>
+      <c r="AF27" s="21"/>
+    </row>
+    <row r="28" spans="1:32" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A28" s="58"/>
       <c r="B28" s="17"/>
       <c r="C28" s="22" t="s">
         <v>31</v>
@@ -3447,7 +3440,7 @@
       <c r="H28" s="24" t="s">
         <v>26</v>
       </c>
-      <c r="J28" s="65"/>
+      <c r="J28" s="58"/>
       <c r="K28" s="22" t="s">
         <v>32</v>
       </c>
@@ -3466,7 +3459,7 @@
       <c r="P28" s="24" t="s">
         <v>36</v>
       </c>
-      <c r="R28" s="65"/>
+      <c r="R28" s="58"/>
       <c r="S28" s="22" t="s">
         <v>31</v>
       </c>
@@ -3485,18 +3478,18 @@
       <c r="X28" s="24" t="s">
         <v>33</v>
       </c>
-      <c r="Z28" s="65"/>
-      <c r="AA28" s="32" t="s">
+      <c r="Z28" s="58"/>
+      <c r="AA28" s="31" t="s">
         <v>39</v>
       </c>
-      <c r="AB28" s="29"/>
-      <c r="AC28" s="29"/>
-      <c r="AD28" s="29"/>
-      <c r="AE28" s="29"/>
-      <c r="AF28" s="29"/>
-    </row>
-    <row r="29" spans="1:32" ht="17.25" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A29" s="65"/>
+      <c r="AB28" s="21"/>
+      <c r="AC28" s="21"/>
+      <c r="AD28" s="21"/>
+      <c r="AE28" s="21"/>
+      <c r="AF28" s="21"/>
+    </row>
+    <row r="29" spans="1:32" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A29" s="58"/>
       <c r="B29" s="17"/>
       <c r="C29" s="22" t="s">
         <v>30</v>
@@ -3516,7 +3509,7 @@
       <c r="H29" s="24" t="s">
         <v>28</v>
       </c>
-      <c r="J29" s="65"/>
+      <c r="J29" s="58"/>
       <c r="K29" s="22" t="s">
         <v>31</v>
       </c>
@@ -3535,7 +3528,7 @@
       <c r="P29" s="24" t="s">
         <v>39</v>
       </c>
-      <c r="R29" s="65"/>
+      <c r="R29" s="58"/>
       <c r="S29" s="22" t="s">
         <v>30</v>
       </c>
@@ -3555,15 +3548,15 @@
         <v>37</v>
       </c>
       <c r="Z29" s="28"/>
-      <c r="AA29" s="29"/>
-      <c r="AB29" s="29"/>
-      <c r="AC29" s="29"/>
-      <c r="AD29" s="29"/>
-      <c r="AE29" s="29"/>
-      <c r="AF29" s="29"/>
-    </row>
-    <row r="30" spans="1:32" ht="17.25" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A30" s="65"/>
+      <c r="AA29" s="21"/>
+      <c r="AB29" s="21"/>
+      <c r="AC29" s="21"/>
+      <c r="AD29" s="21"/>
+      <c r="AE29" s="21"/>
+      <c r="AF29" s="21"/>
+    </row>
+    <row r="30" spans="1:32" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A30" s="58"/>
       <c r="B30" s="17"/>
       <c r="C30" s="22" t="s">
         <v>33</v>
@@ -3583,7 +3576,7 @@
       <c r="H30" s="24" t="s">
         <v>32</v>
       </c>
-      <c r="J30" s="65"/>
+      <c r="J30" s="58"/>
       <c r="K30" s="22" t="s">
         <v>30</v>
       </c>
@@ -3598,7 +3591,7 @@
         <v>37</v>
       </c>
       <c r="P30" s="24"/>
-      <c r="R30" s="65"/>
+      <c r="R30" s="58"/>
       <c r="S30" s="22" t="s">
         <v>33</v>
       </c>
@@ -3612,15 +3605,15 @@
         <v>36</v>
       </c>
       <c r="Z30" s="28"/>
-      <c r="AA30" s="29"/>
-      <c r="AB30" s="29"/>
-      <c r="AC30" s="29"/>
-      <c r="AD30" s="29"/>
-      <c r="AE30" s="29"/>
-      <c r="AF30" s="29"/>
-    </row>
-    <row r="31" spans="1:32" ht="17.25" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A31" s="65"/>
+      <c r="AA30" s="21"/>
+      <c r="AB30" s="21"/>
+      <c r="AC30" s="21"/>
+      <c r="AD30" s="21"/>
+      <c r="AE30" s="21"/>
+      <c r="AF30" s="21"/>
+    </row>
+    <row r="31" spans="1:32" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A31" s="58"/>
       <c r="B31" s="17"/>
       <c r="C31" s="22" t="s">
         <v>37</v>
@@ -3640,7 +3633,7 @@
       <c r="H31" s="24" t="s">
         <v>29</v>
       </c>
-      <c r="J31" s="65"/>
+      <c r="J31" s="58"/>
       <c r="K31" s="22" t="s">
         <v>33</v>
       </c>
@@ -3655,7 +3648,7 @@
         <v>36</v>
       </c>
       <c r="P31" s="24"/>
-      <c r="R31" s="65"/>
+      <c r="R31" s="58"/>
       <c r="S31" s="22" t="s">
         <v>36</v>
       </c>
@@ -3667,15 +3660,15 @@
         <v>39</v>
       </c>
       <c r="Z31" s="28"/>
-      <c r="AA31" s="29"/>
-      <c r="AB31" s="29"/>
-      <c r="AC31" s="29"/>
-      <c r="AD31" s="29"/>
-      <c r="AE31" s="29"/>
-      <c r="AF31" s="29"/>
-    </row>
-    <row r="32" spans="1:32" ht="17.25" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A32" s="65"/>
+      <c r="AA31" s="21"/>
+      <c r="AB31" s="21"/>
+      <c r="AC31" s="21"/>
+      <c r="AD31" s="21"/>
+      <c r="AE31" s="21"/>
+      <c r="AF31" s="21"/>
+    </row>
+    <row r="32" spans="1:32" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A32" s="58"/>
       <c r="B32" s="17"/>
       <c r="C32" s="22" t="s">
         <v>36</v>
@@ -3695,7 +3688,7 @@
       <c r="H32" s="24" t="s">
         <v>33</v>
       </c>
-      <c r="J32" s="65"/>
+      <c r="J32" s="58"/>
       <c r="K32" s="22" t="s">
         <v>37</v>
       </c>
@@ -3706,7 +3699,7 @@
       <c r="N32" s="23"/>
       <c r="O32" s="23"/>
       <c r="P32" s="24"/>
-      <c r="R32" s="65"/>
+      <c r="R32" s="58"/>
       <c r="S32" s="22" t="s">
         <v>39</v>
       </c>
@@ -3716,15 +3709,15 @@
       <c r="W32" s="23"/>
       <c r="X32" s="24"/>
       <c r="Z32" s="28"/>
-      <c r="AA32" s="29"/>
-      <c r="AB32" s="29"/>
-      <c r="AC32" s="29"/>
-      <c r="AD32" s="29"/>
-      <c r="AE32" s="29"/>
-      <c r="AF32" s="29"/>
-    </row>
-    <row r="33" spans="1:32" ht="17.25" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A33" s="65"/>
+      <c r="AA32" s="21"/>
+      <c r="AB32" s="21"/>
+      <c r="AC32" s="21"/>
+      <c r="AD32" s="21"/>
+      <c r="AE32" s="21"/>
+      <c r="AF32" s="21"/>
+    </row>
+    <row r="33" spans="1:32" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A33" s="58"/>
       <c r="B33" s="17"/>
       <c r="C33" s="22" t="s">
         <v>39</v>
@@ -3744,7 +3737,7 @@
       <c r="H33" s="24" t="s">
         <v>37</v>
       </c>
-      <c r="J33" s="65"/>
+      <c r="J33" s="58"/>
       <c r="K33" s="22" t="s">
         <v>36</v>
       </c>
@@ -3755,7 +3748,7 @@
       <c r="N33" s="23"/>
       <c r="O33" s="23"/>
       <c r="P33" s="24"/>
-      <c r="R33" s="65"/>
+      <c r="R33" s="58"/>
       <c r="S33" s="25" t="s">
         <v>42</v>
       </c>
@@ -3765,15 +3758,15 @@
       <c r="W33" s="26"/>
       <c r="X33" s="27"/>
       <c r="Z33" s="28"/>
-      <c r="AA33" s="29"/>
-      <c r="AB33" s="29"/>
-      <c r="AC33" s="29"/>
-      <c r="AD33" s="29"/>
-      <c r="AE33" s="29"/>
-      <c r="AF33" s="29"/>
-    </row>
-    <row r="34" spans="1:32" ht="17.25" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A34" s="65"/>
+      <c r="AA33" s="21"/>
+      <c r="AB33" s="21"/>
+      <c r="AC33" s="21"/>
+      <c r="AD33" s="21"/>
+      <c r="AE33" s="21"/>
+      <c r="AF33" s="21"/>
+    </row>
+    <row r="34" spans="1:32" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A34" s="58"/>
       <c r="B34" s="17"/>
       <c r="C34" s="22"/>
       <c r="D34" s="23" t="s">
@@ -3791,7 +3784,7 @@
       <c r="H34" s="24" t="s">
         <v>36</v>
       </c>
-      <c r="J34" s="65"/>
+      <c r="J34" s="58"/>
       <c r="K34" s="25" t="s">
         <v>39</v>
       </c>
@@ -3801,22 +3794,22 @@
       <c r="O34" s="26"/>
       <c r="P34" s="27"/>
       <c r="R34" s="28"/>
-      <c r="S34" s="29"/>
-      <c r="T34" s="29"/>
-      <c r="U34" s="29"/>
-      <c r="V34" s="29"/>
-      <c r="W34" s="29"/>
-      <c r="X34" s="29"/>
+      <c r="S34" s="21"/>
+      <c r="T34" s="21"/>
+      <c r="U34" s="21"/>
+      <c r="V34" s="21"/>
+      <c r="W34" s="21"/>
+      <c r="X34" s="21"/>
       <c r="Z34" s="28"/>
-      <c r="AA34" s="29"/>
-      <c r="AB34" s="29"/>
-      <c r="AC34" s="29"/>
-      <c r="AD34" s="29"/>
-      <c r="AE34" s="29"/>
-      <c r="AF34" s="29"/>
-    </row>
-    <row r="35" spans="1:32" ht="17.25" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A35" s="65"/>
+      <c r="AA34" s="21"/>
+      <c r="AB34" s="21"/>
+      <c r="AC34" s="21"/>
+      <c r="AD34" s="21"/>
+      <c r="AE34" s="21"/>
+      <c r="AF34" s="21"/>
+    </row>
+    <row r="35" spans="1:32" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A35" s="58"/>
       <c r="B35" s="17"/>
       <c r="C35" s="22"/>
       <c r="D35" s="23" t="s">
@@ -3833,29 +3826,29 @@
         <v>39</v>
       </c>
       <c r="J35" s="28"/>
-      <c r="K35" s="29"/>
-      <c r="L35" s="29"/>
-      <c r="M35" s="29"/>
-      <c r="N35" s="29"/>
-      <c r="O35" s="29"/>
-      <c r="P35" s="29"/>
+      <c r="K35" s="21"/>
+      <c r="L35" s="21"/>
+      <c r="M35" s="21"/>
+      <c r="N35" s="21"/>
+      <c r="O35" s="21"/>
+      <c r="P35" s="21"/>
       <c r="R35" s="28"/>
-      <c r="S35" s="29"/>
-      <c r="T35" s="29"/>
-      <c r="U35" s="29"/>
-      <c r="V35" s="29"/>
-      <c r="W35" s="29"/>
-      <c r="X35" s="29"/>
+      <c r="S35" s="21"/>
+      <c r="T35" s="21"/>
+      <c r="U35" s="21"/>
+      <c r="V35" s="21"/>
+      <c r="W35" s="21"/>
+      <c r="X35" s="21"/>
       <c r="Z35" s="28"/>
-      <c r="AA35" s="29"/>
-      <c r="AB35" s="29"/>
-      <c r="AC35" s="29"/>
-      <c r="AD35" s="29"/>
-      <c r="AE35" s="29"/>
-      <c r="AF35" s="29"/>
-    </row>
-    <row r="36" spans="1:32" ht="17.25" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A36" s="65"/>
+      <c r="AA35" s="21"/>
+      <c r="AB35" s="21"/>
+      <c r="AC35" s="21"/>
+      <c r="AD35" s="21"/>
+      <c r="AE35" s="21"/>
+      <c r="AF35" s="21"/>
+    </row>
+    <row r="36" spans="1:32" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A36" s="58"/>
       <c r="B36" s="17"/>
       <c r="C36" s="22"/>
       <c r="D36" s="23"/>
@@ -3870,29 +3863,29 @@
         <v>41</v>
       </c>
       <c r="J36" s="28"/>
-      <c r="K36" s="29"/>
-      <c r="L36" s="29"/>
-      <c r="M36" s="29"/>
-      <c r="N36" s="29"/>
-      <c r="O36" s="29"/>
-      <c r="P36" s="29"/>
+      <c r="K36" s="21"/>
+      <c r="L36" s="21"/>
+      <c r="M36" s="21"/>
+      <c r="N36" s="21"/>
+      <c r="O36" s="21"/>
+      <c r="P36" s="21"/>
       <c r="R36" s="28"/>
-      <c r="S36" s="29"/>
-      <c r="T36" s="29"/>
-      <c r="U36" s="29"/>
-      <c r="V36" s="29"/>
-      <c r="W36" s="29"/>
-      <c r="X36" s="29"/>
+      <c r="S36" s="21"/>
+      <c r="T36" s="21"/>
+      <c r="U36" s="21"/>
+      <c r="V36" s="21"/>
+      <c r="W36" s="21"/>
+      <c r="X36" s="21"/>
       <c r="Z36" s="28"/>
-      <c r="AA36" s="29"/>
-      <c r="AB36" s="29"/>
-      <c r="AC36" s="29"/>
-      <c r="AD36" s="29"/>
-      <c r="AE36" s="29"/>
-      <c r="AF36" s="29"/>
-    </row>
-    <row r="37" spans="1:32" ht="17.25" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A37" s="65"/>
+      <c r="AA36" s="21"/>
+      <c r="AB36" s="21"/>
+      <c r="AC36" s="21"/>
+      <c r="AD36" s="21"/>
+      <c r="AE36" s="21"/>
+      <c r="AF36" s="21"/>
+    </row>
+    <row r="37" spans="1:32" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A37" s="58"/>
       <c r="B37" s="17"/>
       <c r="C37" s="25"/>
       <c r="D37" s="26"/>
@@ -3903,55 +3896,54 @@
       </c>
       <c r="H37" s="27"/>
       <c r="J37" s="28"/>
-      <c r="K37" s="29"/>
-      <c r="L37" s="29"/>
-      <c r="M37" s="29"/>
-      <c r="N37" s="29"/>
-      <c r="O37" s="29"/>
-      <c r="P37" s="29"/>
+      <c r="K37" s="21"/>
+      <c r="L37" s="21"/>
+      <c r="M37" s="21"/>
+      <c r="N37" s="21"/>
+      <c r="O37" s="21"/>
+      <c r="P37" s="21"/>
       <c r="R37" s="28"/>
-      <c r="S37" s="29"/>
-      <c r="T37" s="29"/>
-      <c r="U37" s="29"/>
-      <c r="V37" s="29"/>
-      <c r="W37" s="29"/>
-      <c r="X37" s="29"/>
+      <c r="S37" s="21"/>
+      <c r="T37" s="21"/>
+      <c r="U37" s="21"/>
+      <c r="V37" s="21"/>
+      <c r="W37" s="21"/>
+      <c r="X37" s="21"/>
       <c r="Z37" s="28"/>
-      <c r="AA37" s="29"/>
-      <c r="AB37" s="29"/>
-      <c r="AC37" s="29"/>
-      <c r="AD37" s="29"/>
-      <c r="AE37" s="29"/>
-      <c r="AF37" s="29"/>
-    </row>
-    <row r="38" spans="1:32" ht="17.25" hidden="1" x14ac:dyDescent="0.35">
-      <c r="C38" s="29"/>
-      <c r="D38" s="29"/>
-      <c r="E38" s="29"/>
-      <c r="F38" s="29"/>
-      <c r="G38" s="29"/>
-      <c r="H38" s="29"/>
-      <c r="K38" s="29"/>
-      <c r="L38" s="29"/>
-      <c r="M38" s="29"/>
-      <c r="N38" s="29"/>
-      <c r="O38" s="29"/>
-      <c r="P38" s="29"/>
-      <c r="S38" s="29"/>
-      <c r="T38" s="29"/>
-      <c r="U38" s="29"/>
-      <c r="V38" s="29"/>
-      <c r="W38" s="29"/>
-      <c r="X38" s="29"/>
-      <c r="Z38" s="33"/>
-      <c r="AA38" s="29"/>
-      <c r="AB38" s="29"/>
-      <c r="AC38" s="29"/>
-      <c r="AD38" s="29"/>
-      <c r="AE38" s="29"/>
-      <c r="AF38" s="29"/>
-    </row>
-    <row r="39" spans="1:32" s="16" customFormat="1" ht="17.25" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="AA37" s="21"/>
+      <c r="AB37" s="21"/>
+      <c r="AC37" s="21"/>
+      <c r="AD37" s="21"/>
+      <c r="AE37" s="21"/>
+      <c r="AF37" s="21"/>
+    </row>
+    <row r="38" spans="1:32" hidden="1" x14ac:dyDescent="0.3">
+      <c r="C38" s="21"/>
+      <c r="D38" s="21"/>
+      <c r="E38" s="21"/>
+      <c r="F38" s="21"/>
+      <c r="G38" s="21"/>
+      <c r="H38" s="21"/>
+      <c r="K38" s="21"/>
+      <c r="L38" s="21"/>
+      <c r="M38" s="21"/>
+      <c r="N38" s="21"/>
+      <c r="O38" s="21"/>
+      <c r="P38" s="21"/>
+      <c r="S38" s="21"/>
+      <c r="T38" s="21"/>
+      <c r="U38" s="21"/>
+      <c r="V38" s="21"/>
+      <c r="W38" s="21"/>
+      <c r="X38" s="21"/>
+      <c r="AA38" s="21"/>
+      <c r="AB38" s="21"/>
+      <c r="AC38" s="21"/>
+      <c r="AD38" s="21"/>
+      <c r="AE38" s="21"/>
+      <c r="AF38" s="21"/>
+    </row>
+    <row r="39" spans="1:32" s="16" customFormat="1" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A39" s="16" t="s">
         <v>40</v>
       </c>
@@ -4015,16 +4007,9 @@
       <c r="X39" s="15" t="s">
         <v>12</v>
       </c>
-      <c r="Z39" s="34"/>
-      <c r="AA39" s="34"/>
-      <c r="AB39" s="34"/>
-      <c r="AC39" s="34"/>
-      <c r="AD39" s="34"/>
-      <c r="AE39" s="34"/>
-      <c r="AF39" s="34"/>
-    </row>
-    <row r="40" spans="1:32" ht="15.75" hidden="1" customHeight="1" thickTop="1" x14ac:dyDescent="0.35">
-      <c r="A40" s="65" t="s">
+    </row>
+    <row r="40" spans="1:32" ht="15.75" hidden="1" customHeight="1" thickTop="1" x14ac:dyDescent="0.3">
+      <c r="A40" s="58" t="s">
         <v>16</v>
       </c>
       <c r="B40" s="17"/>
@@ -4046,7 +4031,7 @@
       <c r="H40" s="20" t="s">
         <v>17</v>
       </c>
-      <c r="J40" s="65" t="s">
+      <c r="J40" s="58" t="s">
         <v>16</v>
       </c>
       <c r="K40" s="18" t="s">
@@ -4067,7 +4052,7 @@
       <c r="P40" s="20" t="s">
         <v>20</v>
       </c>
-      <c r="R40" s="65" t="s">
+      <c r="R40" s="58" t="s">
         <v>16</v>
       </c>
       <c r="S40" s="18" t="s">
@@ -4088,16 +4073,10 @@
       <c r="X40" s="20" t="s">
         <v>20</v>
       </c>
-      <c r="Z40" s="35"/>
-      <c r="AA40" s="33"/>
-      <c r="AB40" s="33"/>
-      <c r="AC40" s="33"/>
-      <c r="AD40" s="33"/>
-      <c r="AE40" s="33"/>
-      <c r="AF40" s="33"/>
-    </row>
-    <row r="41" spans="1:32" ht="17.25" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A41" s="65"/>
+      <c r="Z40" s="32"/>
+    </row>
+    <row r="41" spans="1:32" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A41" s="58"/>
       <c r="B41" s="17"/>
       <c r="C41" s="22" t="s">
         <v>20</v>
@@ -4117,7 +4096,7 @@
       <c r="H41" s="24" t="s">
         <v>20</v>
       </c>
-      <c r="J41" s="65"/>
+      <c r="J41" s="58"/>
       <c r="K41" s="22" t="s">
         <v>20</v>
       </c>
@@ -4136,7 +4115,7 @@
       <c r="P41" s="24" t="s">
         <v>22</v>
       </c>
-      <c r="R41" s="65"/>
+      <c r="R41" s="58"/>
       <c r="S41" s="22" t="s">
         <v>20</v>
       </c>
@@ -4155,16 +4134,10 @@
       <c r="X41" s="24" t="s">
         <v>22</v>
       </c>
-      <c r="Z41" s="35"/>
-      <c r="AA41" s="33"/>
-      <c r="AB41" s="33"/>
-      <c r="AC41" s="33"/>
-      <c r="AD41" s="33"/>
-      <c r="AE41" s="33"/>
-      <c r="AF41" s="33"/>
-    </row>
-    <row r="42" spans="1:32" ht="17.25" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A42" s="65"/>
+      <c r="Z41" s="32"/>
+    </row>
+    <row r="42" spans="1:32" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A42" s="58"/>
       <c r="B42" s="17"/>
       <c r="C42" s="22" t="s">
         <v>21</v>
@@ -4184,7 +4157,7 @@
       <c r="H42" s="24" t="s">
         <v>22</v>
       </c>
-      <c r="J42" s="65"/>
+      <c r="J42" s="58"/>
       <c r="K42" s="22" t="s">
         <v>21</v>
       </c>
@@ -4203,7 +4176,7 @@
       <c r="P42" s="24" t="s">
         <v>25</v>
       </c>
-      <c r="R42" s="65"/>
+      <c r="R42" s="58"/>
       <c r="S42" s="22" t="s">
         <v>22</v>
       </c>
@@ -4222,16 +4195,10 @@
       <c r="X42" s="24" t="s">
         <v>24</v>
       </c>
-      <c r="Z42" s="35"/>
-      <c r="AA42" s="33"/>
-      <c r="AB42" s="33"/>
-      <c r="AC42" s="33"/>
-      <c r="AD42" s="33"/>
-      <c r="AE42" s="33"/>
-      <c r="AF42" s="33"/>
-    </row>
-    <row r="43" spans="1:32" ht="17.25" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A43" s="65"/>
+      <c r="Z42" s="32"/>
+    </row>
+    <row r="43" spans="1:32" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A43" s="58"/>
       <c r="B43" s="17"/>
       <c r="C43" s="22" t="s">
         <v>23</v>
@@ -4251,7 +4218,7 @@
       <c r="H43" s="24" t="s">
         <v>48</v>
       </c>
-      <c r="J43" s="65"/>
+      <c r="J43" s="58"/>
       <c r="K43" s="22" t="s">
         <v>23</v>
       </c>
@@ -4270,7 +4237,7 @@
       <c r="P43" s="24" t="s">
         <v>26</v>
       </c>
-      <c r="R43" s="65"/>
+      <c r="R43" s="58"/>
       <c r="S43" s="22" t="s">
         <v>21</v>
       </c>
@@ -4289,16 +4256,10 @@
       <c r="X43" s="24" t="s">
         <v>25</v>
       </c>
-      <c r="Z43" s="35"/>
-      <c r="AA43" s="33"/>
-      <c r="AB43" s="33"/>
-      <c r="AC43" s="33"/>
-      <c r="AD43" s="33"/>
-      <c r="AE43" s="33"/>
-      <c r="AF43" s="33"/>
-    </row>
-    <row r="44" spans="1:32" ht="17.25" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A44" s="65"/>
+      <c r="Z43" s="32"/>
+    </row>
+    <row r="44" spans="1:32" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A44" s="58"/>
       <c r="B44" s="17"/>
       <c r="C44" s="22" t="s">
         <v>48</v>
@@ -4318,7 +4279,7 @@
       <c r="H44" s="24" t="s">
         <v>24</v>
       </c>
-      <c r="J44" s="65"/>
+      <c r="J44" s="58"/>
       <c r="K44" s="22" t="s">
         <v>25</v>
       </c>
@@ -4337,7 +4298,7 @@
       <c r="P44" s="24" t="s">
         <v>38</v>
       </c>
-      <c r="R44" s="65"/>
+      <c r="R44" s="58"/>
       <c r="S44" s="22" t="s">
         <v>23</v>
       </c>
@@ -4356,16 +4317,10 @@
       <c r="X44" s="24" t="s">
         <v>26</v>
       </c>
-      <c r="Z44" s="35"/>
-      <c r="AA44" s="33"/>
-      <c r="AB44" s="33"/>
-      <c r="AC44" s="33"/>
-      <c r="AD44" s="33"/>
-      <c r="AE44" s="33"/>
-      <c r="AF44" s="33"/>
-    </row>
-    <row r="45" spans="1:32" ht="17.25" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A45" s="65"/>
+      <c r="Z44" s="32"/>
+    </row>
+    <row r="45" spans="1:32" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A45" s="58"/>
       <c r="B45" s="17"/>
       <c r="C45" s="22" t="s">
         <v>24</v>
@@ -4385,7 +4340,7 @@
       <c r="H45" s="24" t="s">
         <v>25</v>
       </c>
-      <c r="J45" s="65"/>
+      <c r="J45" s="58"/>
       <c r="K45" s="22" t="s">
         <v>26</v>
       </c>
@@ -4404,7 +4359,7 @@
       <c r="P45" s="24" t="s">
         <v>33</v>
       </c>
-      <c r="R45" s="65"/>
+      <c r="R45" s="58"/>
       <c r="S45" s="22" t="s">
         <v>24</v>
       </c>
@@ -4423,16 +4378,10 @@
       <c r="X45" s="24" t="s">
         <v>28</v>
       </c>
-      <c r="Z45" s="35"/>
-      <c r="AA45" s="33"/>
-      <c r="AB45" s="33"/>
-      <c r="AC45" s="33"/>
-      <c r="AD45" s="33"/>
-      <c r="AE45" s="33"/>
-      <c r="AF45" s="33"/>
-    </row>
-    <row r="46" spans="1:32" ht="17.25" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A46" s="65"/>
+      <c r="Z45" s="32"/>
+    </row>
+    <row r="46" spans="1:32" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A46" s="58"/>
       <c r="B46" s="17"/>
       <c r="C46" s="22" t="s">
         <v>25</v>
@@ -4452,7 +4401,7 @@
       <c r="H46" s="24" t="s">
         <v>26</v>
       </c>
-      <c r="J46" s="65"/>
+      <c r="J46" s="58"/>
       <c r="K46" s="22" t="s">
         <v>33</v>
       </c>
@@ -4471,7 +4420,7 @@
       <c r="P46" s="24" t="s">
         <v>36</v>
       </c>
-      <c r="R46" s="65"/>
+      <c r="R46" s="58"/>
       <c r="S46" s="22" t="s">
         <v>25</v>
       </c>
@@ -4490,16 +4439,10 @@
       <c r="X46" s="24" t="s">
         <v>32</v>
       </c>
-      <c r="Z46" s="35"/>
-      <c r="AA46" s="33"/>
-      <c r="AB46" s="33"/>
-      <c r="AC46" s="33"/>
-      <c r="AD46" s="33"/>
-      <c r="AE46" s="33"/>
-      <c r="AF46" s="33"/>
-    </row>
-    <row r="47" spans="1:32" ht="17.25" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A47" s="65"/>
+      <c r="Z46" s="32"/>
+    </row>
+    <row r="47" spans="1:32" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A47" s="58"/>
       <c r="B47" s="17"/>
       <c r="C47" s="22" t="s">
         <v>26</v>
@@ -4519,7 +4462,7 @@
       <c r="H47" s="24" t="s">
         <v>28</v>
       </c>
-      <c r="J47" s="65"/>
+      <c r="J47" s="58"/>
       <c r="K47" s="22" t="s">
         <v>36</v>
       </c>
@@ -4534,7 +4477,7 @@
         <v>33</v>
       </c>
       <c r="P47" s="24"/>
-      <c r="R47" s="65"/>
+      <c r="R47" s="58"/>
       <c r="S47" s="22" t="s">
         <v>26</v>
       </c>
@@ -4553,16 +4496,10 @@
       <c r="X47" s="24" t="s">
         <v>30</v>
       </c>
-      <c r="Z47" s="35"/>
-      <c r="AA47" s="33"/>
-      <c r="AB47" s="33"/>
-      <c r="AC47" s="33"/>
-      <c r="AD47" s="33"/>
-      <c r="AE47" s="33"/>
-      <c r="AF47" s="33"/>
-    </row>
-    <row r="48" spans="1:32" ht="17.25" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A48" s="65"/>
+      <c r="Z47" s="32"/>
+    </row>
+    <row r="48" spans="1:32" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A48" s="58"/>
       <c r="B48" s="17"/>
       <c r="C48" s="22" t="s">
         <v>28</v>
@@ -4582,7 +4519,7 @@
       <c r="H48" s="24" t="s">
         <v>32</v>
       </c>
-      <c r="J48" s="65"/>
+      <c r="J48" s="58"/>
       <c r="K48" s="22" t="s">
         <v>39</v>
       </c>
@@ -4593,7 +4530,7 @@
         <v>37</v>
       </c>
       <c r="P48" s="24"/>
-      <c r="R48" s="65"/>
+      <c r="R48" s="58"/>
       <c r="S48" s="22" t="s">
         <v>28</v>
       </c>
@@ -4610,16 +4547,10 @@
       <c r="X48" s="24" t="s">
         <v>38</v>
       </c>
-      <c r="Z48" s="35"/>
-      <c r="AA48" s="33"/>
-      <c r="AB48" s="33"/>
-      <c r="AC48" s="33"/>
-      <c r="AD48" s="33"/>
-      <c r="AE48" s="33"/>
-      <c r="AF48" s="33"/>
-    </row>
-    <row r="49" spans="1:32" ht="17.25" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A49" s="65"/>
+      <c r="Z48" s="32"/>
+    </row>
+    <row r="49" spans="1:26" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A49" s="58"/>
       <c r="B49" s="17"/>
       <c r="C49" s="22" t="s">
         <v>31</v>
@@ -4639,7 +4570,7 @@
       <c r="H49" s="24" t="s">
         <v>38</v>
       </c>
-      <c r="J49" s="65"/>
+      <c r="J49" s="58"/>
       <c r="K49" s="22"/>
       <c r="L49" s="23"/>
       <c r="M49" s="23"/>
@@ -4648,7 +4579,7 @@
         <v>36</v>
       </c>
       <c r="P49" s="24"/>
-      <c r="R49" s="65"/>
+      <c r="R49" s="58"/>
       <c r="S49" s="22" t="s">
         <v>30</v>
       </c>
@@ -4663,16 +4594,10 @@
       <c r="X49" s="24" t="s">
         <v>33</v>
       </c>
-      <c r="Z49" s="35"/>
-      <c r="AA49" s="33"/>
-      <c r="AB49" s="33"/>
-      <c r="AC49" s="33"/>
-      <c r="AD49" s="33"/>
-      <c r="AE49" s="33"/>
-      <c r="AF49" s="33"/>
-    </row>
-    <row r="50" spans="1:32" ht="17.25" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A50" s="65"/>
+      <c r="Z49" s="32"/>
+    </row>
+    <row r="50" spans="1:26" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A50" s="58"/>
       <c r="B50" s="17"/>
       <c r="C50" s="22" t="s">
         <v>29</v>
@@ -4692,7 +4617,7 @@
       <c r="H50" s="24" t="s">
         <v>33</v>
       </c>
-      <c r="J50" s="65"/>
+      <c r="J50" s="58"/>
       <c r="K50" s="25"/>
       <c r="L50" s="26"/>
       <c r="M50" s="26"/>
@@ -4701,7 +4626,7 @@
         <v>42</v>
       </c>
       <c r="P50" s="27"/>
-      <c r="R50" s="65"/>
+      <c r="R50" s="58"/>
       <c r="S50" s="22" t="s">
         <v>33</v>
       </c>
@@ -4714,16 +4639,10 @@
       <c r="X50" s="24" t="s">
         <v>37</v>
       </c>
-      <c r="Z50" s="35"/>
-      <c r="AA50" s="33"/>
-      <c r="AB50" s="33"/>
-      <c r="AC50" s="33"/>
-      <c r="AD50" s="33"/>
-      <c r="AE50" s="33"/>
-      <c r="AF50" s="33"/>
-    </row>
-    <row r="51" spans="1:32" ht="17.25" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A51" s="65"/>
+      <c r="Z50" s="32"/>
+    </row>
+    <row r="51" spans="1:26" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A51" s="58"/>
       <c r="B51" s="17"/>
       <c r="C51" s="22" t="s">
         <v>38</v>
@@ -4744,13 +4663,13 @@
         <v>37</v>
       </c>
       <c r="J51" s="28"/>
-      <c r="K51" s="29"/>
-      <c r="L51" s="29"/>
-      <c r="M51" s="29"/>
-      <c r="N51" s="29"/>
-      <c r="O51" s="29"/>
-      <c r="P51" s="29"/>
-      <c r="R51" s="65"/>
+      <c r="K51" s="21"/>
+      <c r="L51" s="21"/>
+      <c r="M51" s="21"/>
+      <c r="N51" s="21"/>
+      <c r="O51" s="21"/>
+      <c r="P51" s="21"/>
+      <c r="R51" s="58"/>
       <c r="S51" s="22" t="s">
         <v>36</v>
       </c>
@@ -4763,16 +4682,9 @@
       <c r="X51" s="24" t="s">
         <v>36</v>
       </c>
-      <c r="Z51" s="33"/>
-      <c r="AA51" s="33"/>
-      <c r="AB51" s="33"/>
-      <c r="AC51" s="33"/>
-      <c r="AD51" s="33"/>
-      <c r="AE51" s="33"/>
-      <c r="AF51" s="33"/>
-    </row>
-    <row r="52" spans="1:32" ht="17.25" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A52" s="65"/>
+    </row>
+    <row r="52" spans="1:26" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A52" s="58"/>
       <c r="B52" s="17"/>
       <c r="C52" s="22" t="s">
         <v>33</v>
@@ -4793,13 +4705,13 @@
         <v>36</v>
       </c>
       <c r="J52" s="28"/>
-      <c r="K52" s="29"/>
-      <c r="L52" s="29"/>
-      <c r="M52" s="29"/>
-      <c r="N52" s="29"/>
-      <c r="O52" s="29"/>
-      <c r="P52" s="29"/>
-      <c r="R52" s="65"/>
+      <c r="K52" s="21"/>
+      <c r="L52" s="21"/>
+      <c r="M52" s="21"/>
+      <c r="N52" s="21"/>
+      <c r="O52" s="21"/>
+      <c r="P52" s="21"/>
+      <c r="R52" s="58"/>
       <c r="S52" s="25" t="s">
         <v>39</v>
       </c>
@@ -4810,16 +4722,9 @@
       <c r="V52" s="26"/>
       <c r="W52" s="26"/>
       <c r="X52" s="27"/>
-      <c r="Z52" s="33"/>
-      <c r="AA52" s="33"/>
-      <c r="AB52" s="33"/>
-      <c r="AC52" s="33"/>
-      <c r="AD52" s="33"/>
-      <c r="AE52" s="33"/>
-      <c r="AF52" s="33"/>
-    </row>
-    <row r="53" spans="1:32" ht="17.25" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A53" s="65"/>
+    </row>
+    <row r="53" spans="1:26" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A53" s="58"/>
       <c r="B53" s="17"/>
       <c r="C53" s="22" t="s">
         <v>36</v>
@@ -4836,29 +4741,22 @@
         <v>39</v>
       </c>
       <c r="J53" s="28"/>
-      <c r="K53" s="29"/>
-      <c r="L53" s="29"/>
-      <c r="M53" s="29"/>
-      <c r="N53" s="29"/>
-      <c r="O53" s="29"/>
-      <c r="P53" s="29"/>
+      <c r="K53" s="21"/>
+      <c r="L53" s="21"/>
+      <c r="M53" s="21"/>
+      <c r="N53" s="21"/>
+      <c r="O53" s="21"/>
+      <c r="P53" s="21"/>
       <c r="R53" s="28"/>
-      <c r="S53" s="29"/>
-      <c r="T53" s="29"/>
-      <c r="U53" s="29"/>
-      <c r="V53" s="29"/>
-      <c r="W53" s="29"/>
-      <c r="X53" s="29"/>
-      <c r="Z53" s="33"/>
-      <c r="AA53" s="33"/>
-      <c r="AB53" s="33"/>
-      <c r="AC53" s="33"/>
-      <c r="AD53" s="33"/>
-      <c r="AE53" s="33"/>
-      <c r="AF53" s="33"/>
-    </row>
-    <row r="54" spans="1:32" ht="17.25" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A54" s="65"/>
+      <c r="S53" s="21"/>
+      <c r="T53" s="21"/>
+      <c r="U53" s="21"/>
+      <c r="V53" s="21"/>
+      <c r="W53" s="21"/>
+      <c r="X53" s="21"/>
+    </row>
+    <row r="54" spans="1:26" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A54" s="58"/>
       <c r="B54" s="17"/>
       <c r="C54" s="22" t="s">
         <v>39</v>
@@ -4873,29 +4771,22 @@
         <v>41</v>
       </c>
       <c r="J54" s="28"/>
-      <c r="K54" s="29"/>
-      <c r="L54" s="29"/>
-      <c r="M54" s="29"/>
-      <c r="N54" s="29"/>
-      <c r="O54" s="29"/>
-      <c r="P54" s="29"/>
+      <c r="K54" s="21"/>
+      <c r="L54" s="21"/>
+      <c r="M54" s="21"/>
+      <c r="N54" s="21"/>
+      <c r="O54" s="21"/>
+      <c r="P54" s="21"/>
       <c r="R54" s="28"/>
-      <c r="S54" s="29"/>
-      <c r="T54" s="29"/>
-      <c r="U54" s="29"/>
-      <c r="V54" s="29"/>
-      <c r="W54" s="29"/>
-      <c r="X54" s="29"/>
-      <c r="Z54" s="33"/>
-      <c r="AA54" s="33"/>
-      <c r="AB54" s="33"/>
-      <c r="AC54" s="33"/>
-      <c r="AD54" s="33"/>
-      <c r="AE54" s="33"/>
-      <c r="AF54" s="33"/>
-    </row>
-    <row r="55" spans="1:32" ht="17.25" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A55" s="65"/>
+      <c r="S54" s="21"/>
+      <c r="T54" s="21"/>
+      <c r="U54" s="21"/>
+      <c r="V54" s="21"/>
+      <c r="W54" s="21"/>
+      <c r="X54" s="21"/>
+    </row>
+    <row r="55" spans="1:26" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A55" s="58"/>
       <c r="B55" s="17"/>
       <c r="C55" s="25" t="s">
         <v>42</v>
@@ -4906,55 +4797,41 @@
       <c r="G55" s="26"/>
       <c r="H55" s="27"/>
       <c r="J55" s="28"/>
-      <c r="K55" s="29"/>
-      <c r="L55" s="29"/>
-      <c r="M55" s="29"/>
-      <c r="N55" s="29"/>
-      <c r="O55" s="29"/>
-      <c r="P55" s="29"/>
+      <c r="K55" s="21"/>
+      <c r="L55" s="21"/>
+      <c r="M55" s="21"/>
+      <c r="N55" s="21"/>
+      <c r="O55" s="21"/>
+      <c r="P55" s="21"/>
       <c r="R55" s="28"/>
-      <c r="S55" s="29"/>
-      <c r="T55" s="29"/>
-      <c r="U55" s="29"/>
-      <c r="V55" s="29"/>
-      <c r="W55" s="29"/>
-      <c r="X55" s="29"/>
-      <c r="Z55" s="33"/>
-      <c r="AA55" s="33"/>
-      <c r="AB55" s="33"/>
-      <c r="AC55" s="33"/>
-      <c r="AD55" s="33"/>
-      <c r="AE55" s="33"/>
-      <c r="AF55" s="33"/>
-    </row>
-    <row r="56" spans="1:32" ht="17.25" hidden="1" x14ac:dyDescent="0.35">
-      <c r="C56" s="29"/>
-      <c r="D56" s="29"/>
-      <c r="E56" s="29"/>
-      <c r="F56" s="29"/>
-      <c r="G56" s="29"/>
-      <c r="H56" s="29"/>
-      <c r="K56" s="29"/>
-      <c r="L56" s="29"/>
-      <c r="M56" s="29"/>
-      <c r="N56" s="29"/>
-      <c r="O56" s="29"/>
-      <c r="P56" s="29"/>
-      <c r="S56" s="29"/>
-      <c r="T56" s="29"/>
-      <c r="U56" s="29"/>
-      <c r="V56" s="29"/>
-      <c r="W56" s="29"/>
-      <c r="X56" s="29"/>
-      <c r="Z56" s="33"/>
-      <c r="AA56" s="33"/>
-      <c r="AB56" s="33"/>
-      <c r="AC56" s="33"/>
-      <c r="AD56" s="33"/>
-      <c r="AE56" s="33"/>
-      <c r="AF56" s="33"/>
-    </row>
-    <row r="57" spans="1:32" s="16" customFormat="1" ht="17.25" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="S55" s="21"/>
+      <c r="T55" s="21"/>
+      <c r="U55" s="21"/>
+      <c r="V55" s="21"/>
+      <c r="W55" s="21"/>
+      <c r="X55" s="21"/>
+    </row>
+    <row r="56" spans="1:26" hidden="1" x14ac:dyDescent="0.3">
+      <c r="C56" s="21"/>
+      <c r="D56" s="21"/>
+      <c r="E56" s="21"/>
+      <c r="F56" s="21"/>
+      <c r="G56" s="21"/>
+      <c r="H56" s="21"/>
+      <c r="K56" s="21"/>
+      <c r="L56" s="21"/>
+      <c r="M56" s="21"/>
+      <c r="N56" s="21"/>
+      <c r="O56" s="21"/>
+      <c r="P56" s="21"/>
+      <c r="S56" s="21"/>
+      <c r="T56" s="21"/>
+      <c r="U56" s="21"/>
+      <c r="V56" s="21"/>
+      <c r="W56" s="21"/>
+      <c r="X56" s="21"/>
+    </row>
+    <row r="57" spans="1:26" s="16" customFormat="1" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A57" s="16" t="s">
         <v>43</v>
       </c>
@@ -5018,16 +4895,9 @@
       <c r="X57" s="15" t="s">
         <v>12</v>
       </c>
-      <c r="Z57" s="34"/>
-      <c r="AA57" s="34"/>
-      <c r="AB57" s="34"/>
-      <c r="AC57" s="34"/>
-      <c r="AD57" s="34"/>
-      <c r="AE57" s="34"/>
-      <c r="AF57" s="34"/>
-    </row>
-    <row r="58" spans="1:32" ht="15" hidden="1" customHeight="1" thickTop="1" x14ac:dyDescent="0.35">
-      <c r="A58" s="65" t="s">
+    </row>
+    <row r="58" spans="1:26" ht="15" hidden="1" customHeight="1" thickTop="1" x14ac:dyDescent="0.3">
+      <c r="A58" s="58" t="s">
         <v>16</v>
       </c>
       <c r="B58" s="17"/>
@@ -5049,7 +4919,7 @@
       <c r="H58" s="20" t="s">
         <v>17</v>
       </c>
-      <c r="J58" s="65" t="s">
+      <c r="J58" s="58" t="s">
         <v>16</v>
       </c>
       <c r="K58" s="18" t="s">
@@ -5070,7 +4940,7 @@
       <c r="P58" s="20" t="s">
         <v>20</v>
       </c>
-      <c r="R58" s="65" t="s">
+      <c r="R58" s="58" t="s">
         <v>16</v>
       </c>
       <c r="S58" s="18" t="s">
@@ -5091,16 +4961,10 @@
       <c r="X58" s="20" t="s">
         <v>20</v>
       </c>
-      <c r="Z58" s="36"/>
-      <c r="AA58" s="33"/>
-      <c r="AB58" s="33"/>
-      <c r="AC58" s="33"/>
-      <c r="AD58" s="33"/>
-      <c r="AE58" s="33"/>
-      <c r="AF58" s="33"/>
-    </row>
-    <row r="59" spans="1:32" ht="17.25" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A59" s="65"/>
+      <c r="Z58" s="28"/>
+    </row>
+    <row r="59" spans="1:26" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A59" s="58"/>
       <c r="B59" s="17"/>
       <c r="C59" s="22" t="s">
         <v>23</v>
@@ -5120,7 +4984,7 @@
       <c r="H59" s="24" t="s">
         <v>20</v>
       </c>
-      <c r="J59" s="65"/>
+      <c r="J59" s="58"/>
       <c r="K59" s="22" t="s">
         <v>23</v>
       </c>
@@ -5139,7 +5003,7 @@
       <c r="P59" s="24" t="s">
         <v>24</v>
       </c>
-      <c r="R59" s="65"/>
+      <c r="R59" s="58"/>
       <c r="S59" s="22" t="s">
         <v>25</v>
       </c>
@@ -5158,16 +5022,10 @@
       <c r="X59" s="24" t="s">
         <v>24</v>
       </c>
-      <c r="Z59" s="36"/>
-      <c r="AA59" s="33"/>
-      <c r="AB59" s="33"/>
-      <c r="AC59" s="33"/>
-      <c r="AD59" s="33"/>
-      <c r="AE59" s="33"/>
-      <c r="AF59" s="33"/>
-    </row>
-    <row r="60" spans="1:32" ht="17.25" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A60" s="65"/>
+      <c r="Z59" s="28"/>
+    </row>
+    <row r="60" spans="1:26" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A60" s="58"/>
       <c r="B60" s="17"/>
       <c r="C60" s="22" t="s">
         <v>24</v>
@@ -5187,7 +5045,7 @@
       <c r="H60" s="24" t="s">
         <v>21</v>
       </c>
-      <c r="J60" s="65"/>
+      <c r="J60" s="58"/>
       <c r="K60" s="22" t="s">
         <v>25</v>
       </c>
@@ -5206,7 +5064,7 @@
       <c r="P60" s="24" t="s">
         <v>25</v>
       </c>
-      <c r="R60" s="65"/>
+      <c r="R60" s="58"/>
       <c r="S60" s="22" t="s">
         <v>26</v>
       </c>
@@ -5225,16 +5083,10 @@
       <c r="X60" s="24" t="s">
         <v>25</v>
       </c>
-      <c r="Z60" s="36"/>
-      <c r="AA60" s="33"/>
-      <c r="AB60" s="33"/>
-      <c r="AC60" s="33"/>
-      <c r="AD60" s="33"/>
-      <c r="AE60" s="33"/>
-      <c r="AF60" s="33"/>
-    </row>
-    <row r="61" spans="1:32" ht="17.25" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A61" s="65"/>
+      <c r="Z60" s="28"/>
+    </row>
+    <row r="61" spans="1:26" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A61" s="58"/>
       <c r="B61" s="17"/>
       <c r="C61" s="22" t="s">
         <v>25</v>
@@ -5254,7 +5106,7 @@
       <c r="H61" s="24" t="s">
         <v>24</v>
       </c>
-      <c r="J61" s="65"/>
+      <c r="J61" s="58"/>
       <c r="K61" s="22" t="s">
         <v>26</v>
       </c>
@@ -5273,7 +5125,7 @@
       <c r="P61" s="24" t="s">
         <v>26</v>
       </c>
-      <c r="R61" s="65"/>
+      <c r="R61" s="58"/>
       <c r="S61" s="22" t="s">
         <v>32</v>
       </c>
@@ -5292,16 +5144,10 @@
       <c r="X61" s="24" t="s">
         <v>26</v>
       </c>
-      <c r="Z61" s="36"/>
-      <c r="AA61" s="33"/>
-      <c r="AB61" s="33"/>
-      <c r="AC61" s="33"/>
-      <c r="AD61" s="33"/>
-      <c r="AE61" s="33"/>
-      <c r="AF61" s="33"/>
-    </row>
-    <row r="62" spans="1:32" ht="17.25" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A62" s="65"/>
+      <c r="Z61" s="28"/>
+    </row>
+    <row r="62" spans="1:26" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A62" s="58"/>
       <c r="B62" s="17"/>
       <c r="C62" s="22" t="s">
         <v>26</v>
@@ -5321,7 +5167,7 @@
       <c r="H62" s="24" t="s">
         <v>25</v>
       </c>
-      <c r="J62" s="65"/>
+      <c r="J62" s="58"/>
       <c r="K62" s="22" t="s">
         <v>32</v>
       </c>
@@ -5340,7 +5186,7 @@
       <c r="P62" s="24" t="s">
         <v>32</v>
       </c>
-      <c r="R62" s="65"/>
+      <c r="R62" s="58"/>
       <c r="S62" s="22" t="s">
         <v>38</v>
       </c>
@@ -5359,16 +5205,10 @@
       <c r="X62" s="24" t="s">
         <v>28</v>
       </c>
-      <c r="Z62" s="36"/>
-      <c r="AA62" s="33"/>
-      <c r="AB62" s="33"/>
-      <c r="AC62" s="33"/>
-      <c r="AD62" s="33"/>
-      <c r="AE62" s="33"/>
-      <c r="AF62" s="33"/>
-    </row>
-    <row r="63" spans="1:32" ht="17.25" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A63" s="65"/>
+      <c r="Z62" s="28"/>
+    </row>
+    <row r="63" spans="1:26" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A63" s="58"/>
       <c r="B63" s="17"/>
       <c r="C63" s="22" t="s">
         <v>32</v>
@@ -5388,7 +5228,7 @@
       <c r="H63" s="24" t="s">
         <v>26</v>
       </c>
-      <c r="J63" s="65"/>
+      <c r="J63" s="58"/>
       <c r="K63" s="22" t="s">
         <v>38</v>
       </c>
@@ -5407,7 +5247,7 @@
       <c r="P63" s="24" t="s">
         <v>37</v>
       </c>
-      <c r="R63" s="65"/>
+      <c r="R63" s="58"/>
       <c r="S63" s="22" t="s">
         <v>33</v>
       </c>
@@ -5426,16 +5266,10 @@
       <c r="X63" s="24" t="s">
         <v>32</v>
       </c>
-      <c r="Z63" s="36"/>
-      <c r="AA63" s="33"/>
-      <c r="AB63" s="33"/>
-      <c r="AC63" s="33"/>
-      <c r="AD63" s="33"/>
-      <c r="AE63" s="33"/>
-      <c r="AF63" s="33"/>
-    </row>
-    <row r="64" spans="1:32" ht="17.25" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A64" s="65"/>
+      <c r="Z63" s="28"/>
+    </row>
+    <row r="64" spans="1:26" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A64" s="58"/>
       <c r="B64" s="17"/>
       <c r="C64" s="22" t="s">
         <v>30</v>
@@ -5455,7 +5289,7 @@
       <c r="H64" s="24" t="s">
         <v>32</v>
       </c>
-      <c r="J64" s="65"/>
+      <c r="J64" s="58"/>
       <c r="K64" s="22" t="s">
         <v>33</v>
       </c>
@@ -5474,7 +5308,7 @@
       <c r="P64" s="24" t="s">
         <v>36</v>
       </c>
-      <c r="R64" s="65"/>
+      <c r="R64" s="58"/>
       <c r="S64" s="22" t="s">
         <v>36</v>
       </c>
@@ -5491,16 +5325,10 @@
       <c r="X64" s="24" t="s">
         <v>30</v>
       </c>
-      <c r="Z64" s="36"/>
-      <c r="AA64" s="33"/>
-      <c r="AB64" s="33"/>
-      <c r="AC64" s="33"/>
-      <c r="AD64" s="33"/>
-      <c r="AE64" s="33"/>
-      <c r="AF64" s="33"/>
-    </row>
-    <row r="65" spans="1:33" ht="17.25" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A65" s="65"/>
+      <c r="Z64" s="28"/>
+    </row>
+    <row r="65" spans="1:26" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A65" s="58"/>
       <c r="B65" s="17"/>
       <c r="C65" s="22" t="s">
         <v>38</v>
@@ -5520,7 +5348,7 @@
       <c r="H65" s="24" t="s">
         <v>30</v>
       </c>
-      <c r="J65" s="65"/>
+      <c r="J65" s="58"/>
       <c r="K65" s="22" t="s">
         <v>36</v>
       </c>
@@ -5533,7 +5361,7 @@
       <c r="N65" s="23"/>
       <c r="O65" s="23"/>
       <c r="P65" s="24"/>
-      <c r="R65" s="65"/>
+      <c r="R65" s="58"/>
       <c r="S65" s="22"/>
       <c r="T65" s="23" t="s">
         <v>36</v>
@@ -5546,17 +5374,10 @@
       <c r="X65" s="24" t="s">
         <v>38</v>
       </c>
-      <c r="Z65" s="36"/>
-      <c r="AA65" s="33"/>
-      <c r="AB65" s="33"/>
-      <c r="AC65" s="33"/>
-      <c r="AD65" s="33"/>
-      <c r="AE65" s="33"/>
-      <c r="AF65" s="33"/>
-      <c r="AG65" s="33"/>
-    </row>
-    <row r="66" spans="1:33" ht="17.25" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A66" s="65"/>
+      <c r="Z65" s="28"/>
+    </row>
+    <row r="66" spans="1:26" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A66" s="58"/>
       <c r="B66" s="17"/>
       <c r="C66" s="22" t="s">
         <v>33</v>
@@ -5576,7 +5397,7 @@
       <c r="H66" s="24" t="s">
         <v>29</v>
       </c>
-      <c r="J66" s="65"/>
+      <c r="J66" s="58"/>
       <c r="K66" s="22"/>
       <c r="L66" s="23"/>
       <c r="M66" s="23" t="s">
@@ -5585,7 +5406,7 @@
       <c r="N66" s="23"/>
       <c r="O66" s="23"/>
       <c r="P66" s="24"/>
-      <c r="R66" s="65"/>
+      <c r="R66" s="58"/>
       <c r="S66" s="22"/>
       <c r="T66" s="23" t="s">
         <v>39</v>
@@ -5598,17 +5419,10 @@
       <c r="X66" s="24" t="s">
         <v>37</v>
       </c>
-      <c r="Z66" s="36"/>
-      <c r="AA66" s="33"/>
-      <c r="AB66" s="33"/>
-      <c r="AC66" s="33"/>
-      <c r="AD66" s="33"/>
-      <c r="AE66" s="33"/>
-      <c r="AF66" s="33"/>
-      <c r="AG66" s="33"/>
-    </row>
-    <row r="67" spans="1:33" ht="17.25" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A67" s="65"/>
+      <c r="Z66" s="28"/>
+    </row>
+    <row r="67" spans="1:26" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A67" s="58"/>
       <c r="B67" s="17"/>
       <c r="C67" s="22" t="s">
         <v>36</v>
@@ -5628,7 +5442,7 @@
       <c r="H67" s="24" t="s">
         <v>33</v>
       </c>
-      <c r="J67" s="65"/>
+      <c r="J67" s="58"/>
       <c r="K67" s="25"/>
       <c r="L67" s="26"/>
       <c r="M67" s="26" t="s">
@@ -5637,7 +5451,7 @@
       <c r="N67" s="26"/>
       <c r="O67" s="26"/>
       <c r="P67" s="27"/>
-      <c r="R67" s="65"/>
+      <c r="R67" s="58"/>
       <c r="S67" s="25"/>
       <c r="T67" s="26"/>
       <c r="U67" s="26" t="s">
@@ -5648,17 +5462,10 @@
       <c r="X67" s="27" t="s">
         <v>36</v>
       </c>
-      <c r="Z67" s="36"/>
-      <c r="AA67" s="33"/>
-      <c r="AB67" s="33"/>
-      <c r="AC67" s="33"/>
-      <c r="AD67" s="33"/>
-      <c r="AE67" s="33"/>
-      <c r="AF67" s="33"/>
-      <c r="AG67" s="33"/>
-    </row>
-    <row r="68" spans="1:33" ht="17.25" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A68" s="65"/>
+      <c r="Z67" s="28"/>
+    </row>
+    <row r="68" spans="1:26" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A68" s="58"/>
       <c r="B68" s="17"/>
       <c r="C68" s="22" t="s">
         <v>39</v>
@@ -5679,30 +5486,23 @@
         <v>36</v>
       </c>
       <c r="J68" s="28"/>
-      <c r="K68" s="29"/>
-      <c r="L68" s="29"/>
-      <c r="M68" s="29"/>
-      <c r="N68" s="29"/>
-      <c r="O68" s="29"/>
-      <c r="P68" s="29"/>
+      <c r="K68" s="21"/>
+      <c r="L68" s="21"/>
+      <c r="M68" s="21"/>
+      <c r="N68" s="21"/>
+      <c r="O68" s="21"/>
+      <c r="P68" s="21"/>
       <c r="R68" s="28"/>
-      <c r="S68" s="29"/>
-      <c r="T68" s="29"/>
-      <c r="U68" s="29"/>
-      <c r="V68" s="29"/>
-      <c r="W68" s="29"/>
-      <c r="X68" s="29"/>
-      <c r="Z68" s="37"/>
-      <c r="AA68" s="38"/>
-      <c r="AB68" s="38"/>
-      <c r="AC68" s="38"/>
-      <c r="AD68" s="38"/>
-      <c r="AE68" s="38"/>
-      <c r="AF68" s="38"/>
-      <c r="AG68" s="33"/>
-    </row>
-    <row r="69" spans="1:33" ht="17.25" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A69" s="65"/>
+      <c r="S68" s="21"/>
+      <c r="T68" s="21"/>
+      <c r="U68" s="21"/>
+      <c r="V68" s="21"/>
+      <c r="W68" s="21"/>
+      <c r="X68" s="21"/>
+      <c r="Z68" s="28"/>
+    </row>
+    <row r="69" spans="1:26" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A69" s="58"/>
       <c r="B69" s="17"/>
       <c r="C69" s="22"/>
       <c r="D69" s="23"/>
@@ -5719,30 +5519,22 @@
         <v>39</v>
       </c>
       <c r="J69" s="28"/>
-      <c r="K69" s="29"/>
-      <c r="L69" s="29"/>
-      <c r="M69" s="29"/>
-      <c r="N69" s="29"/>
-      <c r="O69" s="29"/>
-      <c r="P69" s="29"/>
+      <c r="K69" s="21"/>
+      <c r="L69" s="21"/>
+      <c r="M69" s="21"/>
+      <c r="N69" s="21"/>
+      <c r="O69" s="21"/>
+      <c r="P69" s="21"/>
       <c r="R69" s="28"/>
-      <c r="S69" s="29"/>
-      <c r="T69" s="29"/>
-      <c r="U69" s="29"/>
-      <c r="V69" s="29"/>
-      <c r="W69" s="29"/>
-      <c r="X69" s="29"/>
-      <c r="Z69" s="38"/>
-      <c r="AA69" s="38"/>
-      <c r="AB69" s="38"/>
-      <c r="AC69" s="38"/>
-      <c r="AD69" s="38"/>
-      <c r="AE69" s="38"/>
-      <c r="AF69" s="38"/>
-      <c r="AG69" s="33"/>
-    </row>
-    <row r="70" spans="1:33" ht="17.25" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A70" s="65"/>
+      <c r="S69" s="21"/>
+      <c r="T69" s="21"/>
+      <c r="U69" s="21"/>
+      <c r="V69" s="21"/>
+      <c r="W69" s="21"/>
+      <c r="X69" s="21"/>
+    </row>
+    <row r="70" spans="1:26" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A70" s="58"/>
       <c r="B70" s="17"/>
       <c r="C70" s="22"/>
       <c r="D70" s="23"/>
@@ -5755,30 +5547,22 @@
         <v>42</v>
       </c>
       <c r="J70" s="28"/>
-      <c r="K70" s="29"/>
-      <c r="L70" s="29"/>
-      <c r="M70" s="29"/>
-      <c r="N70" s="29"/>
-      <c r="O70" s="29"/>
-      <c r="P70" s="29"/>
+      <c r="K70" s="21"/>
+      <c r="L70" s="21"/>
+      <c r="M70" s="21"/>
+      <c r="N70" s="21"/>
+      <c r="O70" s="21"/>
+      <c r="P70" s="21"/>
       <c r="R70" s="28"/>
-      <c r="S70" s="29"/>
-      <c r="T70" s="29"/>
-      <c r="U70" s="29"/>
-      <c r="V70" s="29"/>
-      <c r="W70" s="29"/>
-      <c r="X70" s="29"/>
-      <c r="Z70" s="33"/>
-      <c r="AA70" s="33"/>
-      <c r="AB70" s="33"/>
-      <c r="AC70" s="33"/>
-      <c r="AD70" s="33"/>
-      <c r="AE70" s="33"/>
-      <c r="AF70" s="33"/>
-      <c r="AG70" s="33"/>
-    </row>
-    <row r="71" spans="1:33" ht="17.25" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A71" s="65"/>
+      <c r="S70" s="21"/>
+      <c r="T70" s="21"/>
+      <c r="U70" s="21"/>
+      <c r="V70" s="21"/>
+      <c r="W70" s="21"/>
+      <c r="X70" s="21"/>
+    </row>
+    <row r="71" spans="1:26" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A71" s="58"/>
       <c r="B71" s="17"/>
       <c r="C71" s="25"/>
       <c r="D71" s="26"/>
@@ -5789,86 +5573,86 @@
       <c r="G71" s="26"/>
       <c r="H71" s="27"/>
       <c r="J71" s="28"/>
-      <c r="K71" s="29"/>
-      <c r="L71" s="29"/>
-      <c r="M71" s="29"/>
-      <c r="N71" s="29"/>
-      <c r="O71" s="29"/>
-      <c r="P71" s="29"/>
+      <c r="K71" s="21"/>
+      <c r="L71" s="21"/>
+      <c r="M71" s="21"/>
+      <c r="N71" s="21"/>
+      <c r="O71" s="21"/>
+      <c r="P71" s="21"/>
       <c r="R71" s="28"/>
-      <c r="S71" s="29"/>
-      <c r="T71" s="29"/>
-      <c r="U71" s="29"/>
-      <c r="V71" s="29"/>
-      <c r="W71" s="29"/>
-      <c r="X71" s="29"/>
-    </row>
-    <row r="72" spans="1:33" ht="17.25" x14ac:dyDescent="0.35">
+      <c r="S71" s="21"/>
+      <c r="T71" s="21"/>
+      <c r="U71" s="21"/>
+      <c r="V71" s="21"/>
+      <c r="W71" s="21"/>
+      <c r="X71" s="21"/>
+    </row>
+    <row r="72" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A72" s="17"/>
       <c r="B72" s="17"/>
-      <c r="C72" s="39"/>
-      <c r="D72" s="39"/>
-      <c r="E72" s="39"/>
-      <c r="F72" s="39"/>
-      <c r="G72" s="39"/>
-      <c r="H72" s="39"/>
+      <c r="C72" s="21"/>
+      <c r="D72" s="21"/>
+      <c r="E72" s="21"/>
+      <c r="F72" s="21"/>
+      <c r="G72" s="21"/>
+      <c r="H72" s="21"/>
       <c r="J72" s="28"/>
-      <c r="K72" s="29"/>
-      <c r="L72" s="29"/>
-      <c r="M72" s="29"/>
-      <c r="N72" s="29"/>
-      <c r="O72" s="29"/>
-      <c r="P72" s="29"/>
+      <c r="K72" s="21"/>
+      <c r="L72" s="21"/>
+      <c r="M72" s="21"/>
+      <c r="N72" s="21"/>
+      <c r="O72" s="21"/>
+      <c r="P72" s="21"/>
       <c r="R72" s="28"/>
-      <c r="S72" s="29"/>
-      <c r="T72" s="29"/>
-      <c r="U72" s="29"/>
-      <c r="V72" s="29"/>
-      <c r="W72" s="29"/>
-      <c r="X72" s="29"/>
-    </row>
-    <row r="73" spans="1:33" ht="19.5" x14ac:dyDescent="0.35">
-      <c r="B73" s="41"/>
-      <c r="C73" s="39" t="s">
+      <c r="S72" s="21"/>
+      <c r="T72" s="21"/>
+      <c r="U72" s="21"/>
+      <c r="V72" s="21"/>
+      <c r="W72" s="21"/>
+      <c r="X72" s="21"/>
+    </row>
+    <row r="73" spans="1:26" ht="18" x14ac:dyDescent="0.35">
+      <c r="B73" s="34"/>
+      <c r="C73" s="21" t="s">
         <v>55</v>
       </c>
-      <c r="D73" s="29"/>
-      <c r="E73" s="29"/>
-      <c r="F73" s="29"/>
-      <c r="G73" s="29"/>
-      <c r="H73" s="29"/>
-      <c r="K73" s="29"/>
-      <c r="L73" s="29"/>
-      <c r="M73" s="29"/>
-      <c r="N73" s="29"/>
-      <c r="O73" s="29"/>
-      <c r="P73" s="29"/>
-      <c r="S73" s="29"/>
-      <c r="T73" s="29"/>
-      <c r="U73" s="29"/>
-      <c r="V73" s="29"/>
-      <c r="W73" s="29"/>
-      <c r="X73" s="29"/>
-    </row>
-    <row r="74" spans="1:33" ht="17.25" x14ac:dyDescent="0.35">
-      <c r="C74" s="39"/>
-      <c r="D74" s="29"/>
-      <c r="E74" s="29"/>
-      <c r="F74" s="29"/>
-      <c r="G74" s="29"/>
-      <c r="H74" s="29"/>
-      <c r="K74" s="29"/>
-      <c r="L74" s="29"/>
-      <c r="M74" s="29"/>
-      <c r="N74" s="29"/>
-      <c r="O74" s="29"/>
-      <c r="P74" s="29"/>
-      <c r="S74" s="29"/>
-      <c r="T74" s="29"/>
-      <c r="U74" s="29"/>
-      <c r="V74" s="29"/>
-      <c r="W74" s="29"/>
-      <c r="X74" s="29"/>
+      <c r="D73" s="21"/>
+      <c r="E73" s="21"/>
+      <c r="F73" s="21"/>
+      <c r="G73" s="21"/>
+      <c r="H73" s="21"/>
+      <c r="K73" s="21"/>
+      <c r="L73" s="21"/>
+      <c r="M73" s="21"/>
+      <c r="N73" s="21"/>
+      <c r="O73" s="21"/>
+      <c r="P73" s="21"/>
+      <c r="S73" s="21"/>
+      <c r="T73" s="21"/>
+      <c r="U73" s="21"/>
+      <c r="V73" s="21"/>
+      <c r="W73" s="21"/>
+      <c r="X73" s="21"/>
+    </row>
+    <row r="74" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="C74" s="21"/>
+      <c r="D74" s="21"/>
+      <c r="E74" s="21"/>
+      <c r="F74" s="21"/>
+      <c r="G74" s="21"/>
+      <c r="H74" s="21"/>
+      <c r="K74" s="21"/>
+      <c r="L74" s="21"/>
+      <c r="M74" s="21"/>
+      <c r="N74" s="21"/>
+      <c r="O74" s="21"/>
+      <c r="P74" s="21"/>
+      <c r="S74" s="21"/>
+      <c r="T74" s="21"/>
+      <c r="U74" s="21"/>
+      <c r="V74" s="21"/>
+      <c r="W74" s="21"/>
+      <c r="X74" s="21"/>
     </row>
   </sheetData>
   <mergeCells count="23">
@@ -5908,16 +5692,16 @@
     <pageSetUpPr autoPageBreaks="0" fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:H168"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.75" defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.77734375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="2" customWidth="1"/>
-    <col min="2" max="2" width="18.25" customWidth="1"/>
-    <col min="3" max="8" width="17.625" customWidth="1"/>
-    <col min="9" max="9" width="2.5" customWidth="1"/>
-    <col min="14" max="14" width="6.75" customWidth="1"/>
+    <col min="2" max="2" width="18.21875" customWidth="1"/>
+    <col min="3" max="8" width="17.6640625" customWidth="1"/>
+    <col min="9" max="9" width="2.44140625" customWidth="1"/>
+    <col min="14" max="14" width="6.77734375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="54" customHeight="1" x14ac:dyDescent="0.7">
+    <row r="1" spans="1:8" ht="54" customHeight="1" x14ac:dyDescent="0.9">
       <c r="A1" s="2"/>
       <c r="B1" s="1">
         <v>2019</v>
@@ -6162,24 +5946,24 @@
       <c r="C13" s="4">
         <v>43501</v>
       </c>
-      <c r="D13" s="73" t="s">
+      <c r="D13" s="66" t="s">
         <v>1</v>
       </c>
-      <c r="E13" s="74"/>
-      <c r="F13" s="74"/>
-      <c r="G13" s="74"/>
-      <c r="H13" s="74"/>
+      <c r="E13" s="67"/>
+      <c r="F13" s="67"/>
+      <c r="G13" s="67"/>
+      <c r="H13" s="67"/>
     </row>
     <row r="14" spans="1:8" ht="63.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B14" s="10"/>
       <c r="C14" s="10"/>
-      <c r="D14" s="72"/>
-      <c r="E14" s="71"/>
-      <c r="F14" s="71"/>
-      <c r="G14" s="71"/>
-      <c r="H14" s="71"/>
-    </row>
-    <row r="15" spans="1:8" ht="54" customHeight="1" x14ac:dyDescent="0.7">
+      <c r="D14" s="65"/>
+      <c r="E14" s="64"/>
+      <c r="F14" s="64"/>
+      <c r="G14" s="64"/>
+      <c r="H14" s="64"/>
+    </row>
+    <row r="15" spans="1:8" ht="54" customHeight="1" x14ac:dyDescent="0.9">
       <c r="A15" s="2"/>
       <c r="B15" s="1">
         <f>YEAR(DATE(Calendario1Año,Calendario1MesOpción+1,1))</f>
@@ -6425,24 +6209,24 @@
       <c r="C27" s="4">
         <v>43529</v>
       </c>
-      <c r="D27" s="75" t="s">
+      <c r="D27" s="63" t="s">
         <v>1</v>
       </c>
-      <c r="E27" s="75"/>
-      <c r="F27" s="75"/>
-      <c r="G27" s="75"/>
-      <c r="H27" s="75"/>
+      <c r="E27" s="63"/>
+      <c r="F27" s="63"/>
+      <c r="G27" s="63"/>
+      <c r="H27" s="63"/>
     </row>
     <row r="28" spans="1:8" ht="63.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B28" s="10"/>
       <c r="C28" s="10"/>
-      <c r="D28" s="71"/>
-      <c r="E28" s="71"/>
-      <c r="F28" s="71"/>
-      <c r="G28" s="71"/>
-      <c r="H28" s="71"/>
-    </row>
-    <row r="29" spans="1:8" ht="54" customHeight="1" x14ac:dyDescent="0.7">
+      <c r="D28" s="64"/>
+      <c r="E28" s="64"/>
+      <c r="F28" s="64"/>
+      <c r="G28" s="64"/>
+      <c r="H28" s="64"/>
+    </row>
+    <row r="29" spans="1:8" ht="54" customHeight="1" x14ac:dyDescent="0.9">
       <c r="A29" s="2"/>
       <c r="B29" s="1">
         <f>YEAR(DATE(Calendario2Año,Calendario2MesOpción+1,1))</f>
@@ -6686,24 +6470,24 @@
       <c r="C41" s="4">
         <v>43557</v>
       </c>
-      <c r="D41" s="75" t="s">
+      <c r="D41" s="63" t="s">
         <v>1</v>
       </c>
-      <c r="E41" s="75"/>
-      <c r="F41" s="75"/>
-      <c r="G41" s="75"/>
-      <c r="H41" s="75"/>
+      <c r="E41" s="63"/>
+      <c r="F41" s="63"/>
+      <c r="G41" s="63"/>
+      <c r="H41" s="63"/>
     </row>
     <row r="42" spans="1:8" ht="63.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B42" s="10"/>
       <c r="C42" s="10"/>
-      <c r="D42" s="71"/>
-      <c r="E42" s="71"/>
-      <c r="F42" s="71"/>
-      <c r="G42" s="71"/>
-      <c r="H42" s="71"/>
-    </row>
-    <row r="43" spans="1:8" ht="54" customHeight="1" x14ac:dyDescent="0.7">
+      <c r="D42" s="64"/>
+      <c r="E42" s="64"/>
+      <c r="F42" s="64"/>
+      <c r="G42" s="64"/>
+      <c r="H42" s="64"/>
+    </row>
+    <row r="43" spans="1:8" ht="54" customHeight="1" x14ac:dyDescent="0.9">
       <c r="A43" s="2"/>
       <c r="B43" s="1">
         <f>YEAR(DATE(Calendario3Año,Calendario3MesOpción+1,1))</f>
@@ -6949,24 +6733,24 @@
       <c r="C55" s="4">
         <v>43592</v>
       </c>
-      <c r="D55" s="69" t="s">
+      <c r="D55" s="62" t="s">
         <v>1</v>
       </c>
-      <c r="E55" s="70"/>
-      <c r="F55" s="70"/>
-      <c r="G55" s="70"/>
-      <c r="H55" s="70"/>
+      <c r="E55" s="63"/>
+      <c r="F55" s="63"/>
+      <c r="G55" s="63"/>
+      <c r="H55" s="63"/>
     </row>
     <row r="56" spans="1:8" ht="63.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B56" s="10"/>
       <c r="C56" s="10"/>
-      <c r="D56" s="71"/>
-      <c r="E56" s="71"/>
-      <c r="F56" s="71"/>
-      <c r="G56" s="71"/>
-      <c r="H56" s="71"/>
-    </row>
-    <row r="57" spans="1:8" ht="54" customHeight="1" x14ac:dyDescent="0.7">
+      <c r="D56" s="64"/>
+      <c r="E56" s="64"/>
+      <c r="F56" s="64"/>
+      <c r="G56" s="64"/>
+      <c r="H56" s="64"/>
+    </row>
+    <row r="57" spans="1:8" ht="54" customHeight="1" x14ac:dyDescent="0.9">
       <c r="A57" s="2"/>
       <c r="B57" s="1">
         <f>YEAR(DATE(Calendario4Año,Calendario4MesOpción+1,1))</f>
@@ -7186,24 +6970,24 @@
       <c r="C69" s="4">
         <v>43620</v>
       </c>
-      <c r="D69" s="69" t="s">
+      <c r="D69" s="62" t="s">
         <v>1</v>
       </c>
-      <c r="E69" s="70"/>
-      <c r="F69" s="70"/>
-      <c r="G69" s="70"/>
-      <c r="H69" s="70"/>
+      <c r="E69" s="63"/>
+      <c r="F69" s="63"/>
+      <c r="G69" s="63"/>
+      <c r="H69" s="63"/>
     </row>
     <row r="70" spans="1:8" ht="63.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B70" s="10"/>
       <c r="C70" s="10"/>
-      <c r="D70" s="71"/>
-      <c r="E70" s="71"/>
-      <c r="F70" s="71"/>
-      <c r="G70" s="71"/>
-      <c r="H70" s="71"/>
-    </row>
-    <row r="71" spans="1:8" ht="54" customHeight="1" x14ac:dyDescent="0.7">
+      <c r="D70" s="64"/>
+      <c r="E70" s="64"/>
+      <c r="F70" s="64"/>
+      <c r="G70" s="64"/>
+      <c r="H70" s="64"/>
+    </row>
+    <row r="71" spans="1:8" ht="54" customHeight="1" x14ac:dyDescent="0.9">
       <c r="A71" s="2"/>
       <c r="B71" s="1">
         <f>YEAR(DATE(Calendario5Año,Calendario5MesOpción+1,1))</f>
@@ -7423,24 +7207,24 @@
       <c r="C83" s="4">
         <v>43648</v>
       </c>
-      <c r="D83" s="69" t="s">
+      <c r="D83" s="62" t="s">
         <v>1</v>
       </c>
-      <c r="E83" s="70"/>
-      <c r="F83" s="70"/>
-      <c r="G83" s="70"/>
-      <c r="H83" s="70"/>
+      <c r="E83" s="63"/>
+      <c r="F83" s="63"/>
+      <c r="G83" s="63"/>
+      <c r="H83" s="63"/>
     </row>
     <row r="84" spans="1:8" ht="63.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B84" s="10"/>
       <c r="C84" s="10"/>
-      <c r="D84" s="71"/>
-      <c r="E84" s="71"/>
-      <c r="F84" s="71"/>
-      <c r="G84" s="71"/>
-      <c r="H84" s="71"/>
-    </row>
-    <row r="85" spans="1:8" ht="54" customHeight="1" x14ac:dyDescent="0.7">
+      <c r="D84" s="64"/>
+      <c r="E84" s="64"/>
+      <c r="F84" s="64"/>
+      <c r="G84" s="64"/>
+      <c r="H84" s="64"/>
+    </row>
+    <row r="85" spans="1:8" ht="54" customHeight="1" x14ac:dyDescent="0.9">
       <c r="A85" s="2"/>
       <c r="B85" s="1">
         <f>YEAR(DATE(Calendario6Año,Calendario6MesOpción+1,1))</f>
@@ -7660,24 +7444,24 @@
       <c r="C97" s="4">
         <v>43683</v>
       </c>
-      <c r="D97" s="69" t="s">
+      <c r="D97" s="62" t="s">
         <v>1</v>
       </c>
-      <c r="E97" s="70"/>
-      <c r="F97" s="70"/>
-      <c r="G97" s="70"/>
-      <c r="H97" s="70"/>
+      <c r="E97" s="63"/>
+      <c r="F97" s="63"/>
+      <c r="G97" s="63"/>
+      <c r="H97" s="63"/>
     </row>
     <row r="98" spans="1:8" ht="63.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B98" s="10"/>
       <c r="C98" s="10"/>
-      <c r="D98" s="71"/>
-      <c r="E98" s="71"/>
-      <c r="F98" s="71"/>
-      <c r="G98" s="71"/>
-      <c r="H98" s="71"/>
-    </row>
-    <row r="99" spans="1:8" ht="54" customHeight="1" x14ac:dyDescent="0.7">
+      <c r="D98" s="64"/>
+      <c r="E98" s="64"/>
+      <c r="F98" s="64"/>
+      <c r="G98" s="64"/>
+      <c r="H98" s="64"/>
+    </row>
+    <row r="99" spans="1:8" ht="54" customHeight="1" x14ac:dyDescent="0.9">
       <c r="A99" s="2"/>
       <c r="B99" s="1">
         <f>YEAR(DATE(Calendario7Año,Calendario7MesOpción+1,1))</f>
@@ -7897,24 +7681,24 @@
       <c r="C111" s="4">
         <v>43711</v>
       </c>
-      <c r="D111" s="69" t="s">
+      <c r="D111" s="62" t="s">
         <v>1</v>
       </c>
-      <c r="E111" s="70"/>
-      <c r="F111" s="70"/>
-      <c r="G111" s="70"/>
-      <c r="H111" s="70"/>
+      <c r="E111" s="63"/>
+      <c r="F111" s="63"/>
+      <c r="G111" s="63"/>
+      <c r="H111" s="63"/>
     </row>
     <row r="112" spans="1:8" ht="63.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B112" s="10"/>
       <c r="C112" s="10"/>
-      <c r="D112" s="71"/>
-      <c r="E112" s="71"/>
-      <c r="F112" s="71"/>
-      <c r="G112" s="71"/>
-      <c r="H112" s="71"/>
-    </row>
-    <row r="113" spans="1:8" ht="54" customHeight="1" x14ac:dyDescent="0.7">
+      <c r="D112" s="64"/>
+      <c r="E112" s="64"/>
+      <c r="F112" s="64"/>
+      <c r="G112" s="64"/>
+      <c r="H112" s="64"/>
+    </row>
+    <row r="113" spans="1:8" ht="54" customHeight="1" x14ac:dyDescent="0.9">
       <c r="A113" s="2"/>
       <c r="B113" s="1">
         <f>YEAR(DATE(Calendario8Año,Calendario8MesOpción+1,1))</f>
@@ -8134,24 +7918,24 @@
       <c r="C125" s="4">
         <v>43739</v>
       </c>
-      <c r="D125" s="69" t="s">
+      <c r="D125" s="62" t="s">
         <v>1</v>
       </c>
-      <c r="E125" s="70"/>
-      <c r="F125" s="70"/>
-      <c r="G125" s="70"/>
-      <c r="H125" s="70"/>
+      <c r="E125" s="63"/>
+      <c r="F125" s="63"/>
+      <c r="G125" s="63"/>
+      <c r="H125" s="63"/>
     </row>
     <row r="126" spans="1:8" ht="63.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B126" s="10"/>
       <c r="C126" s="10"/>
-      <c r="D126" s="71"/>
-      <c r="E126" s="71"/>
-      <c r="F126" s="71"/>
-      <c r="G126" s="71"/>
-      <c r="H126" s="71"/>
-    </row>
-    <row r="127" spans="1:8" ht="54" customHeight="1" x14ac:dyDescent="0.7">
+      <c r="D126" s="64"/>
+      <c r="E126" s="64"/>
+      <c r="F126" s="64"/>
+      <c r="G126" s="64"/>
+      <c r="H126" s="64"/>
+    </row>
+    <row r="127" spans="1:8" ht="54" customHeight="1" x14ac:dyDescent="0.9">
       <c r="A127" s="2"/>
       <c r="B127" s="1">
         <f>YEAR(DATE(Calendario9Año,Calendario9MesOpción+1,1))</f>
@@ -8371,24 +8155,24 @@
       <c r="C139" s="4">
         <v>43774</v>
       </c>
-      <c r="D139" s="69" t="s">
+      <c r="D139" s="62" t="s">
         <v>1</v>
       </c>
-      <c r="E139" s="70"/>
-      <c r="F139" s="70"/>
-      <c r="G139" s="70"/>
-      <c r="H139" s="70"/>
+      <c r="E139" s="63"/>
+      <c r="F139" s="63"/>
+      <c r="G139" s="63"/>
+      <c r="H139" s="63"/>
     </row>
     <row r="140" spans="2:8" ht="63.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B140" s="10"/>
       <c r="C140" s="10"/>
-      <c r="D140" s="71"/>
-      <c r="E140" s="71"/>
-      <c r="F140" s="71"/>
-      <c r="G140" s="71"/>
-      <c r="H140" s="71"/>
-    </row>
-    <row r="141" spans="2:8" ht="54" customHeight="1" x14ac:dyDescent="0.7">
+      <c r="D140" s="64"/>
+      <c r="E140" s="64"/>
+      <c r="F140" s="64"/>
+      <c r="G140" s="64"/>
+      <c r="H140" s="64"/>
+    </row>
+    <row r="141" spans="2:8" ht="54" customHeight="1" x14ac:dyDescent="0.9">
       <c r="B141" s="1">
         <f>YEAR(DATE(Calendario10Año,Calendario10MesOpción+1,1))</f>
         <v>2019</v>
@@ -8606,24 +8390,24 @@
       <c r="C153" s="4">
         <v>43802</v>
       </c>
-      <c r="D153" s="69" t="s">
+      <c r="D153" s="62" t="s">
         <v>1</v>
       </c>
-      <c r="E153" s="70"/>
-      <c r="F153" s="70"/>
-      <c r="G153" s="70"/>
-      <c r="H153" s="70"/>
+      <c r="E153" s="63"/>
+      <c r="F153" s="63"/>
+      <c r="G153" s="63"/>
+      <c r="H153" s="63"/>
     </row>
     <row r="154" spans="2:8" ht="63.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B154" s="10"/>
       <c r="C154" s="10"/>
-      <c r="D154" s="71"/>
-      <c r="E154" s="71"/>
-      <c r="F154" s="71"/>
-      <c r="G154" s="71"/>
-      <c r="H154" s="71"/>
-    </row>
-    <row r="155" spans="2:8" ht="54" customHeight="1" x14ac:dyDescent="0.7">
+      <c r="D154" s="64"/>
+      <c r="E154" s="64"/>
+      <c r="F154" s="64"/>
+      <c r="G154" s="64"/>
+      <c r="H154" s="64"/>
+    </row>
+    <row r="155" spans="2:8" ht="54" customHeight="1" x14ac:dyDescent="0.9">
       <c r="B155" s="1">
         <f>YEAR(DATE(Calendario11Año,Calendario11MesOpción+1,1))</f>
         <v>2019</v>
@@ -8841,22 +8625,22 @@
       <c r="C167" s="4">
         <v>43830</v>
       </c>
-      <c r="D167" s="69" t="s">
+      <c r="D167" s="62" t="s">
         <v>1</v>
       </c>
-      <c r="E167" s="70"/>
-      <c r="F167" s="70"/>
-      <c r="G167" s="70"/>
-      <c r="H167" s="70"/>
+      <c r="E167" s="63"/>
+      <c r="F167" s="63"/>
+      <c r="G167" s="63"/>
+      <c r="H167" s="63"/>
     </row>
     <row r="168" spans="2:8" ht="63.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B168" s="10"/>
       <c r="C168" s="10"/>
-      <c r="D168" s="71"/>
-      <c r="E168" s="71"/>
-      <c r="F168" s="71"/>
-      <c r="G168" s="71"/>
-      <c r="H168" s="71"/>
+      <c r="D168" s="64"/>
+      <c r="E168" s="64"/>
+      <c r="F168" s="64"/>
+      <c r="G168" s="64"/>
+      <c r="H168" s="64"/>
     </row>
   </sheetData>
   <mergeCells count="24">
@@ -8995,16 +8779,16 @@
     <pageSetUpPr autoPageBreaks="0" fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:H168"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.75" defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.77734375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="2" customWidth="1"/>
-    <col min="2" max="2" width="18.25" customWidth="1"/>
-    <col min="3" max="8" width="17.625" customWidth="1"/>
-    <col min="9" max="9" width="2.5" customWidth="1"/>
-    <col min="14" max="14" width="6.75" customWidth="1"/>
+    <col min="2" max="2" width="18.21875" customWidth="1"/>
+    <col min="3" max="8" width="17.6640625" customWidth="1"/>
+    <col min="9" max="9" width="2.44140625" customWidth="1"/>
+    <col min="14" max="14" width="6.77734375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="54" customHeight="1" x14ac:dyDescent="0.7">
+    <row r="1" spans="1:8" ht="54" customHeight="1" x14ac:dyDescent="0.9">
       <c r="A1" s="2"/>
       <c r="B1" s="1">
         <v>2020</v>
@@ -9249,24 +9033,24 @@
       <c r="C13" s="4">
         <v>43865</v>
       </c>
-      <c r="D13" s="73" t="s">
+      <c r="D13" s="66" t="s">
         <v>1</v>
       </c>
-      <c r="E13" s="74"/>
-      <c r="F13" s="74"/>
-      <c r="G13" s="74"/>
-      <c r="H13" s="74"/>
+      <c r="E13" s="67"/>
+      <c r="F13" s="67"/>
+      <c r="G13" s="67"/>
+      <c r="H13" s="67"/>
     </row>
     <row r="14" spans="1:8" ht="63.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B14" s="10"/>
       <c r="C14" s="10"/>
-      <c r="D14" s="72"/>
-      <c r="E14" s="71"/>
-      <c r="F14" s="71"/>
-      <c r="G14" s="71"/>
-      <c r="H14" s="71"/>
-    </row>
-    <row r="15" spans="1:8" ht="54" customHeight="1" x14ac:dyDescent="0.7">
+      <c r="D14" s="65"/>
+      <c r="E14" s="64"/>
+      <c r="F14" s="64"/>
+      <c r="G14" s="64"/>
+      <c r="H14" s="64"/>
+    </row>
+    <row r="15" spans="1:8" ht="54" customHeight="1" x14ac:dyDescent="0.9">
       <c r="A15" s="2"/>
       <c r="B15" s="1">
         <f>YEAR(DATE(Calendario1Año,Calendario1MesOpción+1,1))</f>
@@ -9512,24 +9296,24 @@
       <c r="C27" s="4">
         <v>43893</v>
       </c>
-      <c r="D27" s="75" t="s">
+      <c r="D27" s="63" t="s">
         <v>1</v>
       </c>
-      <c r="E27" s="75"/>
-      <c r="F27" s="75"/>
-      <c r="G27" s="75"/>
-      <c r="H27" s="75"/>
+      <c r="E27" s="63"/>
+      <c r="F27" s="63"/>
+      <c r="G27" s="63"/>
+      <c r="H27" s="63"/>
     </row>
     <row r="28" spans="1:8" ht="63.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B28" s="10"/>
       <c r="C28" s="10"/>
-      <c r="D28" s="71"/>
-      <c r="E28" s="71"/>
-      <c r="F28" s="71"/>
-      <c r="G28" s="71"/>
-      <c r="H28" s="71"/>
-    </row>
-    <row r="29" spans="1:8" ht="54" customHeight="1" x14ac:dyDescent="0.7">
+      <c r="D28" s="64"/>
+      <c r="E28" s="64"/>
+      <c r="F28" s="64"/>
+      <c r="G28" s="64"/>
+      <c r="H28" s="64"/>
+    </row>
+    <row r="29" spans="1:8" ht="54" customHeight="1" x14ac:dyDescent="0.9">
       <c r="A29" s="2"/>
       <c r="B29" s="1">
         <f>YEAR(DATE(Calendario2Año,Calendario2MesOpción+1,1))</f>
@@ -9773,24 +9557,24 @@
       <c r="C41" s="4">
         <v>43921</v>
       </c>
-      <c r="D41" s="75" t="s">
+      <c r="D41" s="63" t="s">
         <v>1</v>
       </c>
-      <c r="E41" s="75"/>
-      <c r="F41" s="75"/>
-      <c r="G41" s="75"/>
-      <c r="H41" s="75"/>
+      <c r="E41" s="63"/>
+      <c r="F41" s="63"/>
+      <c r="G41" s="63"/>
+      <c r="H41" s="63"/>
     </row>
     <row r="42" spans="1:8" ht="63.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B42" s="10"/>
       <c r="C42" s="10"/>
-      <c r="D42" s="71"/>
-      <c r="E42" s="71"/>
-      <c r="F42" s="71"/>
-      <c r="G42" s="71"/>
-      <c r="H42" s="71"/>
-    </row>
-    <row r="43" spans="1:8" ht="54" customHeight="1" x14ac:dyDescent="0.7">
+      <c r="D42" s="64"/>
+      <c r="E42" s="64"/>
+      <c r="F42" s="64"/>
+      <c r="G42" s="64"/>
+      <c r="H42" s="64"/>
+    </row>
+    <row r="43" spans="1:8" ht="54" customHeight="1" x14ac:dyDescent="0.9">
       <c r="A43" s="2"/>
       <c r="B43" s="1">
         <f>YEAR(DATE(Calendario3Año,Calendario3MesOpción+1,1))</f>
@@ -10036,24 +9820,24 @@
       <c r="C55" s="4">
         <v>43956</v>
       </c>
-      <c r="D55" s="69" t="s">
+      <c r="D55" s="62" t="s">
         <v>1</v>
       </c>
-      <c r="E55" s="70"/>
-      <c r="F55" s="70"/>
-      <c r="G55" s="70"/>
-      <c r="H55" s="70"/>
+      <c r="E55" s="63"/>
+      <c r="F55" s="63"/>
+      <c r="G55" s="63"/>
+      <c r="H55" s="63"/>
     </row>
     <row r="56" spans="1:8" ht="63.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B56" s="10"/>
       <c r="C56" s="10"/>
-      <c r="D56" s="71"/>
-      <c r="E56" s="71"/>
-      <c r="F56" s="71"/>
-      <c r="G56" s="71"/>
-      <c r="H56" s="71"/>
-    </row>
-    <row r="57" spans="1:8" ht="54" customHeight="1" x14ac:dyDescent="0.7">
+      <c r="D56" s="64"/>
+      <c r="E56" s="64"/>
+      <c r="F56" s="64"/>
+      <c r="G56" s="64"/>
+      <c r="H56" s="64"/>
+    </row>
+    <row r="57" spans="1:8" ht="54" customHeight="1" x14ac:dyDescent="0.9">
       <c r="A57" s="2"/>
       <c r="B57" s="1">
         <f>YEAR(DATE(Calendario4Año,Calendario4MesOpción+1,1))</f>
@@ -10273,24 +10057,24 @@
       <c r="C69" s="4">
         <v>43984</v>
       </c>
-      <c r="D69" s="69" t="s">
+      <c r="D69" s="62" t="s">
         <v>1</v>
       </c>
-      <c r="E69" s="70"/>
-      <c r="F69" s="70"/>
-      <c r="G69" s="70"/>
-      <c r="H69" s="70"/>
+      <c r="E69" s="63"/>
+      <c r="F69" s="63"/>
+      <c r="G69" s="63"/>
+      <c r="H69" s="63"/>
     </row>
     <row r="70" spans="1:8" ht="63.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B70" s="10"/>
       <c r="C70" s="10"/>
-      <c r="D70" s="71"/>
-      <c r="E70" s="71"/>
-      <c r="F70" s="71"/>
-      <c r="G70" s="71"/>
-      <c r="H70" s="71"/>
-    </row>
-    <row r="71" spans="1:8" ht="54" customHeight="1" x14ac:dyDescent="0.7">
+      <c r="D70" s="64"/>
+      <c r="E70" s="64"/>
+      <c r="F70" s="64"/>
+      <c r="G70" s="64"/>
+      <c r="H70" s="64"/>
+    </row>
+    <row r="71" spans="1:8" ht="54" customHeight="1" x14ac:dyDescent="0.9">
       <c r="A71" s="2"/>
       <c r="B71" s="1">
         <f>YEAR(DATE(Calendario5Año,Calendario5MesOpción+1,1))</f>
@@ -10510,24 +10294,24 @@
       <c r="C83" s="4">
         <v>44019</v>
       </c>
-      <c r="D83" s="69" t="s">
+      <c r="D83" s="62" t="s">
         <v>1</v>
       </c>
-      <c r="E83" s="70"/>
-      <c r="F83" s="70"/>
-      <c r="G83" s="70"/>
-      <c r="H83" s="70"/>
+      <c r="E83" s="63"/>
+      <c r="F83" s="63"/>
+      <c r="G83" s="63"/>
+      <c r="H83" s="63"/>
     </row>
     <row r="84" spans="1:8" ht="63.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B84" s="10"/>
       <c r="C84" s="10"/>
-      <c r="D84" s="71"/>
-      <c r="E84" s="71"/>
-      <c r="F84" s="71"/>
-      <c r="G84" s="71"/>
-      <c r="H84" s="71"/>
-    </row>
-    <row r="85" spans="1:8" ht="54" customHeight="1" x14ac:dyDescent="0.7">
+      <c r="D84" s="64"/>
+      <c r="E84" s="64"/>
+      <c r="F84" s="64"/>
+      <c r="G84" s="64"/>
+      <c r="H84" s="64"/>
+    </row>
+    <row r="85" spans="1:8" ht="54" customHeight="1" x14ac:dyDescent="0.9">
       <c r="A85" s="2"/>
       <c r="B85" s="1">
         <f>YEAR(DATE(Calendario6Año,Calendario6MesOpción+1,1))</f>
@@ -10747,24 +10531,24 @@
       <c r="C97" s="4">
         <v>44047</v>
       </c>
-      <c r="D97" s="69" t="s">
+      <c r="D97" s="62" t="s">
         <v>1</v>
       </c>
-      <c r="E97" s="70"/>
-      <c r="F97" s="70"/>
-      <c r="G97" s="70"/>
-      <c r="H97" s="70"/>
+      <c r="E97" s="63"/>
+      <c r="F97" s="63"/>
+      <c r="G97" s="63"/>
+      <c r="H97" s="63"/>
     </row>
     <row r="98" spans="1:8" ht="63.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B98" s="10"/>
       <c r="C98" s="10"/>
-      <c r="D98" s="71"/>
-      <c r="E98" s="71"/>
-      <c r="F98" s="71"/>
-      <c r="G98" s="71"/>
-      <c r="H98" s="71"/>
-    </row>
-    <row r="99" spans="1:8" ht="54" customHeight="1" x14ac:dyDescent="0.7">
+      <c r="D98" s="64"/>
+      <c r="E98" s="64"/>
+      <c r="F98" s="64"/>
+      <c r="G98" s="64"/>
+      <c r="H98" s="64"/>
+    </row>
+    <row r="99" spans="1:8" ht="54" customHeight="1" x14ac:dyDescent="0.9">
       <c r="A99" s="2"/>
       <c r="B99" s="1">
         <f>YEAR(DATE(Calendario7Año,Calendario7MesOpción+1,1))</f>
@@ -10984,24 +10768,24 @@
       <c r="C111" s="4">
         <v>44075</v>
       </c>
-      <c r="D111" s="69" t="s">
+      <c r="D111" s="62" t="s">
         <v>1</v>
       </c>
-      <c r="E111" s="70"/>
-      <c r="F111" s="70"/>
-      <c r="G111" s="70"/>
-      <c r="H111" s="70"/>
+      <c r="E111" s="63"/>
+      <c r="F111" s="63"/>
+      <c r="G111" s="63"/>
+      <c r="H111" s="63"/>
     </row>
     <row r="112" spans="1:8" ht="63.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B112" s="10"/>
       <c r="C112" s="10"/>
-      <c r="D112" s="71"/>
-      <c r="E112" s="71"/>
-      <c r="F112" s="71"/>
-      <c r="G112" s="71"/>
-      <c r="H112" s="71"/>
-    </row>
-    <row r="113" spans="1:8" ht="54" customHeight="1" x14ac:dyDescent="0.7">
+      <c r="D112" s="64"/>
+      <c r="E112" s="64"/>
+      <c r="F112" s="64"/>
+      <c r="G112" s="64"/>
+      <c r="H112" s="64"/>
+    </row>
+    <row r="113" spans="1:8" ht="54" customHeight="1" x14ac:dyDescent="0.9">
       <c r="A113" s="2"/>
       <c r="B113" s="1">
         <f>YEAR(DATE(Calendario8Año,Calendario8MesOpción+1,1))</f>
@@ -11221,24 +11005,24 @@
       <c r="C125" s="4">
         <v>44110</v>
       </c>
-      <c r="D125" s="69" t="s">
+      <c r="D125" s="62" t="s">
         <v>1</v>
       </c>
-      <c r="E125" s="70"/>
-      <c r="F125" s="70"/>
-      <c r="G125" s="70"/>
-      <c r="H125" s="70"/>
+      <c r="E125" s="63"/>
+      <c r="F125" s="63"/>
+      <c r="G125" s="63"/>
+      <c r="H125" s="63"/>
     </row>
     <row r="126" spans="1:8" ht="63.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B126" s="10"/>
       <c r="C126" s="10"/>
-      <c r="D126" s="71"/>
-      <c r="E126" s="71"/>
-      <c r="F126" s="71"/>
-      <c r="G126" s="71"/>
-      <c r="H126" s="71"/>
-    </row>
-    <row r="127" spans="1:8" ht="54" customHeight="1" x14ac:dyDescent="0.7">
+      <c r="D126" s="64"/>
+      <c r="E126" s="64"/>
+      <c r="F126" s="64"/>
+      <c r="G126" s="64"/>
+      <c r="H126" s="64"/>
+    </row>
+    <row r="127" spans="1:8" ht="54" customHeight="1" x14ac:dyDescent="0.9">
       <c r="A127" s="2"/>
       <c r="B127" s="1">
         <f>YEAR(DATE(Calendario9Año,Calendario9MesOpción+1,1))</f>
@@ -11458,24 +11242,24 @@
       <c r="C139" s="4">
         <v>44138</v>
       </c>
-      <c r="D139" s="69" t="s">
+      <c r="D139" s="62" t="s">
         <v>1</v>
       </c>
-      <c r="E139" s="70"/>
-      <c r="F139" s="70"/>
-      <c r="G139" s="70"/>
-      <c r="H139" s="70"/>
+      <c r="E139" s="63"/>
+      <c r="F139" s="63"/>
+      <c r="G139" s="63"/>
+      <c r="H139" s="63"/>
     </row>
     <row r="140" spans="2:8" ht="63.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B140" s="10"/>
       <c r="C140" s="10"/>
-      <c r="D140" s="71"/>
-      <c r="E140" s="71"/>
-      <c r="F140" s="71"/>
-      <c r="G140" s="71"/>
-      <c r="H140" s="71"/>
-    </row>
-    <row r="141" spans="2:8" ht="54" customHeight="1" x14ac:dyDescent="0.7">
+      <c r="D140" s="64"/>
+      <c r="E140" s="64"/>
+      <c r="F140" s="64"/>
+      <c r="G140" s="64"/>
+      <c r="H140" s="64"/>
+    </row>
+    <row r="141" spans="2:8" ht="54" customHeight="1" x14ac:dyDescent="0.9">
       <c r="B141" s="1">
         <f>YEAR(DATE(Calendario10Año,Calendario10MesOpción+1,1))</f>
         <v>2020</v>
@@ -11693,24 +11477,24 @@
       <c r="C153" s="4">
         <v>44166</v>
       </c>
-      <c r="D153" s="69" t="s">
+      <c r="D153" s="62" t="s">
         <v>1</v>
       </c>
-      <c r="E153" s="70"/>
-      <c r="F153" s="70"/>
-      <c r="G153" s="70"/>
-      <c r="H153" s="70"/>
+      <c r="E153" s="63"/>
+      <c r="F153" s="63"/>
+      <c r="G153" s="63"/>
+      <c r="H153" s="63"/>
     </row>
     <row r="154" spans="2:8" ht="63.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B154" s="10"/>
       <c r="C154" s="10"/>
-      <c r="D154" s="71"/>
-      <c r="E154" s="71"/>
-      <c r="F154" s="71"/>
-      <c r="G154" s="71"/>
-      <c r="H154" s="71"/>
-    </row>
-    <row r="155" spans="2:8" ht="54" customHeight="1" x14ac:dyDescent="0.7">
+      <c r="D154" s="64"/>
+      <c r="E154" s="64"/>
+      <c r="F154" s="64"/>
+      <c r="G154" s="64"/>
+      <c r="H154" s="64"/>
+    </row>
+    <row r="155" spans="2:8" ht="54" customHeight="1" x14ac:dyDescent="0.9">
       <c r="B155" s="1">
         <f>YEAR(DATE(Calendario11Año,Calendario11MesOpción+1,1))</f>
         <v>2020</v>
@@ -11928,22 +11712,22 @@
       <c r="C167" s="4">
         <v>44201</v>
       </c>
-      <c r="D167" s="69" t="s">
+      <c r="D167" s="62" t="s">
         <v>1</v>
       </c>
-      <c r="E167" s="70"/>
-      <c r="F167" s="70"/>
-      <c r="G167" s="70"/>
-      <c r="H167" s="70"/>
+      <c r="E167" s="63"/>
+      <c r="F167" s="63"/>
+      <c r="G167" s="63"/>
+      <c r="H167" s="63"/>
     </row>
     <row r="168" spans="2:8" ht="63.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B168" s="10"/>
       <c r="C168" s="10"/>
-      <c r="D168" s="71"/>
-      <c r="E168" s="71"/>
-      <c r="F168" s="71"/>
-      <c r="G168" s="71"/>
-      <c r="H168" s="71"/>
+      <c r="D168" s="64"/>
+      <c r="E168" s="64"/>
+      <c r="F168" s="64"/>
+      <c r="G168" s="64"/>
+      <c r="H168" s="64"/>
     </row>
   </sheetData>
   <mergeCells count="24">
@@ -12076,16 +11860,16 @@
     <pageSetUpPr autoPageBreaks="0" fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:H168"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.75" defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.77734375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="2" customWidth="1"/>
-    <col min="2" max="2" width="18.25" customWidth="1"/>
-    <col min="3" max="8" width="17.625" customWidth="1"/>
-    <col min="9" max="9" width="2.5" customWidth="1"/>
-    <col min="14" max="14" width="6.75" customWidth="1"/>
+    <col min="2" max="2" width="18.21875" customWidth="1"/>
+    <col min="3" max="8" width="17.6640625" customWidth="1"/>
+    <col min="9" max="9" width="2.44140625" customWidth="1"/>
+    <col min="14" max="14" width="6.77734375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="54" customHeight="1" x14ac:dyDescent="0.7">
+    <row r="1" spans="1:8" ht="54" customHeight="1" x14ac:dyDescent="0.9">
       <c r="A1" s="2"/>
       <c r="B1" s="1">
         <v>2026</v>
@@ -12302,24 +12086,24 @@
       <c r="C13" s="4">
         <v>46056</v>
       </c>
-      <c r="D13" s="73" t="s">
+      <c r="D13" s="66" t="s">
         <v>1</v>
       </c>
-      <c r="E13" s="74"/>
-      <c r="F13" s="74"/>
-      <c r="G13" s="74"/>
-      <c r="H13" s="74"/>
+      <c r="E13" s="67"/>
+      <c r="F13" s="67"/>
+      <c r="G13" s="67"/>
+      <c r="H13" s="67"/>
     </row>
     <row r="14" spans="1:8" ht="63.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B14" s="10"/>
       <c r="C14" s="10"/>
-      <c r="D14" s="72"/>
-      <c r="E14" s="71"/>
-      <c r="F14" s="71"/>
-      <c r="G14" s="71"/>
-      <c r="H14" s="71"/>
-    </row>
-    <row r="15" spans="1:8" ht="54" customHeight="1" x14ac:dyDescent="0.7">
+      <c r="D14" s="65"/>
+      <c r="E14" s="64"/>
+      <c r="F14" s="64"/>
+      <c r="G14" s="64"/>
+      <c r="H14" s="64"/>
+    </row>
+    <row r="15" spans="1:8" ht="54" customHeight="1" x14ac:dyDescent="0.9">
       <c r="A15" s="2"/>
       <c r="B15" s="1">
         <f>YEAR(DATE(Calendario1Año,Calendario1MesOpción+1,1))</f>
@@ -12539,24 +12323,24 @@
       <c r="C27" s="4">
         <v>46084</v>
       </c>
-      <c r="D27" s="75" t="s">
+      <c r="D27" s="63" t="s">
         <v>1</v>
       </c>
-      <c r="E27" s="75"/>
-      <c r="F27" s="75"/>
-      <c r="G27" s="75"/>
-      <c r="H27" s="75"/>
+      <c r="E27" s="63"/>
+      <c r="F27" s="63"/>
+      <c r="G27" s="63"/>
+      <c r="H27" s="63"/>
     </row>
     <row r="28" spans="1:8" ht="63.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B28" s="10"/>
       <c r="C28" s="10"/>
-      <c r="D28" s="71"/>
-      <c r="E28" s="71"/>
-      <c r="F28" s="71"/>
-      <c r="G28" s="71"/>
-      <c r="H28" s="71"/>
-    </row>
-    <row r="29" spans="1:8" ht="54" customHeight="1" x14ac:dyDescent="0.7">
+      <c r="D28" s="64"/>
+      <c r="E28" s="64"/>
+      <c r="F28" s="64"/>
+      <c r="G28" s="64"/>
+      <c r="H28" s="64"/>
+    </row>
+    <row r="29" spans="1:8" ht="54" customHeight="1" x14ac:dyDescent="0.9">
       <c r="A29" s="2"/>
       <c r="B29" s="1">
         <f>YEAR(DATE(Calendario2Año,Calendario2MesOpción+1,1))</f>
@@ -12776,24 +12560,24 @@
       <c r="C41" s="4">
         <v>46112</v>
       </c>
-      <c r="D41" s="75" t="s">
+      <c r="D41" s="63" t="s">
         <v>1</v>
       </c>
-      <c r="E41" s="75"/>
-      <c r="F41" s="75"/>
-      <c r="G41" s="75"/>
-      <c r="H41" s="75"/>
+      <c r="E41" s="63"/>
+      <c r="F41" s="63"/>
+      <c r="G41" s="63"/>
+      <c r="H41" s="63"/>
     </row>
     <row r="42" spans="1:8" ht="63.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B42" s="10"/>
       <c r="C42" s="10"/>
-      <c r="D42" s="71"/>
-      <c r="E42" s="71"/>
-      <c r="F42" s="71"/>
-      <c r="G42" s="71"/>
-      <c r="H42" s="71"/>
-    </row>
-    <row r="43" spans="1:8" ht="54" customHeight="1" x14ac:dyDescent="0.7">
+      <c r="D42" s="64"/>
+      <c r="E42" s="64"/>
+      <c r="F42" s="64"/>
+      <c r="G42" s="64"/>
+      <c r="H42" s="64"/>
+    </row>
+    <row r="43" spans="1:8" ht="54" customHeight="1" x14ac:dyDescent="0.9">
       <c r="A43" s="2"/>
       <c r="B43" s="1">
         <f>YEAR(DATE(Calendario3Año,Calendario3MesOpción+1,1))</f>
@@ -13013,24 +12797,24 @@
       <c r="C55" s="4">
         <v>46147</v>
       </c>
-      <c r="D55" s="69" t="s">
+      <c r="D55" s="62" t="s">
         <v>1</v>
       </c>
-      <c r="E55" s="70"/>
-      <c r="F55" s="70"/>
-      <c r="G55" s="70"/>
-      <c r="H55" s="70"/>
+      <c r="E55" s="63"/>
+      <c r="F55" s="63"/>
+      <c r="G55" s="63"/>
+      <c r="H55" s="63"/>
     </row>
     <row r="56" spans="1:8" ht="63.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B56" s="10"/>
       <c r="C56" s="10"/>
-      <c r="D56" s="71"/>
-      <c r="E56" s="71"/>
-      <c r="F56" s="71"/>
-      <c r="G56" s="71"/>
-      <c r="H56" s="71"/>
-    </row>
-    <row r="57" spans="1:8" ht="54" customHeight="1" x14ac:dyDescent="0.7">
+      <c r="D56" s="64"/>
+      <c r="E56" s="64"/>
+      <c r="F56" s="64"/>
+      <c r="G56" s="64"/>
+      <c r="H56" s="64"/>
+    </row>
+    <row r="57" spans="1:8" ht="54" customHeight="1" x14ac:dyDescent="0.9">
       <c r="A57" s="2"/>
       <c r="B57" s="1">
         <f>YEAR(DATE(Calendario4Año,Calendario4MesOpción+1,1))</f>
@@ -13250,24 +13034,24 @@
       <c r="C69" s="4">
         <v>46175</v>
       </c>
-      <c r="D69" s="69" t="s">
+      <c r="D69" s="62" t="s">
         <v>1</v>
       </c>
-      <c r="E69" s="70"/>
-      <c r="F69" s="70"/>
-      <c r="G69" s="70"/>
-      <c r="H69" s="70"/>
+      <c r="E69" s="63"/>
+      <c r="F69" s="63"/>
+      <c r="G69" s="63"/>
+      <c r="H69" s="63"/>
     </row>
     <row r="70" spans="1:8" ht="63.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B70" s="13"/>
       <c r="C70" s="10"/>
-      <c r="D70" s="71"/>
-      <c r="E70" s="71"/>
-      <c r="F70" s="71"/>
-      <c r="G70" s="71"/>
-      <c r="H70" s="71"/>
-    </row>
-    <row r="71" spans="1:8" ht="54" customHeight="1" x14ac:dyDescent="0.7">
+      <c r="D70" s="64"/>
+      <c r="E70" s="64"/>
+      <c r="F70" s="64"/>
+      <c r="G70" s="64"/>
+      <c r="H70" s="64"/>
+    </row>
+    <row r="71" spans="1:8" ht="54" customHeight="1" x14ac:dyDescent="0.9">
       <c r="A71" s="2"/>
       <c r="B71" s="1">
         <f>YEAR(DATE(Calendario5Año,Calendario5MesOpción+1,1))</f>
@@ -13340,11 +13124,11 @@
     </row>
     <row r="74" spans="1:8" ht="56.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B74" s="10"/>
-      <c r="C74" s="59"/>
+      <c r="C74" s="52"/>
       <c r="D74" s="13"/>
-      <c r="E74" s="59"/>
+      <c r="E74" s="52"/>
       <c r="F74" s="13"/>
-      <c r="G74" s="59"/>
+      <c r="G74" s="52"/>
       <c r="H74" s="11"/>
     </row>
     <row r="75" spans="1:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
@@ -13373,11 +13157,11 @@
     </row>
     <row r="76" spans="1:8" ht="56.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B76" s="13"/>
-      <c r="C76" s="59"/>
+      <c r="C76" s="52"/>
       <c r="D76" s="13"/>
-      <c r="E76" s="59"/>
+      <c r="E76" s="52"/>
       <c r="F76" s="13"/>
-      <c r="G76" s="59"/>
+      <c r="G76" s="52"/>
       <c r="H76" s="11"/>
     </row>
     <row r="77" spans="1:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
@@ -13406,11 +13190,11 @@
     </row>
     <row r="78" spans="1:8" ht="56.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B78" s="13"/>
-      <c r="C78" s="59"/>
+      <c r="C78" s="52"/>
       <c r="D78" s="13"/>
-      <c r="E78" s="59"/>
+      <c r="E78" s="52"/>
       <c r="F78" s="13"/>
-      <c r="G78" s="59"/>
+      <c r="G78" s="52"/>
       <c r="H78" s="11"/>
     </row>
     <row r="79" spans="1:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
@@ -13439,11 +13223,11 @@
     </row>
     <row r="80" spans="1:8" ht="56.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B80" s="13"/>
-      <c r="C80" s="59"/>
+      <c r="C80" s="52"/>
       <c r="D80" s="13"/>
-      <c r="E80" s="59"/>
+      <c r="E80" s="52"/>
       <c r="F80" s="13"/>
-      <c r="G80" s="59"/>
+      <c r="G80" s="52"/>
       <c r="H80" s="11"/>
     </row>
     <row r="81" spans="1:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
@@ -13472,7 +13256,7 @@
     </row>
     <row r="82" spans="1:8" ht="57" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B82" s="13"/>
-      <c r="C82" s="59"/>
+      <c r="C82" s="52"/>
       <c r="D82" s="13"/>
       <c r="E82" s="10"/>
       <c r="F82" s="10"/>
@@ -13487,24 +13271,24 @@
       <c r="C83" s="4">
         <v>46210</v>
       </c>
-      <c r="D83" s="69" t="s">
+      <c r="D83" s="62" t="s">
         <v>1</v>
       </c>
-      <c r="E83" s="70"/>
-      <c r="F83" s="70"/>
-      <c r="G83" s="70"/>
-      <c r="H83" s="70"/>
+      <c r="E83" s="63"/>
+      <c r="F83" s="63"/>
+      <c r="G83" s="63"/>
+      <c r="H83" s="63"/>
     </row>
     <row r="84" spans="1:8" ht="63.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B84" s="10"/>
       <c r="C84" s="10"/>
-      <c r="D84" s="71"/>
-      <c r="E84" s="71"/>
-      <c r="F84" s="71"/>
-      <c r="G84" s="71"/>
-      <c r="H84" s="71"/>
-    </row>
-    <row r="85" spans="1:8" ht="54" customHeight="1" x14ac:dyDescent="0.7">
+      <c r="D84" s="64"/>
+      <c r="E84" s="64"/>
+      <c r="F84" s="64"/>
+      <c r="G84" s="64"/>
+      <c r="H84" s="64"/>
+    </row>
+    <row r="85" spans="1:8" ht="54" customHeight="1" x14ac:dyDescent="0.9">
       <c r="A85" s="2"/>
       <c r="B85" s="1">
         <f>YEAR(DATE(Calendario6Año,Calendario6MesOpción+1,1))</f>
@@ -13724,24 +13508,24 @@
       <c r="C97" s="4">
         <v>46238</v>
       </c>
-      <c r="D97" s="69" t="s">
+      <c r="D97" s="62" t="s">
         <v>1</v>
       </c>
-      <c r="E97" s="70"/>
-      <c r="F97" s="70"/>
-      <c r="G97" s="70"/>
-      <c r="H97" s="70"/>
+      <c r="E97" s="63"/>
+      <c r="F97" s="63"/>
+      <c r="G97" s="63"/>
+      <c r="H97" s="63"/>
     </row>
     <row r="98" spans="1:8" ht="63.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B98" s="10"/>
       <c r="C98" s="10"/>
-      <c r="D98" s="71"/>
-      <c r="E98" s="71"/>
-      <c r="F98" s="71"/>
-      <c r="G98" s="71"/>
-      <c r="H98" s="71"/>
-    </row>
-    <row r="99" spans="1:8" ht="54" customHeight="1" x14ac:dyDescent="0.7">
+      <c r="D98" s="64"/>
+      <c r="E98" s="64"/>
+      <c r="F98" s="64"/>
+      <c r="G98" s="64"/>
+      <c r="H98" s="64"/>
+    </row>
+    <row r="99" spans="1:8" ht="54" customHeight="1" x14ac:dyDescent="0.9">
       <c r="A99" s="2"/>
       <c r="B99" s="1">
         <f>YEAR(DATE(Calendario7Año,Calendario7MesOpción+1,1))</f>
@@ -13961,24 +13745,24 @@
       <c r="C111" s="4">
         <v>46266</v>
       </c>
-      <c r="D111" s="69" t="s">
+      <c r="D111" s="62" t="s">
         <v>1</v>
       </c>
-      <c r="E111" s="70"/>
-      <c r="F111" s="70"/>
-      <c r="G111" s="70"/>
-      <c r="H111" s="70"/>
+      <c r="E111" s="63"/>
+      <c r="F111" s="63"/>
+      <c r="G111" s="63"/>
+      <c r="H111" s="63"/>
     </row>
     <row r="112" spans="1:8" ht="63.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B112" s="13"/>
       <c r="C112" s="10"/>
-      <c r="D112" s="71"/>
-      <c r="E112" s="71"/>
-      <c r="F112" s="71"/>
-      <c r="G112" s="71"/>
-      <c r="H112" s="71"/>
-    </row>
-    <row r="113" spans="1:8" ht="54" customHeight="1" x14ac:dyDescent="0.7">
+      <c r="D112" s="64"/>
+      <c r="E112" s="64"/>
+      <c r="F112" s="64"/>
+      <c r="G112" s="64"/>
+      <c r="H112" s="64"/>
+    </row>
+    <row r="113" spans="1:8" ht="54" customHeight="1" x14ac:dyDescent="0.9">
       <c r="A113" s="2"/>
       <c r="B113" s="1">
         <f>YEAR(DATE(Calendario8Año,Calendario8MesOpción+1,1))</f>
@@ -14198,30 +13982,30 @@
       <c r="C125" s="4">
         <v>46301</v>
       </c>
-      <c r="D125" s="69" t="s">
+      <c r="D125" s="62" t="s">
         <v>1</v>
       </c>
-      <c r="E125" s="70"/>
-      <c r="F125" s="70"/>
-      <c r="G125" s="70"/>
-      <c r="H125" s="70"/>
+      <c r="E125" s="63"/>
+      <c r="F125" s="63"/>
+      <c r="G125" s="63"/>
+      <c r="H125" s="63"/>
     </row>
     <row r="126" spans="1:8" ht="63.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B126" s="10"/>
       <c r="C126" s="10"/>
-      <c r="D126" s="71"/>
-      <c r="E126" s="71"/>
-      <c r="F126" s="71"/>
-      <c r="G126" s="71"/>
-      <c r="H126" s="71"/>
-    </row>
-    <row r="127" spans="1:8" ht="54" customHeight="1" x14ac:dyDescent="0.7">
+      <c r="D126" s="64"/>
+      <c r="E126" s="64"/>
+      <c r="F126" s="64"/>
+      <c r="G126" s="64"/>
+      <c r="H126" s="64"/>
+    </row>
+    <row r="127" spans="1:8" ht="54" customHeight="1" x14ac:dyDescent="0.9">
       <c r="A127" s="2"/>
-      <c r="B127" s="60">
+      <c r="B127" s="53">
         <f>YEAR(DATE(Calendario9Año,Calendario9MesOpción+1,1))</f>
         <v>2026</v>
       </c>
-      <c r="C127" s="61" t="str">
+      <c r="C127" s="54" t="str">
         <f>TEXT(DATE(Calendario9Año,Calendario9MesOpción+1,1),"mmmm")</f>
         <v>octubre</v>
       </c>
@@ -14233,31 +14017,31 @@
     </row>
     <row r="128" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A128" s="3"/>
-      <c r="B128" s="62" t="str">
+      <c r="B128" s="55" t="str">
         <f>UPPER(TEXT(B129,"dddd"))</f>
         <v>LUNES</v>
       </c>
-      <c r="C128" s="63" t="str">
+      <c r="C128" s="56" t="str">
         <f t="shared" ref="C128:H128" si="9">UPPER(TEXT(C129,"dddd"))</f>
         <v>MARTES</v>
       </c>
-      <c r="D128" s="62" t="str">
+      <c r="D128" s="55" t="str">
         <f t="shared" si="9"/>
         <v>MIÉRCOLES</v>
       </c>
-      <c r="E128" s="63" t="str">
+      <c r="E128" s="56" t="str">
         <f t="shared" si="9"/>
         <v>JUEVES</v>
       </c>
-      <c r="F128" s="62" t="str">
+      <c r="F128" s="55" t="str">
         <f t="shared" si="9"/>
         <v>VIERNES</v>
       </c>
-      <c r="G128" s="63" t="str">
+      <c r="G128" s="56" t="str">
         <f t="shared" si="9"/>
         <v>SÁBADO</v>
       </c>
-      <c r="H128" s="62" t="str">
+      <c r="H128" s="55" t="str">
         <f t="shared" si="9"/>
         <v>DOMINGO</v>
       </c>
@@ -14291,7 +14075,7 @@
       <c r="C130" s="10"/>
       <c r="D130" s="10"/>
       <c r="E130" s="10"/>
-      <c r="F130" s="59"/>
+      <c r="F130" s="52"/>
       <c r="G130" s="10"/>
       <c r="H130" s="11"/>
     </row>
@@ -14320,11 +14104,11 @@
       </c>
     </row>
     <row r="132" spans="2:8" ht="56.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B132" s="59"/>
+      <c r="B132" s="52"/>
       <c r="C132" s="10"/>
-      <c r="D132" s="59"/>
+      <c r="D132" s="52"/>
       <c r="E132" s="10"/>
-      <c r="F132" s="59"/>
+      <c r="F132" s="52"/>
       <c r="G132" s="10"/>
       <c r="H132" s="11"/>
     </row>
@@ -14353,11 +14137,11 @@
       </c>
     </row>
     <row r="134" spans="2:8" ht="56.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B134" s="59"/>
+      <c r="B134" s="52"/>
       <c r="C134" s="10"/>
-      <c r="D134" s="59"/>
+      <c r="D134" s="52"/>
       <c r="E134" s="10"/>
-      <c r="F134" s="59"/>
+      <c r="F134" s="52"/>
       <c r="G134" s="10"/>
       <c r="H134" s="11"/>
     </row>
@@ -14386,13 +14170,13 @@
       </c>
     </row>
     <row r="136" spans="2:8" ht="56.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B136" s="59"/>
+      <c r="B136" s="52"/>
       <c r="C136" s="10"/>
-      <c r="D136" s="76" t="s">
+      <c r="D136" s="68" t="s">
         <v>56</v>
       </c>
-      <c r="E136" s="77"/>
-      <c r="F136" s="59"/>
+      <c r="E136" s="69"/>
+      <c r="F136" s="52"/>
       <c r="G136" s="10"/>
       <c r="H136" s="11"/>
     </row>
@@ -14421,11 +14205,11 @@
       </c>
     </row>
     <row r="138" spans="2:8" ht="57" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B138" s="59"/>
+      <c r="B138" s="52"/>
       <c r="C138" s="10"/>
-      <c r="D138" s="59"/>
+      <c r="D138" s="52"/>
       <c r="E138" s="10"/>
-      <c r="F138" s="59"/>
+      <c r="F138" s="52"/>
       <c r="G138" s="10"/>
       <c r="H138" s="12"/>
     </row>
@@ -14437,29 +14221,29 @@
       <c r="C139" s="4">
         <v>46329</v>
       </c>
-      <c r="D139" s="69" t="s">
+      <c r="D139" s="62" t="s">
         <v>1</v>
       </c>
-      <c r="E139" s="70"/>
-      <c r="F139" s="70"/>
-      <c r="G139" s="70"/>
-      <c r="H139" s="70"/>
+      <c r="E139" s="63"/>
+      <c r="F139" s="63"/>
+      <c r="G139" s="63"/>
+      <c r="H139" s="63"/>
     </row>
     <row r="140" spans="2:8" ht="63.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B140" s="10"/>
       <c r="C140" s="10"/>
-      <c r="D140" s="71"/>
-      <c r="E140" s="71"/>
-      <c r="F140" s="71"/>
-      <c r="G140" s="71"/>
-      <c r="H140" s="71"/>
-    </row>
-    <row r="141" spans="2:8" ht="54" customHeight="1" x14ac:dyDescent="0.7">
-      <c r="B141" s="60">
+      <c r="D140" s="64"/>
+      <c r="E140" s="64"/>
+      <c r="F140" s="64"/>
+      <c r="G140" s="64"/>
+      <c r="H140" s="64"/>
+    </row>
+    <row r="141" spans="2:8" ht="54" customHeight="1" x14ac:dyDescent="0.9">
+      <c r="B141" s="53">
         <f>YEAR(DATE(Calendario10Año,Calendario10MesOpción+1,1))</f>
         <v>2026</v>
       </c>
-      <c r="C141" s="61" t="str">
+      <c r="C141" s="54" t="str">
         <f>TEXT(DATE(Calendario10Año,Calendario10MesOpción+1,1),"mmmm")</f>
         <v>noviembre</v>
       </c>
@@ -14470,31 +14254,31 @@
       <c r="H141" s="2"/>
     </row>
     <row r="142" spans="2:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B142" s="62" t="str">
+      <c r="B142" s="55" t="str">
         <f>UPPER(TEXT(B143,"dddd"))</f>
         <v>LUNES</v>
       </c>
-      <c r="C142" s="63" t="str">
+      <c r="C142" s="56" t="str">
         <f t="shared" ref="C142:H142" si="10">UPPER(TEXT(C143,"dddd"))</f>
         <v>MARTES</v>
       </c>
-      <c r="D142" s="62" t="str">
+      <c r="D142" s="55" t="str">
         <f t="shared" si="10"/>
         <v>MIÉRCOLES</v>
       </c>
-      <c r="E142" s="63" t="str">
+      <c r="E142" s="56" t="str">
         <f t="shared" si="10"/>
         <v>JUEVES</v>
       </c>
-      <c r="F142" s="62" t="str">
+      <c r="F142" s="55" t="str">
         <f t="shared" si="10"/>
         <v>VIERNES</v>
       </c>
-      <c r="G142" s="63" t="str">
+      <c r="G142" s="56" t="str">
         <f t="shared" si="10"/>
         <v>SÁBADO</v>
       </c>
-      <c r="H142" s="62" t="str">
+      <c r="H142" s="55" t="str">
         <f t="shared" si="10"/>
         <v>DOMINGO</v>
       </c>
@@ -14524,11 +14308,11 @@
       </c>
     </row>
     <row r="144" spans="2:8" ht="56.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B144" s="59"/>
+      <c r="B144" s="52"/>
       <c r="C144" s="10"/>
-      <c r="D144" s="59"/>
+      <c r="D144" s="52"/>
       <c r="E144" s="10"/>
-      <c r="F144" s="59"/>
+      <c r="F144" s="52"/>
       <c r="G144" s="10"/>
       <c r="H144" s="11"/>
     </row>
@@ -14557,11 +14341,11 @@
       </c>
     </row>
     <row r="146" spans="2:8" ht="56.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B146" s="59"/>
+      <c r="B146" s="52"/>
       <c r="C146" s="10"/>
-      <c r="D146" s="59"/>
+      <c r="D146" s="52"/>
       <c r="E146" s="10"/>
-      <c r="F146" s="59"/>
+      <c r="F146" s="52"/>
       <c r="G146" s="10"/>
       <c r="H146" s="11"/>
     </row>
@@ -14590,11 +14374,11 @@
       </c>
     </row>
     <row r="148" spans="2:8" ht="56.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B148" s="59"/>
+      <c r="B148" s="52"/>
       <c r="C148" s="10"/>
-      <c r="D148" s="59"/>
+      <c r="D148" s="52"/>
       <c r="E148" s="10"/>
-      <c r="F148" s="59"/>
+      <c r="F148" s="52"/>
       <c r="G148" s="10"/>
       <c r="H148" s="11"/>
     </row>
@@ -14623,13 +14407,13 @@
       </c>
     </row>
     <row r="150" spans="2:8" ht="56.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B150" s="59"/>
+      <c r="B150" s="52"/>
       <c r="C150" s="10"/>
-      <c r="D150" s="76" t="s">
+      <c r="D150" s="68" t="s">
         <v>57</v>
       </c>
-      <c r="E150" s="77"/>
-      <c r="F150" s="59"/>
+      <c r="E150" s="69"/>
+      <c r="F150" s="52"/>
       <c r="G150" s="10"/>
       <c r="H150" s="11"/>
     </row>
@@ -14658,12 +14442,12 @@
       </c>
     </row>
     <row r="152" spans="2:8" ht="57" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B152" s="59"/>
+      <c r="B152" s="52"/>
       <c r="C152" s="10"/>
-      <c r="D152" s="78" t="s">
+      <c r="D152" s="70" t="s">
         <v>58</v>
       </c>
-      <c r="E152" s="79"/>
+      <c r="E152" s="71"/>
       <c r="F152" s="10"/>
       <c r="G152" s="10"/>
       <c r="H152" s="12"/>
@@ -14676,24 +14460,24 @@
       <c r="C153" s="4">
         <v>46357</v>
       </c>
-      <c r="D153" s="69" t="s">
+      <c r="D153" s="62" t="s">
         <v>1</v>
       </c>
-      <c r="E153" s="70"/>
-      <c r="F153" s="70"/>
-      <c r="G153" s="70"/>
-      <c r="H153" s="70"/>
+      <c r="E153" s="63"/>
+      <c r="F153" s="63"/>
+      <c r="G153" s="63"/>
+      <c r="H153" s="63"/>
     </row>
     <row r="154" spans="2:8" ht="63.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B154" s="10"/>
       <c r="C154" s="10"/>
-      <c r="D154" s="71"/>
-      <c r="E154" s="71"/>
-      <c r="F154" s="71"/>
-      <c r="G154" s="71"/>
-      <c r="H154" s="71"/>
-    </row>
-    <row r="155" spans="2:8" ht="54" customHeight="1" x14ac:dyDescent="0.7">
+      <c r="D154" s="64"/>
+      <c r="E154" s="64"/>
+      <c r="F154" s="64"/>
+      <c r="G154" s="64"/>
+      <c r="H154" s="64"/>
+    </row>
+    <row r="155" spans="2:8" ht="54" customHeight="1" x14ac:dyDescent="0.9">
       <c r="B155" s="1">
         <f>YEAR(DATE(Calendario11Año,Calendario11MesOpción+1,1))</f>
         <v>2026</v>
@@ -14830,7 +14614,7 @@
     </row>
     <row r="162" spans="2:8" ht="56.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B162" s="13"/>
-      <c r="C162" s="59"/>
+      <c r="C162" s="52"/>
       <c r="D162" s="13"/>
       <c r="E162" s="10"/>
       <c r="F162" s="13"/>
@@ -14911,22 +14695,22 @@
       <c r="C167" s="4">
         <v>46392</v>
       </c>
-      <c r="D167" s="69" t="s">
+      <c r="D167" s="62" t="s">
         <v>1</v>
       </c>
-      <c r="E167" s="70"/>
-      <c r="F167" s="70"/>
-      <c r="G167" s="70"/>
-      <c r="H167" s="70"/>
+      <c r="E167" s="63"/>
+      <c r="F167" s="63"/>
+      <c r="G167" s="63"/>
+      <c r="H167" s="63"/>
     </row>
     <row r="168" spans="2:8" ht="63.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B168" s="10"/>
       <c r="C168" s="10"/>
-      <c r="D168" s="71"/>
-      <c r="E168" s="71"/>
-      <c r="F168" s="71"/>
-      <c r="G168" s="71"/>
-      <c r="H168" s="71"/>
+      <c r="D168" s="64"/>
+      <c r="E168" s="64"/>
+      <c r="F168" s="64"/>
+      <c r="G168" s="64"/>
+      <c r="H168" s="64"/>
     </row>
   </sheetData>
   <mergeCells count="27">

--- a/actividades MIR 2026/IPPI SDTI - Calendario Actividades.xlsx
+++ b/actividades MIR 2026/IPPI SDTI - Calendario Actividades.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="26327"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="24334"/>
   <workbookPr codeName="ThisWorkbook" autoCompressPictures="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\MTGH\Documents\GitHub\proyecto-ippi\actividades MIR 2026\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\IPPI 11\Documents\GitHub\proyecto-ippi\actividades MIR 2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2BB2C3C0-2EDD-428C-A516-64F587783FBC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1713BF41-644D-47E1-BB56-44040801A22A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" tabRatio="788" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="16440" tabRatio="788" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Calendario" sheetId="15" r:id="rId1"/>
@@ -1224,14 +1224,14 @@
     <xf numFmtId="0" fontId="11" fillId="13" borderId="3" xfId="11" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="10" borderId="0" xfId="13" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="13" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="14" xfId="13" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="10" borderId="0" xfId="13" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="9" borderId="0" xfId="13" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1239,14 +1239,14 @@
     <xf numFmtId="0" fontId="17" fillId="10" borderId="0" xfId="13" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="7" applyNumberFormat="1">
+      <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
+    </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="8" xfId="8" applyFont="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
     <xf numFmtId="164" fontId="12" fillId="0" borderId="8" xfId="8">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="7" applyNumberFormat="1">
-      <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="7" applyNumberFormat="1" applyBorder="1">
       <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
@@ -1782,10 +1782,10 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A2:AH74"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11" defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="5.6640625" style="14" customWidth="1"/>
-    <col min="2" max="2" width="10.6640625" style="14" customWidth="1"/>
+    <col min="1" max="1" width="5.625" style="14" customWidth="1"/>
+    <col min="2" max="2" width="10.625" style="14" customWidth="1"/>
     <col min="3" max="8" width="12" style="14" customWidth="1"/>
     <col min="9" max="9" width="11" style="14"/>
     <col min="10" max="10" width="0" style="14" hidden="1" customWidth="1"/>
@@ -1797,7 +1797,7 @@
     <col min="33" max="16384" width="11" style="14"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:34" ht="28.5" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="2" spans="1:34" ht="28.5" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A2" s="60"/>
       <c r="B2" s="60"/>
       <c r="C2" s="61" t="s">
@@ -1808,36 +1808,36 @@
       <c r="F2" s="61"/>
       <c r="G2" s="61"/>
       <c r="H2" s="61"/>
-      <c r="K2" s="57" t="s">
+      <c r="K2" s="59" t="s">
         <v>5</v>
       </c>
-      <c r="L2" s="57"/>
-      <c r="M2" s="57"/>
-      <c r="N2" s="57"/>
-      <c r="O2" s="57"/>
-      <c r="P2" s="57"/>
-      <c r="S2" s="57" t="s">
+      <c r="L2" s="59"/>
+      <c r="M2" s="59"/>
+      <c r="N2" s="59"/>
+      <c r="O2" s="59"/>
+      <c r="P2" s="59"/>
+      <c r="S2" s="59" t="s">
         <v>6</v>
       </c>
-      <c r="T2" s="57"/>
-      <c r="U2" s="57"/>
-      <c r="V2" s="57"/>
-      <c r="W2" s="57"/>
-      <c r="X2" s="57"/>
-      <c r="AA2" s="57" t="s">
+      <c r="T2" s="59"/>
+      <c r="U2" s="59"/>
+      <c r="V2" s="59"/>
+      <c r="W2" s="59"/>
+      <c r="X2" s="59"/>
+      <c r="AA2" s="59" t="s">
         <v>7</v>
       </c>
-      <c r="AB2" s="57"/>
-      <c r="AC2" s="57"/>
-      <c r="AD2" s="57"/>
-      <c r="AE2" s="57"/>
-      <c r="AF2" s="57"/>
+      <c r="AB2" s="59"/>
+      <c r="AC2" s="59"/>
+      <c r="AD2" s="59"/>
+      <c r="AE2" s="59"/>
+      <c r="AF2" s="59"/>
     </row>
     <row r="3" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A3" s="60"/>
       <c r="B3" s="60"/>
     </row>
-    <row r="4" spans="1:34" s="16" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:34" s="16" customFormat="1" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A4" s="60"/>
       <c r="B4" s="60"/>
       <c r="C4" s="51" t="s">
@@ -1922,8 +1922,8 @@
         <v>12</v>
       </c>
     </row>
-    <row r="5" spans="1:34" ht="15.75" customHeight="1" thickTop="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="58" t="s">
+    <row r="5" spans="1:34" ht="15.75" customHeight="1" thickTop="1" x14ac:dyDescent="0.35">
+      <c r="A5" s="57" t="s">
         <v>16</v>
       </c>
       <c r="B5" s="17"/>
@@ -1933,7 +1933,7 @@
       <c r="F5" s="19"/>
       <c r="G5" s="19"/>
       <c r="H5" s="20"/>
-      <c r="J5" s="58" t="s">
+      <c r="J5" s="57" t="s">
         <v>16</v>
       </c>
       <c r="K5" s="18" t="s">
@@ -1954,7 +1954,7 @@
       <c r="P5" s="20" t="s">
         <v>17</v>
       </c>
-      <c r="R5" s="58" t="s">
+      <c r="R5" s="57" t="s">
         <v>16</v>
       </c>
       <c r="S5" s="18" t="s">
@@ -1975,7 +1975,7 @@
       <c r="X5" s="20" t="s">
         <v>17</v>
       </c>
-      <c r="Z5" s="58" t="s">
+      <c r="Z5" s="57" t="s">
         <v>16</v>
       </c>
       <c r="AA5" s="18" t="s">
@@ -1998,9 +1998,9 @@
       </c>
       <c r="AH5" s="21"/>
     </row>
-    <row r="6" spans="1:34" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="58"/>
-      <c r="B6" s="59" t="s">
+    <row r="6" spans="1:34" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A6" s="57"/>
+      <c r="B6" s="58" t="s">
         <v>18</v>
       </c>
       <c r="C6" s="33" t="s">
@@ -2015,7 +2015,7 @@
         <v>19</v>
       </c>
       <c r="H6" s="36"/>
-      <c r="J6" s="58"/>
+      <c r="J6" s="57"/>
       <c r="K6" s="22" t="s">
         <v>20</v>
       </c>
@@ -2034,7 +2034,7 @@
       <c r="P6" s="24" t="s">
         <v>21</v>
       </c>
-      <c r="R6" s="58"/>
+      <c r="R6" s="57"/>
       <c r="S6" s="22" t="s">
         <v>21</v>
       </c>
@@ -2053,7 +2053,7 @@
       <c r="X6" s="24" t="s">
         <v>21</v>
       </c>
-      <c r="Z6" s="58"/>
+      <c r="Z6" s="57"/>
       <c r="AA6" s="22" t="s">
         <v>20</v>
       </c>
@@ -2073,16 +2073,16 @@
         <v>21</v>
       </c>
     </row>
-    <row r="7" spans="1:34" ht="8.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="58"/>
-      <c r="B7" s="59"/>
+    <row r="7" spans="1:34" ht="8.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A7" s="57"/>
+      <c r="B7" s="58"/>
       <c r="C7" s="39"/>
       <c r="D7" s="42"/>
       <c r="E7" s="39"/>
       <c r="F7" s="42"/>
       <c r="G7" s="39"/>
       <c r="H7" s="42"/>
-      <c r="J7" s="58"/>
+      <c r="J7" s="57"/>
       <c r="K7" s="22" t="s">
         <v>22</v>
       </c>
@@ -2101,7 +2101,7 @@
       <c r="P7" s="24" t="s">
         <v>23</v>
       </c>
-      <c r="R7" s="58"/>
+      <c r="R7" s="57"/>
       <c r="S7" s="22" t="s">
         <v>23</v>
       </c>
@@ -2120,7 +2120,7 @@
       <c r="X7" s="24" t="s">
         <v>23</v>
       </c>
-      <c r="Z7" s="58"/>
+      <c r="Z7" s="57"/>
       <c r="AA7" s="22" t="s">
         <v>21</v>
       </c>
@@ -2140,9 +2140,9 @@
         <v>23</v>
       </c>
     </row>
-    <row r="8" spans="1:34" ht="27.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="58"/>
-      <c r="B8" s="59"/>
+    <row r="8" spans="1:34" ht="27.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A8" s="57"/>
+      <c r="B8" s="58"/>
       <c r="C8" s="35" t="s">
         <v>2</v>
       </c>
@@ -2155,7 +2155,7 @@
         <v>2</v>
       </c>
       <c r="H8" s="44"/>
-      <c r="J8" s="58"/>
+      <c r="J8" s="57"/>
       <c r="K8" s="22" t="s">
         <v>21</v>
       </c>
@@ -2174,7 +2174,7 @@
       <c r="P8" s="24" t="s">
         <v>24</v>
       </c>
-      <c r="R8" s="58"/>
+      <c r="R8" s="57"/>
       <c r="S8" s="22" t="s">
         <v>25</v>
       </c>
@@ -2193,7 +2193,7 @@
       <c r="X8" s="24" t="s">
         <v>24</v>
       </c>
-      <c r="Z8" s="58"/>
+      <c r="Z8" s="57"/>
       <c r="AA8" s="22" t="s">
         <v>23</v>
       </c>
@@ -2213,8 +2213,8 @@
         <v>24</v>
       </c>
     </row>
-    <row r="9" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="58"/>
+    <row r="9" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A9" s="57"/>
       <c r="B9" s="16"/>
       <c r="C9" s="48"/>
       <c r="D9" s="37"/>
@@ -2222,21 +2222,21 @@
       <c r="F9" s="38"/>
       <c r="G9" s="48"/>
       <c r="H9" s="40"/>
-      <c r="J9" s="58"/>
+      <c r="J9" s="57"/>
       <c r="K9" s="22"/>
       <c r="L9" s="23"/>
       <c r="M9" s="23"/>
       <c r="N9" s="23"/>
       <c r="O9" s="23"/>
       <c r="P9" s="24"/>
-      <c r="R9" s="58"/>
+      <c r="R9" s="57"/>
       <c r="S9" s="22"/>
       <c r="T9" s="23"/>
       <c r="U9" s="23"/>
       <c r="V9" s="23"/>
       <c r="W9" s="23"/>
       <c r="X9" s="24"/>
-      <c r="Z9" s="58"/>
+      <c r="Z9" s="57"/>
       <c r="AA9" s="22"/>
       <c r="AB9" s="23"/>
       <c r="AC9" s="23"/>
@@ -2244,9 +2244,9 @@
       <c r="AE9" s="23"/>
       <c r="AF9" s="24"/>
     </row>
-    <row r="10" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="58"/>
-      <c r="B10" s="59" t="s">
+    <row r="10" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A10" s="57"/>
+      <c r="B10" s="58" t="s">
         <v>27</v>
       </c>
       <c r="C10" s="33" t="s">
@@ -2261,7 +2261,7 @@
         <v>19</v>
       </c>
       <c r="H10" s="36"/>
-      <c r="J10" s="58"/>
+      <c r="J10" s="57"/>
       <c r="K10" s="22" t="s">
         <v>24</v>
       </c>
@@ -2280,7 +2280,7 @@
       <c r="P10" s="24" t="s">
         <v>26</v>
       </c>
-      <c r="R10" s="58"/>
+      <c r="R10" s="57"/>
       <c r="S10" s="22" t="s">
         <v>28</v>
       </c>
@@ -2299,7 +2299,7 @@
       <c r="X10" s="24" t="s">
         <v>26</v>
       </c>
-      <c r="Z10" s="58"/>
+      <c r="Z10" s="57"/>
       <c r="AA10" s="22" t="s">
         <v>25</v>
       </c>
@@ -2319,16 +2319,16 @@
         <v>26</v>
       </c>
     </row>
-    <row r="11" spans="1:34" ht="6.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="58"/>
-      <c r="B11" s="59"/>
+    <row r="11" spans="1:34" ht="6.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A11" s="57"/>
+      <c r="B11" s="58"/>
       <c r="C11" s="39"/>
       <c r="D11" s="42"/>
       <c r="E11" s="39"/>
       <c r="F11" s="42"/>
       <c r="G11" s="39"/>
       <c r="H11" s="42"/>
-      <c r="J11" s="58"/>
+      <c r="J11" s="57"/>
       <c r="K11" s="22" t="s">
         <v>25</v>
       </c>
@@ -2347,7 +2347,7 @@
       <c r="P11" s="24" t="s">
         <v>28</v>
       </c>
-      <c r="R11" s="58"/>
+      <c r="R11" s="57"/>
       <c r="S11" s="22" t="s">
         <v>30</v>
       </c>
@@ -2366,7 +2366,7 @@
       <c r="X11" s="24" t="s">
         <v>30</v>
       </c>
-      <c r="Z11" s="58"/>
+      <c r="Z11" s="57"/>
       <c r="AA11" s="22" t="s">
         <v>26</v>
       </c>
@@ -2386,9 +2386,9 @@
         <v>30</v>
       </c>
     </row>
-    <row r="12" spans="1:34" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="58"/>
-      <c r="B12" s="59"/>
+    <row r="12" spans="1:34" ht="24.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A12" s="57"/>
+      <c r="B12" s="58"/>
       <c r="C12" s="45" t="s">
         <v>2</v>
       </c>
@@ -2401,7 +2401,7 @@
         <v>2</v>
       </c>
       <c r="H12" s="44"/>
-      <c r="J12" s="58"/>
+      <c r="J12" s="57"/>
       <c r="K12" s="22" t="s">
         <v>26</v>
       </c>
@@ -2420,7 +2420,7 @@
       <c r="P12" s="24" t="s">
         <v>30</v>
       </c>
-      <c r="R12" s="58"/>
+      <c r="R12" s="57"/>
       <c r="S12" s="22" t="s">
         <v>33</v>
       </c>
@@ -2439,7 +2439,7 @@
       <c r="X12" s="24" t="s">
         <v>29</v>
       </c>
-      <c r="Z12" s="58"/>
+      <c r="Z12" s="57"/>
       <c r="AA12" s="22" t="s">
         <v>28</v>
       </c>
@@ -2459,8 +2459,8 @@
         <v>29</v>
       </c>
     </row>
-    <row r="13" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="58"/>
+    <row r="13" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A13" s="57"/>
       <c r="B13" s="16"/>
       <c r="C13" s="48"/>
       <c r="D13" s="49"/>
@@ -2468,7 +2468,7 @@
       <c r="F13" s="49"/>
       <c r="G13" s="48"/>
       <c r="H13" s="50"/>
-      <c r="J13" s="58"/>
+      <c r="J13" s="57"/>
       <c r="K13" s="22" t="s">
         <v>28</v>
       </c>
@@ -2487,7 +2487,7 @@
       <c r="P13" s="24" t="s">
         <v>29</v>
       </c>
-      <c r="R13" s="58"/>
+      <c r="R13" s="57"/>
       <c r="S13" s="22" t="s">
         <v>36</v>
       </c>
@@ -2506,7 +2506,7 @@
       <c r="X13" s="24" t="s">
         <v>38</v>
       </c>
-      <c r="Z13" s="58"/>
+      <c r="Z13" s="57"/>
       <c r="AA13" s="22" t="s">
         <v>30</v>
       </c>
@@ -2526,9 +2526,9 @@
         <v>38</v>
       </c>
     </row>
-    <row r="14" spans="1:34" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="58"/>
-      <c r="B14" s="59" t="s">
+    <row r="14" spans="1:34" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A14" s="57"/>
+      <c r="B14" s="58" t="s">
         <v>40</v>
       </c>
       <c r="C14" s="33" t="s">
@@ -2543,7 +2543,7 @@
         <v>19</v>
       </c>
       <c r="H14" s="36"/>
-      <c r="J14" s="58"/>
+      <c r="J14" s="57"/>
       <c r="K14" s="22" t="s">
         <v>30</v>
       </c>
@@ -2562,7 +2562,7 @@
       <c r="P14" s="24" t="s">
         <v>38</v>
       </c>
-      <c r="R14" s="58"/>
+      <c r="R14" s="57"/>
       <c r="S14" s="22" t="s">
         <v>39</v>
       </c>
@@ -2579,7 +2579,7 @@
       <c r="X14" s="24" t="s">
         <v>33</v>
       </c>
-      <c r="Z14" s="58"/>
+      <c r="Z14" s="57"/>
       <c r="AA14" s="22" t="s">
         <v>38</v>
       </c>
@@ -2599,16 +2599,16 @@
         <v>33</v>
       </c>
     </row>
-    <row r="15" spans="1:34" ht="8.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="58"/>
-      <c r="B15" s="59"/>
+    <row r="15" spans="1:34" ht="8.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A15" s="57"/>
+      <c r="B15" s="58"/>
       <c r="C15" s="39"/>
       <c r="D15" s="42"/>
       <c r="E15" s="39"/>
       <c r="F15" s="42"/>
       <c r="G15" s="39"/>
       <c r="H15" s="42"/>
-      <c r="J15" s="58"/>
+      <c r="J15" s="57"/>
       <c r="K15" s="22" t="s">
         <v>38</v>
       </c>
@@ -2627,7 +2627,7 @@
       <c r="P15" s="24" t="s">
         <v>33</v>
       </c>
-      <c r="R15" s="58"/>
+      <c r="R15" s="57"/>
       <c r="S15" s="22" t="s">
         <v>42</v>
       </c>
@@ -2642,7 +2642,7 @@
       <c r="X15" s="24" t="s">
         <v>36</v>
       </c>
-      <c r="Z15" s="58"/>
+      <c r="Z15" s="57"/>
       <c r="AA15" s="22" t="s">
         <v>33</v>
       </c>
@@ -2662,9 +2662,9 @@
         <v>36</v>
       </c>
     </row>
-    <row r="16" spans="1:34" ht="23.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="58"/>
-      <c r="B16" s="59"/>
+    <row r="16" spans="1:34" ht="23.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A16" s="57"/>
+      <c r="B16" s="58"/>
       <c r="C16" s="45" t="s">
         <v>2</v>
       </c>
@@ -2677,7 +2677,7 @@
         <v>2</v>
       </c>
       <c r="H16" s="44"/>
-      <c r="J16" s="58"/>
+      <c r="J16" s="57"/>
       <c r="K16" s="22" t="s">
         <v>33</v>
       </c>
@@ -2696,7 +2696,7 @@
       <c r="P16" s="24" t="s">
         <v>36</v>
       </c>
-      <c r="R16" s="58"/>
+      <c r="R16" s="57"/>
       <c r="S16" s="22"/>
       <c r="T16" s="23" t="s">
         <v>36</v>
@@ -2707,7 +2707,7 @@
       <c r="X16" s="24" t="s">
         <v>41</v>
       </c>
-      <c r="Z16" s="58"/>
+      <c r="Z16" s="57"/>
       <c r="AA16" s="22" t="s">
         <v>37</v>
       </c>
@@ -2723,8 +2723,8 @@
         <v>41</v>
       </c>
     </row>
-    <row r="17" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="58"/>
+    <row r="17" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A17" s="57"/>
       <c r="B17" s="16"/>
       <c r="C17" s="48"/>
       <c r="D17" s="49"/>
@@ -2732,7 +2732,7 @@
       <c r="F17" s="49"/>
       <c r="G17" s="48"/>
       <c r="H17" s="50"/>
-      <c r="J17" s="58"/>
+      <c r="J17" s="57"/>
       <c r="K17" s="22" t="s">
         <v>37</v>
       </c>
@@ -2751,7 +2751,7 @@
       <c r="P17" s="24" t="s">
         <v>39</v>
       </c>
-      <c r="R17" s="58"/>
+      <c r="R17" s="57"/>
       <c r="S17" s="25"/>
       <c r="T17" s="26" t="s">
         <v>42</v>
@@ -2760,7 +2760,7 @@
       <c r="V17" s="26"/>
       <c r="W17" s="26"/>
       <c r="X17" s="27"/>
-      <c r="Z17" s="58"/>
+      <c r="Z17" s="57"/>
       <c r="AA17" s="22" t="s">
         <v>36</v>
       </c>
@@ -2774,9 +2774,9 @@
       <c r="AE17" s="23"/>
       <c r="AF17" s="24"/>
     </row>
-    <row r="18" spans="1:32" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="58"/>
-      <c r="B18" s="59" t="s">
+    <row r="18" spans="1:32" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A18" s="57"/>
+      <c r="B18" s="58" t="s">
         <v>43</v>
       </c>
       <c r="C18" s="33" t="s">
@@ -2791,7 +2791,7 @@
         <v>19</v>
       </c>
       <c r="H18" s="36"/>
-      <c r="J18" s="58"/>
+      <c r="J18" s="57"/>
       <c r="K18" s="22" t="s">
         <v>36</v>
       </c>
@@ -2815,7 +2815,7 @@
       <c r="V18" s="21"/>
       <c r="W18" s="21"/>
       <c r="X18" s="21"/>
-      <c r="Z18" s="58"/>
+      <c r="Z18" s="57"/>
       <c r="AA18" s="25" t="s">
         <v>39</v>
       </c>
@@ -2827,16 +2827,16 @@
       <c r="AE18" s="26"/>
       <c r="AF18" s="27"/>
     </row>
-    <row r="19" spans="1:32" ht="6.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="58"/>
-      <c r="B19" s="59"/>
+    <row r="19" spans="1:32" ht="6.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A19" s="57"/>
+      <c r="B19" s="58"/>
       <c r="C19" s="39"/>
       <c r="D19" s="42"/>
       <c r="E19" s="39"/>
       <c r="F19" s="42"/>
       <c r="G19" s="39"/>
       <c r="H19" s="42"/>
-      <c r="J19" s="58"/>
+      <c r="J19" s="57"/>
       <c r="K19" s="22" t="s">
         <v>39</v>
       </c>
@@ -2868,9 +2868,9 @@
       <c r="AE19" s="21"/>
       <c r="AF19" s="21"/>
     </row>
-    <row r="20" spans="1:32" ht="28.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A20" s="58"/>
-      <c r="B20" s="59"/>
+    <row r="20" spans="1:32" ht="28.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A20" s="57"/>
+      <c r="B20" s="58"/>
       <c r="C20" s="45" t="s">
         <v>2</v>
       </c>
@@ -2883,7 +2883,7 @@
         <v>2</v>
       </c>
       <c r="H20" s="47"/>
-      <c r="J20" s="58"/>
+      <c r="J20" s="57"/>
       <c r="K20" s="22" t="s">
         <v>42</v>
       </c>
@@ -2911,7 +2911,7 @@
       <c r="AE20" s="21"/>
       <c r="AF20" s="21"/>
     </row>
-    <row r="21" spans="1:32" s="16" customFormat="1" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:32" s="16" customFormat="1" ht="17.25" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A21" s="16" t="s">
         <v>27</v>
       </c>
@@ -2997,8 +2997,8 @@
         <v>12</v>
       </c>
     </row>
-    <row r="22" spans="1:32" ht="15.75" hidden="1" customHeight="1" thickTop="1" x14ac:dyDescent="0.3">
-      <c r="A22" s="58" t="s">
+    <row r="22" spans="1:32" ht="15.75" hidden="1" customHeight="1" thickTop="1" x14ac:dyDescent="0.35">
+      <c r="A22" s="57" t="s">
         <v>16</v>
       </c>
       <c r="B22" s="17"/>
@@ -3020,7 +3020,7 @@
       <c r="H22" s="20" t="s">
         <v>17</v>
       </c>
-      <c r="J22" s="58" t="s">
+      <c r="J22" s="57" t="s">
         <v>16</v>
       </c>
       <c r="K22" s="18" t="s">
@@ -3041,7 +3041,7 @@
       <c r="P22" s="20" t="s">
         <v>20</v>
       </c>
-      <c r="R22" s="58" t="s">
+      <c r="R22" s="57" t="s">
         <v>16</v>
       </c>
       <c r="S22" s="18" t="s">
@@ -3062,7 +3062,7 @@
       <c r="X22" s="20" t="s">
         <v>20</v>
       </c>
-      <c r="Z22" s="58" t="s">
+      <c r="Z22" s="57" t="s">
         <v>16</v>
       </c>
       <c r="AA22" s="29" t="s">
@@ -3074,8 +3074,8 @@
       <c r="AE22" s="21"/>
       <c r="AF22" s="21"/>
     </row>
-    <row r="23" spans="1:32" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A23" s="58"/>
+    <row r="23" spans="1:32" ht="17.25" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A23" s="57"/>
       <c r="B23" s="17"/>
       <c r="C23" s="22" t="s">
         <v>21</v>
@@ -3095,7 +3095,7 @@
       <c r="H23" s="24" t="s">
         <v>20</v>
       </c>
-      <c r="J23" s="58"/>
+      <c r="J23" s="57"/>
       <c r="K23" s="22" t="s">
         <v>20</v>
       </c>
@@ -3114,7 +3114,7 @@
       <c r="P23" s="24" t="s">
         <v>24</v>
       </c>
-      <c r="R23" s="58"/>
+      <c r="R23" s="57"/>
       <c r="S23" s="22" t="s">
         <v>22</v>
       </c>
@@ -3133,7 +3133,7 @@
       <c r="X23" s="24" t="s">
         <v>24</v>
       </c>
-      <c r="Z23" s="58"/>
+      <c r="Z23" s="57"/>
       <c r="AA23" s="30" t="s">
         <v>25</v>
       </c>
@@ -3143,8 +3143,8 @@
       <c r="AE23" s="21"/>
       <c r="AF23" s="21"/>
     </row>
-    <row r="24" spans="1:32" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A24" s="58"/>
+    <row r="24" spans="1:32" ht="17.25" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A24" s="57"/>
       <c r="B24" s="17"/>
       <c r="C24" s="22" t="s">
         <v>23</v>
@@ -3164,7 +3164,7 @@
       <c r="H24" s="24" t="s">
         <v>21</v>
       </c>
-      <c r="J24" s="58"/>
+      <c r="J24" s="57"/>
       <c r="K24" s="22" t="s">
         <v>23</v>
       </c>
@@ -3183,7 +3183,7 @@
       <c r="P24" s="24" t="s">
         <v>25</v>
       </c>
-      <c r="R24" s="58"/>
+      <c r="R24" s="57"/>
       <c r="S24" s="22" t="s">
         <v>23</v>
       </c>
@@ -3202,7 +3202,7 @@
       <c r="X24" s="24" t="s">
         <v>25</v>
       </c>
-      <c r="Z24" s="58"/>
+      <c r="Z24" s="57"/>
       <c r="AA24" s="30" t="s">
         <v>26</v>
       </c>
@@ -3212,8 +3212,8 @@
       <c r="AE24" s="21"/>
       <c r="AF24" s="21"/>
     </row>
-    <row r="25" spans="1:32" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A25" s="58"/>
+    <row r="25" spans="1:32" ht="17.25" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A25" s="57"/>
       <c r="B25" s="17"/>
       <c r="C25" s="22" t="s">
         <v>25</v>
@@ -3233,7 +3233,7 @@
       <c r="H25" s="24" t="s">
         <v>48</v>
       </c>
-      <c r="J25" s="58"/>
+      <c r="J25" s="57"/>
       <c r="K25" s="22" t="s">
         <v>24</v>
       </c>
@@ -3252,7 +3252,7 @@
       <c r="P25" s="24" t="s">
         <v>26</v>
       </c>
-      <c r="R25" s="58"/>
+      <c r="R25" s="57"/>
       <c r="S25" s="22" t="s">
         <v>25</v>
       </c>
@@ -3271,7 +3271,7 @@
       <c r="X25" s="24" t="s">
         <v>26</v>
       </c>
-      <c r="Z25" s="58"/>
+      <c r="Z25" s="57"/>
       <c r="AA25" s="30" t="s">
         <v>30</v>
       </c>
@@ -3281,8 +3281,8 @@
       <c r="AE25" s="21"/>
       <c r="AF25" s="21"/>
     </row>
-    <row r="26" spans="1:32" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A26" s="58"/>
+    <row r="26" spans="1:32" ht="17.25" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A26" s="57"/>
       <c r="B26" s="17"/>
       <c r="C26" s="22" t="s">
         <v>26</v>
@@ -3302,7 +3302,7 @@
       <c r="H26" s="24" t="s">
         <v>24</v>
       </c>
-      <c r="J26" s="58"/>
+      <c r="J26" s="57"/>
       <c r="K26" s="22" t="s">
         <v>25</v>
       </c>
@@ -3321,7 +3321,7 @@
       <c r="P26" s="24" t="s">
         <v>32</v>
       </c>
-      <c r="R26" s="58"/>
+      <c r="R26" s="57"/>
       <c r="S26" s="22" t="s">
         <v>26</v>
       </c>
@@ -3340,7 +3340,7 @@
       <c r="X26" s="24" t="s">
         <v>28</v>
       </c>
-      <c r="Z26" s="58"/>
+      <c r="Z26" s="57"/>
       <c r="AA26" s="30" t="s">
         <v>29</v>
       </c>
@@ -3350,8 +3350,8 @@
       <c r="AE26" s="21"/>
       <c r="AF26" s="21"/>
     </row>
-    <row r="27" spans="1:32" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A27" s="58"/>
+    <row r="27" spans="1:32" ht="17.25" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A27" s="57"/>
       <c r="B27" s="17"/>
       <c r="C27" s="22" t="s">
         <v>49</v>
@@ -3371,7 +3371,7 @@
       <c r="H27" s="24" t="s">
         <v>25</v>
       </c>
-      <c r="J27" s="58"/>
+      <c r="J27" s="57"/>
       <c r="K27" s="22" t="s">
         <v>26</v>
       </c>
@@ -3390,7 +3390,7 @@
       <c r="P27" s="24" t="s">
         <v>33</v>
       </c>
-      <c r="R27" s="58"/>
+      <c r="R27" s="57"/>
       <c r="S27" s="22" t="s">
         <v>32</v>
       </c>
@@ -3409,7 +3409,7 @@
       <c r="X27" s="24" t="s">
         <v>32</v>
       </c>
-      <c r="Z27" s="58"/>
+      <c r="Z27" s="57"/>
       <c r="AA27" s="30" t="s">
         <v>36</v>
       </c>
@@ -3419,8 +3419,8 @@
       <c r="AE27" s="21"/>
       <c r="AF27" s="21"/>
     </row>
-    <row r="28" spans="1:32" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A28" s="58"/>
+    <row r="28" spans="1:32" ht="17.25" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A28" s="57"/>
       <c r="B28" s="17"/>
       <c r="C28" s="22" t="s">
         <v>31</v>
@@ -3440,7 +3440,7 @@
       <c r="H28" s="24" t="s">
         <v>26</v>
       </c>
-      <c r="J28" s="58"/>
+      <c r="J28" s="57"/>
       <c r="K28" s="22" t="s">
         <v>32</v>
       </c>
@@ -3459,7 +3459,7 @@
       <c r="P28" s="24" t="s">
         <v>36</v>
       </c>
-      <c r="R28" s="58"/>
+      <c r="R28" s="57"/>
       <c r="S28" s="22" t="s">
         <v>31</v>
       </c>
@@ -3478,7 +3478,7 @@
       <c r="X28" s="24" t="s">
         <v>33</v>
       </c>
-      <c r="Z28" s="58"/>
+      <c r="Z28" s="57"/>
       <c r="AA28" s="31" t="s">
         <v>39</v>
       </c>
@@ -3488,8 +3488,8 @@
       <c r="AE28" s="21"/>
       <c r="AF28" s="21"/>
     </row>
-    <row r="29" spans="1:32" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A29" s="58"/>
+    <row r="29" spans="1:32" ht="17.25" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A29" s="57"/>
       <c r="B29" s="17"/>
       <c r="C29" s="22" t="s">
         <v>30</v>
@@ -3509,7 +3509,7 @@
       <c r="H29" s="24" t="s">
         <v>28</v>
       </c>
-      <c r="J29" s="58"/>
+      <c r="J29" s="57"/>
       <c r="K29" s="22" t="s">
         <v>31</v>
       </c>
@@ -3528,7 +3528,7 @@
       <c r="P29" s="24" t="s">
         <v>39</v>
       </c>
-      <c r="R29" s="58"/>
+      <c r="R29" s="57"/>
       <c r="S29" s="22" t="s">
         <v>30</v>
       </c>
@@ -3555,8 +3555,8 @@
       <c r="AE29" s="21"/>
       <c r="AF29" s="21"/>
     </row>
-    <row r="30" spans="1:32" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A30" s="58"/>
+    <row r="30" spans="1:32" ht="17.25" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A30" s="57"/>
       <c r="B30" s="17"/>
       <c r="C30" s="22" t="s">
         <v>33</v>
@@ -3576,7 +3576,7 @@
       <c r="H30" s="24" t="s">
         <v>32</v>
       </c>
-      <c r="J30" s="58"/>
+      <c r="J30" s="57"/>
       <c r="K30" s="22" t="s">
         <v>30</v>
       </c>
@@ -3591,7 +3591,7 @@
         <v>37</v>
       </c>
       <c r="P30" s="24"/>
-      <c r="R30" s="58"/>
+      <c r="R30" s="57"/>
       <c r="S30" s="22" t="s">
         <v>33</v>
       </c>
@@ -3612,8 +3612,8 @@
       <c r="AE30" s="21"/>
       <c r="AF30" s="21"/>
     </row>
-    <row r="31" spans="1:32" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A31" s="58"/>
+    <row r="31" spans="1:32" ht="17.25" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A31" s="57"/>
       <c r="B31" s="17"/>
       <c r="C31" s="22" t="s">
         <v>37</v>
@@ -3633,7 +3633,7 @@
       <c r="H31" s="24" t="s">
         <v>29</v>
       </c>
-      <c r="J31" s="58"/>
+      <c r="J31" s="57"/>
       <c r="K31" s="22" t="s">
         <v>33</v>
       </c>
@@ -3648,7 +3648,7 @@
         <v>36</v>
       </c>
       <c r="P31" s="24"/>
-      <c r="R31" s="58"/>
+      <c r="R31" s="57"/>
       <c r="S31" s="22" t="s">
         <v>36</v>
       </c>
@@ -3667,8 +3667,8 @@
       <c r="AE31" s="21"/>
       <c r="AF31" s="21"/>
     </row>
-    <row r="32" spans="1:32" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A32" s="58"/>
+    <row r="32" spans="1:32" ht="17.25" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A32" s="57"/>
       <c r="B32" s="17"/>
       <c r="C32" s="22" t="s">
         <v>36</v>
@@ -3688,7 +3688,7 @@
       <c r="H32" s="24" t="s">
         <v>33</v>
       </c>
-      <c r="J32" s="58"/>
+      <c r="J32" s="57"/>
       <c r="K32" s="22" t="s">
         <v>37</v>
       </c>
@@ -3699,7 +3699,7 @@
       <c r="N32" s="23"/>
       <c r="O32" s="23"/>
       <c r="P32" s="24"/>
-      <c r="R32" s="58"/>
+      <c r="R32" s="57"/>
       <c r="S32" s="22" t="s">
         <v>39</v>
       </c>
@@ -3716,8 +3716,8 @@
       <c r="AE32" s="21"/>
       <c r="AF32" s="21"/>
     </row>
-    <row r="33" spans="1:32" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A33" s="58"/>
+    <row r="33" spans="1:32" ht="17.25" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A33" s="57"/>
       <c r="B33" s="17"/>
       <c r="C33" s="22" t="s">
         <v>39</v>
@@ -3737,7 +3737,7 @@
       <c r="H33" s="24" t="s">
         <v>37</v>
       </c>
-      <c r="J33" s="58"/>
+      <c r="J33" s="57"/>
       <c r="K33" s="22" t="s">
         <v>36</v>
       </c>
@@ -3748,7 +3748,7 @@
       <c r="N33" s="23"/>
       <c r="O33" s="23"/>
       <c r="P33" s="24"/>
-      <c r="R33" s="58"/>
+      <c r="R33" s="57"/>
       <c r="S33" s="25" t="s">
         <v>42</v>
       </c>
@@ -3765,8 +3765,8 @@
       <c r="AE33" s="21"/>
       <c r="AF33" s="21"/>
     </row>
-    <row r="34" spans="1:32" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A34" s="58"/>
+    <row r="34" spans="1:32" ht="17.25" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A34" s="57"/>
       <c r="B34" s="17"/>
       <c r="C34" s="22"/>
       <c r="D34" s="23" t="s">
@@ -3784,7 +3784,7 @@
       <c r="H34" s="24" t="s">
         <v>36</v>
       </c>
-      <c r="J34" s="58"/>
+      <c r="J34" s="57"/>
       <c r="K34" s="25" t="s">
         <v>39</v>
       </c>
@@ -3808,8 +3808,8 @@
       <c r="AE34" s="21"/>
       <c r="AF34" s="21"/>
     </row>
-    <row r="35" spans="1:32" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A35" s="58"/>
+    <row r="35" spans="1:32" ht="17.25" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A35" s="57"/>
       <c r="B35" s="17"/>
       <c r="C35" s="22"/>
       <c r="D35" s="23" t="s">
@@ -3847,8 +3847,8 @@
       <c r="AE35" s="21"/>
       <c r="AF35" s="21"/>
     </row>
-    <row r="36" spans="1:32" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A36" s="58"/>
+    <row r="36" spans="1:32" ht="17.25" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A36" s="57"/>
       <c r="B36" s="17"/>
       <c r="C36" s="22"/>
       <c r="D36" s="23"/>
@@ -3884,8 +3884,8 @@
       <c r="AE36" s="21"/>
       <c r="AF36" s="21"/>
     </row>
-    <row r="37" spans="1:32" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A37" s="58"/>
+    <row r="37" spans="1:32" ht="17.25" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A37" s="57"/>
       <c r="B37" s="17"/>
       <c r="C37" s="25"/>
       <c r="D37" s="26"/>
@@ -3917,7 +3917,7 @@
       <c r="AE37" s="21"/>
       <c r="AF37" s="21"/>
     </row>
-    <row r="38" spans="1:32" hidden="1" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:32" ht="17.25" hidden="1" x14ac:dyDescent="0.35">
       <c r="C38" s="21"/>
       <c r="D38" s="21"/>
       <c r="E38" s="21"/>
@@ -3943,7 +3943,7 @@
       <c r="AE38" s="21"/>
       <c r="AF38" s="21"/>
     </row>
-    <row r="39" spans="1:32" s="16" customFormat="1" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:32" s="16" customFormat="1" ht="17.25" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A39" s="16" t="s">
         <v>40</v>
       </c>
@@ -4008,8 +4008,8 @@
         <v>12</v>
       </c>
     </row>
-    <row r="40" spans="1:32" ht="15.75" hidden="1" customHeight="1" thickTop="1" x14ac:dyDescent="0.3">
-      <c r="A40" s="58" t="s">
+    <row r="40" spans="1:32" ht="15.75" hidden="1" customHeight="1" thickTop="1" x14ac:dyDescent="0.35">
+      <c r="A40" s="57" t="s">
         <v>16</v>
       </c>
       <c r="B40" s="17"/>
@@ -4031,7 +4031,7 @@
       <c r="H40" s="20" t="s">
         <v>17</v>
       </c>
-      <c r="J40" s="58" t="s">
+      <c r="J40" s="57" t="s">
         <v>16</v>
       </c>
       <c r="K40" s="18" t="s">
@@ -4052,7 +4052,7 @@
       <c r="P40" s="20" t="s">
         <v>20</v>
       </c>
-      <c r="R40" s="58" t="s">
+      <c r="R40" s="57" t="s">
         <v>16</v>
       </c>
       <c r="S40" s="18" t="s">
@@ -4075,8 +4075,8 @@
       </c>
       <c r="Z40" s="32"/>
     </row>
-    <row r="41" spans="1:32" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A41" s="58"/>
+    <row r="41" spans="1:32" ht="17.25" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A41" s="57"/>
       <c r="B41" s="17"/>
       <c r="C41" s="22" t="s">
         <v>20</v>
@@ -4096,7 +4096,7 @@
       <c r="H41" s="24" t="s">
         <v>20</v>
       </c>
-      <c r="J41" s="58"/>
+      <c r="J41" s="57"/>
       <c r="K41" s="22" t="s">
         <v>20</v>
       </c>
@@ -4115,7 +4115,7 @@
       <c r="P41" s="24" t="s">
         <v>22</v>
       </c>
-      <c r="R41" s="58"/>
+      <c r="R41" s="57"/>
       <c r="S41" s="22" t="s">
         <v>20</v>
       </c>
@@ -4136,8 +4136,8 @@
       </c>
       <c r="Z41" s="32"/>
     </row>
-    <row r="42" spans="1:32" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A42" s="58"/>
+    <row r="42" spans="1:32" ht="17.25" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A42" s="57"/>
       <c r="B42" s="17"/>
       <c r="C42" s="22" t="s">
         <v>21</v>
@@ -4157,7 +4157,7 @@
       <c r="H42" s="24" t="s">
         <v>22</v>
       </c>
-      <c r="J42" s="58"/>
+      <c r="J42" s="57"/>
       <c r="K42" s="22" t="s">
         <v>21</v>
       </c>
@@ -4176,7 +4176,7 @@
       <c r="P42" s="24" t="s">
         <v>25</v>
       </c>
-      <c r="R42" s="58"/>
+      <c r="R42" s="57"/>
       <c r="S42" s="22" t="s">
         <v>22</v>
       </c>
@@ -4197,8 +4197,8 @@
       </c>
       <c r="Z42" s="32"/>
     </row>
-    <row r="43" spans="1:32" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A43" s="58"/>
+    <row r="43" spans="1:32" ht="17.25" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A43" s="57"/>
       <c r="B43" s="17"/>
       <c r="C43" s="22" t="s">
         <v>23</v>
@@ -4218,7 +4218,7 @@
       <c r="H43" s="24" t="s">
         <v>48</v>
       </c>
-      <c r="J43" s="58"/>
+      <c r="J43" s="57"/>
       <c r="K43" s="22" t="s">
         <v>23</v>
       </c>
@@ -4237,7 +4237,7 @@
       <c r="P43" s="24" t="s">
         <v>26</v>
       </c>
-      <c r="R43" s="58"/>
+      <c r="R43" s="57"/>
       <c r="S43" s="22" t="s">
         <v>21</v>
       </c>
@@ -4258,8 +4258,8 @@
       </c>
       <c r="Z43" s="32"/>
     </row>
-    <row r="44" spans="1:32" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A44" s="58"/>
+    <row r="44" spans="1:32" ht="17.25" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A44" s="57"/>
       <c r="B44" s="17"/>
       <c r="C44" s="22" t="s">
         <v>48</v>
@@ -4279,7 +4279,7 @@
       <c r="H44" s="24" t="s">
         <v>24</v>
       </c>
-      <c r="J44" s="58"/>
+      <c r="J44" s="57"/>
       <c r="K44" s="22" t="s">
         <v>25</v>
       </c>
@@ -4298,7 +4298,7 @@
       <c r="P44" s="24" t="s">
         <v>38</v>
       </c>
-      <c r="R44" s="58"/>
+      <c r="R44" s="57"/>
       <c r="S44" s="22" t="s">
         <v>23</v>
       </c>
@@ -4319,8 +4319,8 @@
       </c>
       <c r="Z44" s="32"/>
     </row>
-    <row r="45" spans="1:32" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A45" s="58"/>
+    <row r="45" spans="1:32" ht="17.25" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A45" s="57"/>
       <c r="B45" s="17"/>
       <c r="C45" s="22" t="s">
         <v>24</v>
@@ -4340,7 +4340,7 @@
       <c r="H45" s="24" t="s">
         <v>25</v>
       </c>
-      <c r="J45" s="58"/>
+      <c r="J45" s="57"/>
       <c r="K45" s="22" t="s">
         <v>26</v>
       </c>
@@ -4359,7 +4359,7 @@
       <c r="P45" s="24" t="s">
         <v>33</v>
       </c>
-      <c r="R45" s="58"/>
+      <c r="R45" s="57"/>
       <c r="S45" s="22" t="s">
         <v>24</v>
       </c>
@@ -4380,8 +4380,8 @@
       </c>
       <c r="Z45" s="32"/>
     </row>
-    <row r="46" spans="1:32" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A46" s="58"/>
+    <row r="46" spans="1:32" ht="17.25" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A46" s="57"/>
       <c r="B46" s="17"/>
       <c r="C46" s="22" t="s">
         <v>25</v>
@@ -4401,7 +4401,7 @@
       <c r="H46" s="24" t="s">
         <v>26</v>
       </c>
-      <c r="J46" s="58"/>
+      <c r="J46" s="57"/>
       <c r="K46" s="22" t="s">
         <v>33</v>
       </c>
@@ -4420,7 +4420,7 @@
       <c r="P46" s="24" t="s">
         <v>36</v>
       </c>
-      <c r="R46" s="58"/>
+      <c r="R46" s="57"/>
       <c r="S46" s="22" t="s">
         <v>25</v>
       </c>
@@ -4441,8 +4441,8 @@
       </c>
       <c r="Z46" s="32"/>
     </row>
-    <row r="47" spans="1:32" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A47" s="58"/>
+    <row r="47" spans="1:32" ht="17.25" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A47" s="57"/>
       <c r="B47" s="17"/>
       <c r="C47" s="22" t="s">
         <v>26</v>
@@ -4462,7 +4462,7 @@
       <c r="H47" s="24" t="s">
         <v>28</v>
       </c>
-      <c r="J47" s="58"/>
+      <c r="J47" s="57"/>
       <c r="K47" s="22" t="s">
         <v>36</v>
       </c>
@@ -4477,7 +4477,7 @@
         <v>33</v>
       </c>
       <c r="P47" s="24"/>
-      <c r="R47" s="58"/>
+      <c r="R47" s="57"/>
       <c r="S47" s="22" t="s">
         <v>26</v>
       </c>
@@ -4498,8 +4498,8 @@
       </c>
       <c r="Z47" s="32"/>
     </row>
-    <row r="48" spans="1:32" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A48" s="58"/>
+    <row r="48" spans="1:32" ht="17.25" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A48" s="57"/>
       <c r="B48" s="17"/>
       <c r="C48" s="22" t="s">
         <v>28</v>
@@ -4519,7 +4519,7 @@
       <c r="H48" s="24" t="s">
         <v>32</v>
       </c>
-      <c r="J48" s="58"/>
+      <c r="J48" s="57"/>
       <c r="K48" s="22" t="s">
         <v>39</v>
       </c>
@@ -4530,7 +4530,7 @@
         <v>37</v>
       </c>
       <c r="P48" s="24"/>
-      <c r="R48" s="58"/>
+      <c r="R48" s="57"/>
       <c r="S48" s="22" t="s">
         <v>28</v>
       </c>
@@ -4549,8 +4549,8 @@
       </c>
       <c r="Z48" s="32"/>
     </row>
-    <row r="49" spans="1:26" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A49" s="58"/>
+    <row r="49" spans="1:26" ht="17.25" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A49" s="57"/>
       <c r="B49" s="17"/>
       <c r="C49" s="22" t="s">
         <v>31</v>
@@ -4570,7 +4570,7 @@
       <c r="H49" s="24" t="s">
         <v>38</v>
       </c>
-      <c r="J49" s="58"/>
+      <c r="J49" s="57"/>
       <c r="K49" s="22"/>
       <c r="L49" s="23"/>
       <c r="M49" s="23"/>
@@ -4579,7 +4579,7 @@
         <v>36</v>
       </c>
       <c r="P49" s="24"/>
-      <c r="R49" s="58"/>
+      <c r="R49" s="57"/>
       <c r="S49" s="22" t="s">
         <v>30</v>
       </c>
@@ -4596,8 +4596,8 @@
       </c>
       <c r="Z49" s="32"/>
     </row>
-    <row r="50" spans="1:26" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A50" s="58"/>
+    <row r="50" spans="1:26" ht="17.25" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A50" s="57"/>
       <c r="B50" s="17"/>
       <c r="C50" s="22" t="s">
         <v>29</v>
@@ -4617,7 +4617,7 @@
       <c r="H50" s="24" t="s">
         <v>33</v>
       </c>
-      <c r="J50" s="58"/>
+      <c r="J50" s="57"/>
       <c r="K50" s="25"/>
       <c r="L50" s="26"/>
       <c r="M50" s="26"/>
@@ -4626,7 +4626,7 @@
         <v>42</v>
       </c>
       <c r="P50" s="27"/>
-      <c r="R50" s="58"/>
+      <c r="R50" s="57"/>
       <c r="S50" s="22" t="s">
         <v>33</v>
       </c>
@@ -4641,8 +4641,8 @@
       </c>
       <c r="Z50" s="32"/>
     </row>
-    <row r="51" spans="1:26" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A51" s="58"/>
+    <row r="51" spans="1:26" ht="17.25" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A51" s="57"/>
       <c r="B51" s="17"/>
       <c r="C51" s="22" t="s">
         <v>38</v>
@@ -4669,7 +4669,7 @@
       <c r="N51" s="21"/>
       <c r="O51" s="21"/>
       <c r="P51" s="21"/>
-      <c r="R51" s="58"/>
+      <c r="R51" s="57"/>
       <c r="S51" s="22" t="s">
         <v>36</v>
       </c>
@@ -4683,8 +4683,8 @@
         <v>36</v>
       </c>
     </row>
-    <row r="52" spans="1:26" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A52" s="58"/>
+    <row r="52" spans="1:26" ht="17.25" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A52" s="57"/>
       <c r="B52" s="17"/>
       <c r="C52" s="22" t="s">
         <v>33</v>
@@ -4711,7 +4711,7 @@
       <c r="N52" s="21"/>
       <c r="O52" s="21"/>
       <c r="P52" s="21"/>
-      <c r="R52" s="58"/>
+      <c r="R52" s="57"/>
       <c r="S52" s="25" t="s">
         <v>39</v>
       </c>
@@ -4723,8 +4723,8 @@
       <c r="W52" s="26"/>
       <c r="X52" s="27"/>
     </row>
-    <row r="53" spans="1:26" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A53" s="58"/>
+    <row r="53" spans="1:26" ht="17.25" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A53" s="57"/>
       <c r="B53" s="17"/>
       <c r="C53" s="22" t="s">
         <v>36</v>
@@ -4755,8 +4755,8 @@
       <c r="W53" s="21"/>
       <c r="X53" s="21"/>
     </row>
-    <row r="54" spans="1:26" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A54" s="58"/>
+    <row r="54" spans="1:26" ht="17.25" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A54" s="57"/>
       <c r="B54" s="17"/>
       <c r="C54" s="22" t="s">
         <v>39</v>
@@ -4785,8 +4785,8 @@
       <c r="W54" s="21"/>
       <c r="X54" s="21"/>
     </row>
-    <row r="55" spans="1:26" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A55" s="58"/>
+    <row r="55" spans="1:26" ht="17.25" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A55" s="57"/>
       <c r="B55" s="17"/>
       <c r="C55" s="25" t="s">
         <v>42</v>
@@ -4811,7 +4811,7 @@
       <c r="W55" s="21"/>
       <c r="X55" s="21"/>
     </row>
-    <row r="56" spans="1:26" hidden="1" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:26" ht="17.25" hidden="1" x14ac:dyDescent="0.35">
       <c r="C56" s="21"/>
       <c r="D56" s="21"/>
       <c r="E56" s="21"/>
@@ -4831,7 +4831,7 @@
       <c r="W56" s="21"/>
       <c r="X56" s="21"/>
     </row>
-    <row r="57" spans="1:26" s="16" customFormat="1" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="57" spans="1:26" s="16" customFormat="1" ht="17.25" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A57" s="16" t="s">
         <v>43</v>
       </c>
@@ -4896,8 +4896,8 @@
         <v>12</v>
       </c>
     </row>
-    <row r="58" spans="1:26" ht="15" hidden="1" customHeight="1" thickTop="1" x14ac:dyDescent="0.3">
-      <c r="A58" s="58" t="s">
+    <row r="58" spans="1:26" ht="15" hidden="1" customHeight="1" thickTop="1" x14ac:dyDescent="0.35">
+      <c r="A58" s="57" t="s">
         <v>16</v>
       </c>
       <c r="B58" s="17"/>
@@ -4919,7 +4919,7 @@
       <c r="H58" s="20" t="s">
         <v>17</v>
       </c>
-      <c r="J58" s="58" t="s">
+      <c r="J58" s="57" t="s">
         <v>16</v>
       </c>
       <c r="K58" s="18" t="s">
@@ -4940,7 +4940,7 @@
       <c r="P58" s="20" t="s">
         <v>20</v>
       </c>
-      <c r="R58" s="58" t="s">
+      <c r="R58" s="57" t="s">
         <v>16</v>
       </c>
       <c r="S58" s="18" t="s">
@@ -4963,8 +4963,8 @@
       </c>
       <c r="Z58" s="28"/>
     </row>
-    <row r="59" spans="1:26" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A59" s="58"/>
+    <row r="59" spans="1:26" ht="17.25" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A59" s="57"/>
       <c r="B59" s="17"/>
       <c r="C59" s="22" t="s">
         <v>23</v>
@@ -4984,7 +4984,7 @@
       <c r="H59" s="24" t="s">
         <v>20</v>
       </c>
-      <c r="J59" s="58"/>
+      <c r="J59" s="57"/>
       <c r="K59" s="22" t="s">
         <v>23</v>
       </c>
@@ -5003,7 +5003,7 @@
       <c r="P59" s="24" t="s">
         <v>24</v>
       </c>
-      <c r="R59" s="58"/>
+      <c r="R59" s="57"/>
       <c r="S59" s="22" t="s">
         <v>25</v>
       </c>
@@ -5024,8 +5024,8 @@
       </c>
       <c r="Z59" s="28"/>
     </row>
-    <row r="60" spans="1:26" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A60" s="58"/>
+    <row r="60" spans="1:26" ht="17.25" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A60" s="57"/>
       <c r="B60" s="17"/>
       <c r="C60" s="22" t="s">
         <v>24</v>
@@ -5045,7 +5045,7 @@
       <c r="H60" s="24" t="s">
         <v>21</v>
       </c>
-      <c r="J60" s="58"/>
+      <c r="J60" s="57"/>
       <c r="K60" s="22" t="s">
         <v>25</v>
       </c>
@@ -5064,7 +5064,7 @@
       <c r="P60" s="24" t="s">
         <v>25</v>
       </c>
-      <c r="R60" s="58"/>
+      <c r="R60" s="57"/>
       <c r="S60" s="22" t="s">
         <v>26</v>
       </c>
@@ -5085,8 +5085,8 @@
       </c>
       <c r="Z60" s="28"/>
     </row>
-    <row r="61" spans="1:26" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A61" s="58"/>
+    <row r="61" spans="1:26" ht="17.25" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A61" s="57"/>
       <c r="B61" s="17"/>
       <c r="C61" s="22" t="s">
         <v>25</v>
@@ -5106,7 +5106,7 @@
       <c r="H61" s="24" t="s">
         <v>24</v>
       </c>
-      <c r="J61" s="58"/>
+      <c r="J61" s="57"/>
       <c r="K61" s="22" t="s">
         <v>26</v>
       </c>
@@ -5125,7 +5125,7 @@
       <c r="P61" s="24" t="s">
         <v>26</v>
       </c>
-      <c r="R61" s="58"/>
+      <c r="R61" s="57"/>
       <c r="S61" s="22" t="s">
         <v>32</v>
       </c>
@@ -5146,8 +5146,8 @@
       </c>
       <c r="Z61" s="28"/>
     </row>
-    <row r="62" spans="1:26" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A62" s="58"/>
+    <row r="62" spans="1:26" ht="17.25" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A62" s="57"/>
       <c r="B62" s="17"/>
       <c r="C62" s="22" t="s">
         <v>26</v>
@@ -5167,7 +5167,7 @@
       <c r="H62" s="24" t="s">
         <v>25</v>
       </c>
-      <c r="J62" s="58"/>
+      <c r="J62" s="57"/>
       <c r="K62" s="22" t="s">
         <v>32</v>
       </c>
@@ -5186,7 +5186,7 @@
       <c r="P62" s="24" t="s">
         <v>32</v>
       </c>
-      <c r="R62" s="58"/>
+      <c r="R62" s="57"/>
       <c r="S62" s="22" t="s">
         <v>38</v>
       </c>
@@ -5207,8 +5207,8 @@
       </c>
       <c r="Z62" s="28"/>
     </row>
-    <row r="63" spans="1:26" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A63" s="58"/>
+    <row r="63" spans="1:26" ht="17.25" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A63" s="57"/>
       <c r="B63" s="17"/>
       <c r="C63" s="22" t="s">
         <v>32</v>
@@ -5228,7 +5228,7 @@
       <c r="H63" s="24" t="s">
         <v>26</v>
       </c>
-      <c r="J63" s="58"/>
+      <c r="J63" s="57"/>
       <c r="K63" s="22" t="s">
         <v>38</v>
       </c>
@@ -5247,7 +5247,7 @@
       <c r="P63" s="24" t="s">
         <v>37</v>
       </c>
-      <c r="R63" s="58"/>
+      <c r="R63" s="57"/>
       <c r="S63" s="22" t="s">
         <v>33</v>
       </c>
@@ -5268,8 +5268,8 @@
       </c>
       <c r="Z63" s="28"/>
     </row>
-    <row r="64" spans="1:26" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A64" s="58"/>
+    <row r="64" spans="1:26" ht="17.25" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A64" s="57"/>
       <c r="B64" s="17"/>
       <c r="C64" s="22" t="s">
         <v>30</v>
@@ -5289,7 +5289,7 @@
       <c r="H64" s="24" t="s">
         <v>32</v>
       </c>
-      <c r="J64" s="58"/>
+      <c r="J64" s="57"/>
       <c r="K64" s="22" t="s">
         <v>33</v>
       </c>
@@ -5308,7 +5308,7 @@
       <c r="P64" s="24" t="s">
         <v>36</v>
       </c>
-      <c r="R64" s="58"/>
+      <c r="R64" s="57"/>
       <c r="S64" s="22" t="s">
         <v>36</v>
       </c>
@@ -5327,8 +5327,8 @@
       </c>
       <c r="Z64" s="28"/>
     </row>
-    <row r="65" spans="1:26" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A65" s="58"/>
+    <row r="65" spans="1:26" ht="17.25" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A65" s="57"/>
       <c r="B65" s="17"/>
       <c r="C65" s="22" t="s">
         <v>38</v>
@@ -5348,7 +5348,7 @@
       <c r="H65" s="24" t="s">
         <v>30</v>
       </c>
-      <c r="J65" s="58"/>
+      <c r="J65" s="57"/>
       <c r="K65" s="22" t="s">
         <v>36</v>
       </c>
@@ -5361,7 +5361,7 @@
       <c r="N65" s="23"/>
       <c r="O65" s="23"/>
       <c r="P65" s="24"/>
-      <c r="R65" s="58"/>
+      <c r="R65" s="57"/>
       <c r="S65" s="22"/>
       <c r="T65" s="23" t="s">
         <v>36</v>
@@ -5376,8 +5376,8 @@
       </c>
       <c r="Z65" s="28"/>
     </row>
-    <row r="66" spans="1:26" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A66" s="58"/>
+    <row r="66" spans="1:26" ht="17.25" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A66" s="57"/>
       <c r="B66" s="17"/>
       <c r="C66" s="22" t="s">
         <v>33</v>
@@ -5397,7 +5397,7 @@
       <c r="H66" s="24" t="s">
         <v>29</v>
       </c>
-      <c r="J66" s="58"/>
+      <c r="J66" s="57"/>
       <c r="K66" s="22"/>
       <c r="L66" s="23"/>
       <c r="M66" s="23" t="s">
@@ -5406,7 +5406,7 @@
       <c r="N66" s="23"/>
       <c r="O66" s="23"/>
       <c r="P66" s="24"/>
-      <c r="R66" s="58"/>
+      <c r="R66" s="57"/>
       <c r="S66" s="22"/>
       <c r="T66" s="23" t="s">
         <v>39</v>
@@ -5421,8 +5421,8 @@
       </c>
       <c r="Z66" s="28"/>
     </row>
-    <row r="67" spans="1:26" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A67" s="58"/>
+    <row r="67" spans="1:26" ht="17.25" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A67" s="57"/>
       <c r="B67" s="17"/>
       <c r="C67" s="22" t="s">
         <v>36</v>
@@ -5442,7 +5442,7 @@
       <c r="H67" s="24" t="s">
         <v>33</v>
       </c>
-      <c r="J67" s="58"/>
+      <c r="J67" s="57"/>
       <c r="K67" s="25"/>
       <c r="L67" s="26"/>
       <c r="M67" s="26" t="s">
@@ -5451,7 +5451,7 @@
       <c r="N67" s="26"/>
       <c r="O67" s="26"/>
       <c r="P67" s="27"/>
-      <c r="R67" s="58"/>
+      <c r="R67" s="57"/>
       <c r="S67" s="25"/>
       <c r="T67" s="26"/>
       <c r="U67" s="26" t="s">
@@ -5464,8 +5464,8 @@
       </c>
       <c r="Z67" s="28"/>
     </row>
-    <row r="68" spans="1:26" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A68" s="58"/>
+    <row r="68" spans="1:26" ht="17.25" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A68" s="57"/>
       <c r="B68" s="17"/>
       <c r="C68" s="22" t="s">
         <v>39</v>
@@ -5501,8 +5501,8 @@
       <c r="X68" s="21"/>
       <c r="Z68" s="28"/>
     </row>
-    <row r="69" spans="1:26" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A69" s="58"/>
+    <row r="69" spans="1:26" ht="17.25" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A69" s="57"/>
       <c r="B69" s="17"/>
       <c r="C69" s="22"/>
       <c r="D69" s="23"/>
@@ -5533,8 +5533,8 @@
       <c r="W69" s="21"/>
       <c r="X69" s="21"/>
     </row>
-    <row r="70" spans="1:26" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A70" s="58"/>
+    <row r="70" spans="1:26" ht="17.25" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A70" s="57"/>
       <c r="B70" s="17"/>
       <c r="C70" s="22"/>
       <c r="D70" s="23"/>
@@ -5561,8 +5561,8 @@
       <c r="W70" s="21"/>
       <c r="X70" s="21"/>
     </row>
-    <row r="71" spans="1:26" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A71" s="58"/>
+    <row r="71" spans="1:26" ht="17.25" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A71" s="57"/>
       <c r="B71" s="17"/>
       <c r="C71" s="25"/>
       <c r="D71" s="26"/>
@@ -5587,7 +5587,7 @@
       <c r="W71" s="21"/>
       <c r="X71" s="21"/>
     </row>
-    <row r="72" spans="1:26" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:26" ht="17.25" x14ac:dyDescent="0.35">
       <c r="A72" s="17"/>
       <c r="B72" s="17"/>
       <c r="C72" s="21"/>
@@ -5611,7 +5611,7 @@
       <c r="W72" s="21"/>
       <c r="X72" s="21"/>
     </row>
-    <row r="73" spans="1:26" ht="18" x14ac:dyDescent="0.35">
+    <row r="73" spans="1:26" ht="19.5" x14ac:dyDescent="0.35">
       <c r="B73" s="34"/>
       <c r="C73" s="21" t="s">
         <v>55</v>
@@ -5634,7 +5634,7 @@
       <c r="W73" s="21"/>
       <c r="X73" s="21"/>
     </row>
-    <row r="74" spans="1:26" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:26" ht="17.25" x14ac:dyDescent="0.35">
       <c r="C74" s="21"/>
       <c r="D74" s="21"/>
       <c r="E74" s="21"/>
@@ -5656,6 +5656,20 @@
     </row>
   </sheetData>
   <mergeCells count="23">
+    <mergeCell ref="K2:P2"/>
+    <mergeCell ref="A5:A20"/>
+    <mergeCell ref="S2:X2"/>
+    <mergeCell ref="AA2:AF2"/>
+    <mergeCell ref="B10:B12"/>
+    <mergeCell ref="A2:B4"/>
+    <mergeCell ref="C2:H2"/>
+    <mergeCell ref="Z22:Z28"/>
+    <mergeCell ref="Z5:Z18"/>
+    <mergeCell ref="J5:J20"/>
+    <mergeCell ref="R5:R17"/>
+    <mergeCell ref="B6:B8"/>
+    <mergeCell ref="B18:B20"/>
+    <mergeCell ref="B14:B16"/>
     <mergeCell ref="A58:A71"/>
     <mergeCell ref="J58:J67"/>
     <mergeCell ref="R58:R67"/>
@@ -5665,20 +5679,6 @@
     <mergeCell ref="A40:A55"/>
     <mergeCell ref="J40:J50"/>
     <mergeCell ref="R40:R52"/>
-    <mergeCell ref="Z22:Z28"/>
-    <mergeCell ref="Z5:Z18"/>
-    <mergeCell ref="J5:J20"/>
-    <mergeCell ref="R5:R17"/>
-    <mergeCell ref="B6:B8"/>
-    <mergeCell ref="B18:B20"/>
-    <mergeCell ref="B14:B16"/>
-    <mergeCell ref="K2:P2"/>
-    <mergeCell ref="A5:A20"/>
-    <mergeCell ref="S2:X2"/>
-    <mergeCell ref="AA2:AF2"/>
-    <mergeCell ref="B10:B12"/>
-    <mergeCell ref="A2:B4"/>
-    <mergeCell ref="C2:H2"/>
   </mergeCells>
   <pageMargins left="0.39370078740157483" right="0.39370078740157483" top="0.47244094488188981" bottom="0.39370078740157483" header="0.31496062992125984" footer="0.31496062992125984"/>
   <pageSetup scale="142" orientation="landscape" r:id="rId1"/>
@@ -5692,16 +5692,16 @@
     <pageSetUpPr autoPageBreaks="0" fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:H168"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.77734375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.75" defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="2" customWidth="1"/>
-    <col min="2" max="2" width="18.21875" customWidth="1"/>
-    <col min="3" max="8" width="17.6640625" customWidth="1"/>
-    <col min="9" max="9" width="2.44140625" customWidth="1"/>
-    <col min="14" max="14" width="6.77734375" customWidth="1"/>
+    <col min="2" max="2" width="18.25" customWidth="1"/>
+    <col min="3" max="8" width="17.625" customWidth="1"/>
+    <col min="9" max="9" width="2.5" customWidth="1"/>
+    <col min="14" max="14" width="6.75" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="54" customHeight="1" x14ac:dyDescent="0.9">
+    <row r="1" spans="1:8" ht="54" customHeight="1" x14ac:dyDescent="0.7">
       <c r="A1" s="2"/>
       <c r="B1" s="1">
         <v>2019</v>
@@ -5958,12 +5958,12 @@
       <c r="B14" s="10"/>
       <c r="C14" s="10"/>
       <c r="D14" s="65"/>
-      <c r="E14" s="64"/>
-      <c r="F14" s="64"/>
-      <c r="G14" s="64"/>
-      <c r="H14" s="64"/>
-    </row>
-    <row r="15" spans="1:8" ht="54" customHeight="1" x14ac:dyDescent="0.9">
+      <c r="E14" s="62"/>
+      <c r="F14" s="62"/>
+      <c r="G14" s="62"/>
+      <c r="H14" s="62"/>
+    </row>
+    <row r="15" spans="1:8" ht="54" customHeight="1" x14ac:dyDescent="0.7">
       <c r="A15" s="2"/>
       <c r="B15" s="1">
         <f>YEAR(DATE(Calendario1Año,Calendario1MesOpción+1,1))</f>
@@ -6209,24 +6209,24 @@
       <c r="C27" s="4">
         <v>43529</v>
       </c>
-      <c r="D27" s="63" t="s">
+      <c r="D27" s="64" t="s">
         <v>1</v>
       </c>
-      <c r="E27" s="63"/>
-      <c r="F27" s="63"/>
-      <c r="G27" s="63"/>
-      <c r="H27" s="63"/>
+      <c r="E27" s="64"/>
+      <c r="F27" s="64"/>
+      <c r="G27" s="64"/>
+      <c r="H27" s="64"/>
     </row>
     <row r="28" spans="1:8" ht="63.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B28" s="10"/>
       <c r="C28" s="10"/>
-      <c r="D28" s="64"/>
-      <c r="E28" s="64"/>
-      <c r="F28" s="64"/>
-      <c r="G28" s="64"/>
-      <c r="H28" s="64"/>
-    </row>
-    <row r="29" spans="1:8" ht="54" customHeight="1" x14ac:dyDescent="0.9">
+      <c r="D28" s="62"/>
+      <c r="E28" s="62"/>
+      <c r="F28" s="62"/>
+      <c r="G28" s="62"/>
+      <c r="H28" s="62"/>
+    </row>
+    <row r="29" spans="1:8" ht="54" customHeight="1" x14ac:dyDescent="0.7">
       <c r="A29" s="2"/>
       <c r="B29" s="1">
         <f>YEAR(DATE(Calendario2Año,Calendario2MesOpción+1,1))</f>
@@ -6470,24 +6470,24 @@
       <c r="C41" s="4">
         <v>43557</v>
       </c>
-      <c r="D41" s="63" t="s">
+      <c r="D41" s="64" t="s">
         <v>1</v>
       </c>
-      <c r="E41" s="63"/>
-      <c r="F41" s="63"/>
-      <c r="G41" s="63"/>
-      <c r="H41" s="63"/>
+      <c r="E41" s="64"/>
+      <c r="F41" s="64"/>
+      <c r="G41" s="64"/>
+      <c r="H41" s="64"/>
     </row>
     <row r="42" spans="1:8" ht="63.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B42" s="10"/>
       <c r="C42" s="10"/>
-      <c r="D42" s="64"/>
-      <c r="E42" s="64"/>
-      <c r="F42" s="64"/>
-      <c r="G42" s="64"/>
-      <c r="H42" s="64"/>
-    </row>
-    <row r="43" spans="1:8" ht="54" customHeight="1" x14ac:dyDescent="0.9">
+      <c r="D42" s="62"/>
+      <c r="E42" s="62"/>
+      <c r="F42" s="62"/>
+      <c r="G42" s="62"/>
+      <c r="H42" s="62"/>
+    </row>
+    <row r="43" spans="1:8" ht="54" customHeight="1" x14ac:dyDescent="0.7">
       <c r="A43" s="2"/>
       <c r="B43" s="1">
         <f>YEAR(DATE(Calendario3Año,Calendario3MesOpción+1,1))</f>
@@ -6733,24 +6733,24 @@
       <c r="C55" s="4">
         <v>43592</v>
       </c>
-      <c r="D55" s="62" t="s">
+      <c r="D55" s="63" t="s">
         <v>1</v>
       </c>
-      <c r="E55" s="63"/>
-      <c r="F55" s="63"/>
-      <c r="G55" s="63"/>
-      <c r="H55" s="63"/>
+      <c r="E55" s="64"/>
+      <c r="F55" s="64"/>
+      <c r="G55" s="64"/>
+      <c r="H55" s="64"/>
     </row>
     <row r="56" spans="1:8" ht="63.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B56" s="10"/>
       <c r="C56" s="10"/>
-      <c r="D56" s="64"/>
-      <c r="E56" s="64"/>
-      <c r="F56" s="64"/>
-      <c r="G56" s="64"/>
-      <c r="H56" s="64"/>
-    </row>
-    <row r="57" spans="1:8" ht="54" customHeight="1" x14ac:dyDescent="0.9">
+      <c r="D56" s="62"/>
+      <c r="E56" s="62"/>
+      <c r="F56" s="62"/>
+      <c r="G56" s="62"/>
+      <c r="H56" s="62"/>
+    </row>
+    <row r="57" spans="1:8" ht="54" customHeight="1" x14ac:dyDescent="0.7">
       <c r="A57" s="2"/>
       <c r="B57" s="1">
         <f>YEAR(DATE(Calendario4Año,Calendario4MesOpción+1,1))</f>
@@ -6970,24 +6970,24 @@
       <c r="C69" s="4">
         <v>43620</v>
       </c>
-      <c r="D69" s="62" t="s">
+      <c r="D69" s="63" t="s">
         <v>1</v>
       </c>
-      <c r="E69" s="63"/>
-      <c r="F69" s="63"/>
-      <c r="G69" s="63"/>
-      <c r="H69" s="63"/>
+      <c r="E69" s="64"/>
+      <c r="F69" s="64"/>
+      <c r="G69" s="64"/>
+      <c r="H69" s="64"/>
     </row>
     <row r="70" spans="1:8" ht="63.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B70" s="10"/>
       <c r="C70" s="10"/>
-      <c r="D70" s="64"/>
-      <c r="E70" s="64"/>
-      <c r="F70" s="64"/>
-      <c r="G70" s="64"/>
-      <c r="H70" s="64"/>
-    </row>
-    <row r="71" spans="1:8" ht="54" customHeight="1" x14ac:dyDescent="0.9">
+      <c r="D70" s="62"/>
+      <c r="E70" s="62"/>
+      <c r="F70" s="62"/>
+      <c r="G70" s="62"/>
+      <c r="H70" s="62"/>
+    </row>
+    <row r="71" spans="1:8" ht="54" customHeight="1" x14ac:dyDescent="0.7">
       <c r="A71" s="2"/>
       <c r="B71" s="1">
         <f>YEAR(DATE(Calendario5Año,Calendario5MesOpción+1,1))</f>
@@ -7207,24 +7207,24 @@
       <c r="C83" s="4">
         <v>43648</v>
       </c>
-      <c r="D83" s="62" t="s">
+      <c r="D83" s="63" t="s">
         <v>1</v>
       </c>
-      <c r="E83" s="63"/>
-      <c r="F83" s="63"/>
-      <c r="G83" s="63"/>
-      <c r="H83" s="63"/>
+      <c r="E83" s="64"/>
+      <c r="F83" s="64"/>
+      <c r="G83" s="64"/>
+      <c r="H83" s="64"/>
     </row>
     <row r="84" spans="1:8" ht="63.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B84" s="10"/>
       <c r="C84" s="10"/>
-      <c r="D84" s="64"/>
-      <c r="E84" s="64"/>
-      <c r="F84" s="64"/>
-      <c r="G84" s="64"/>
-      <c r="H84" s="64"/>
-    </row>
-    <row r="85" spans="1:8" ht="54" customHeight="1" x14ac:dyDescent="0.9">
+      <c r="D84" s="62"/>
+      <c r="E84" s="62"/>
+      <c r="F84" s="62"/>
+      <c r="G84" s="62"/>
+      <c r="H84" s="62"/>
+    </row>
+    <row r="85" spans="1:8" ht="54" customHeight="1" x14ac:dyDescent="0.7">
       <c r="A85" s="2"/>
       <c r="B85" s="1">
         <f>YEAR(DATE(Calendario6Año,Calendario6MesOpción+1,1))</f>
@@ -7444,24 +7444,24 @@
       <c r="C97" s="4">
         <v>43683</v>
       </c>
-      <c r="D97" s="62" t="s">
+      <c r="D97" s="63" t="s">
         <v>1</v>
       </c>
-      <c r="E97" s="63"/>
-      <c r="F97" s="63"/>
-      <c r="G97" s="63"/>
-      <c r="H97" s="63"/>
+      <c r="E97" s="64"/>
+      <c r="F97" s="64"/>
+      <c r="G97" s="64"/>
+      <c r="H97" s="64"/>
     </row>
     <row r="98" spans="1:8" ht="63.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B98" s="10"/>
       <c r="C98" s="10"/>
-      <c r="D98" s="64"/>
-      <c r="E98" s="64"/>
-      <c r="F98" s="64"/>
-      <c r="G98" s="64"/>
-      <c r="H98" s="64"/>
-    </row>
-    <row r="99" spans="1:8" ht="54" customHeight="1" x14ac:dyDescent="0.9">
+      <c r="D98" s="62"/>
+      <c r="E98" s="62"/>
+      <c r="F98" s="62"/>
+      <c r="G98" s="62"/>
+      <c r="H98" s="62"/>
+    </row>
+    <row r="99" spans="1:8" ht="54" customHeight="1" x14ac:dyDescent="0.7">
       <c r="A99" s="2"/>
       <c r="B99" s="1">
         <f>YEAR(DATE(Calendario7Año,Calendario7MesOpción+1,1))</f>
@@ -7681,24 +7681,24 @@
       <c r="C111" s="4">
         <v>43711</v>
       </c>
-      <c r="D111" s="62" t="s">
+      <c r="D111" s="63" t="s">
         <v>1</v>
       </c>
-      <c r="E111" s="63"/>
-      <c r="F111" s="63"/>
-      <c r="G111" s="63"/>
-      <c r="H111" s="63"/>
+      <c r="E111" s="64"/>
+      <c r="F111" s="64"/>
+      <c r="G111" s="64"/>
+      <c r="H111" s="64"/>
     </row>
     <row r="112" spans="1:8" ht="63.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B112" s="10"/>
       <c r="C112" s="10"/>
-      <c r="D112" s="64"/>
-      <c r="E112" s="64"/>
-      <c r="F112" s="64"/>
-      <c r="G112" s="64"/>
-      <c r="H112" s="64"/>
-    </row>
-    <row r="113" spans="1:8" ht="54" customHeight="1" x14ac:dyDescent="0.9">
+      <c r="D112" s="62"/>
+      <c r="E112" s="62"/>
+      <c r="F112" s="62"/>
+      <c r="G112" s="62"/>
+      <c r="H112" s="62"/>
+    </row>
+    <row r="113" spans="1:8" ht="54" customHeight="1" x14ac:dyDescent="0.7">
       <c r="A113" s="2"/>
       <c r="B113" s="1">
         <f>YEAR(DATE(Calendario8Año,Calendario8MesOpción+1,1))</f>
@@ -7918,24 +7918,24 @@
       <c r="C125" s="4">
         <v>43739</v>
       </c>
-      <c r="D125" s="62" t="s">
+      <c r="D125" s="63" t="s">
         <v>1</v>
       </c>
-      <c r="E125" s="63"/>
-      <c r="F125" s="63"/>
-      <c r="G125" s="63"/>
-      <c r="H125" s="63"/>
+      <c r="E125" s="64"/>
+      <c r="F125" s="64"/>
+      <c r="G125" s="64"/>
+      <c r="H125" s="64"/>
     </row>
     <row r="126" spans="1:8" ht="63.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B126" s="10"/>
       <c r="C126" s="10"/>
-      <c r="D126" s="64"/>
-      <c r="E126" s="64"/>
-      <c r="F126" s="64"/>
-      <c r="G126" s="64"/>
-      <c r="H126" s="64"/>
-    </row>
-    <row r="127" spans="1:8" ht="54" customHeight="1" x14ac:dyDescent="0.9">
+      <c r="D126" s="62"/>
+      <c r="E126" s="62"/>
+      <c r="F126" s="62"/>
+      <c r="G126" s="62"/>
+      <c r="H126" s="62"/>
+    </row>
+    <row r="127" spans="1:8" ht="54" customHeight="1" x14ac:dyDescent="0.7">
       <c r="A127" s="2"/>
       <c r="B127" s="1">
         <f>YEAR(DATE(Calendario9Año,Calendario9MesOpción+1,1))</f>
@@ -8155,24 +8155,24 @@
       <c r="C139" s="4">
         <v>43774</v>
       </c>
-      <c r="D139" s="62" t="s">
+      <c r="D139" s="63" t="s">
         <v>1</v>
       </c>
-      <c r="E139" s="63"/>
-      <c r="F139" s="63"/>
-      <c r="G139" s="63"/>
-      <c r="H139" s="63"/>
+      <c r="E139" s="64"/>
+      <c r="F139" s="64"/>
+      <c r="G139" s="64"/>
+      <c r="H139" s="64"/>
     </row>
     <row r="140" spans="2:8" ht="63.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B140" s="10"/>
       <c r="C140" s="10"/>
-      <c r="D140" s="64"/>
-      <c r="E140" s="64"/>
-      <c r="F140" s="64"/>
-      <c r="G140" s="64"/>
-      <c r="H140" s="64"/>
-    </row>
-    <row r="141" spans="2:8" ht="54" customHeight="1" x14ac:dyDescent="0.9">
+      <c r="D140" s="62"/>
+      <c r="E140" s="62"/>
+      <c r="F140" s="62"/>
+      <c r="G140" s="62"/>
+      <c r="H140" s="62"/>
+    </row>
+    <row r="141" spans="2:8" ht="54" customHeight="1" x14ac:dyDescent="0.7">
       <c r="B141" s="1">
         <f>YEAR(DATE(Calendario10Año,Calendario10MesOpción+1,1))</f>
         <v>2019</v>
@@ -8390,24 +8390,24 @@
       <c r="C153" s="4">
         <v>43802</v>
       </c>
-      <c r="D153" s="62" t="s">
+      <c r="D153" s="63" t="s">
         <v>1</v>
       </c>
-      <c r="E153" s="63"/>
-      <c r="F153" s="63"/>
-      <c r="G153" s="63"/>
-      <c r="H153" s="63"/>
+      <c r="E153" s="64"/>
+      <c r="F153" s="64"/>
+      <c r="G153" s="64"/>
+      <c r="H153" s="64"/>
     </row>
     <row r="154" spans="2:8" ht="63.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B154" s="10"/>
       <c r="C154" s="10"/>
-      <c r="D154" s="64"/>
-      <c r="E154" s="64"/>
-      <c r="F154" s="64"/>
-      <c r="G154" s="64"/>
-      <c r="H154" s="64"/>
-    </row>
-    <row r="155" spans="2:8" ht="54" customHeight="1" x14ac:dyDescent="0.9">
+      <c r="D154" s="62"/>
+      <c r="E154" s="62"/>
+      <c r="F154" s="62"/>
+      <c r="G154" s="62"/>
+      <c r="H154" s="62"/>
+    </row>
+    <row r="155" spans="2:8" ht="54" customHeight="1" x14ac:dyDescent="0.7">
       <c r="B155" s="1">
         <f>YEAR(DATE(Calendario11Año,Calendario11MesOpción+1,1))</f>
         <v>2019</v>
@@ -8625,35 +8625,25 @@
       <c r="C167" s="4">
         <v>43830</v>
       </c>
-      <c r="D167" s="62" t="s">
+      <c r="D167" s="63" t="s">
         <v>1</v>
       </c>
-      <c r="E167" s="63"/>
-      <c r="F167" s="63"/>
-      <c r="G167" s="63"/>
-      <c r="H167" s="63"/>
+      <c r="E167" s="64"/>
+      <c r="F167" s="64"/>
+      <c r="G167" s="64"/>
+      <c r="H167" s="64"/>
     </row>
     <row r="168" spans="2:8" ht="63.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B168" s="10"/>
       <c r="C168" s="10"/>
-      <c r="D168" s="64"/>
-      <c r="E168" s="64"/>
-      <c r="F168" s="64"/>
-      <c r="G168" s="64"/>
-      <c r="H168" s="64"/>
+      <c r="D168" s="62"/>
+      <c r="E168" s="62"/>
+      <c r="F168" s="62"/>
+      <c r="G168" s="62"/>
+      <c r="H168" s="62"/>
     </row>
   </sheetData>
   <mergeCells count="24">
-    <mergeCell ref="D70:H70"/>
-    <mergeCell ref="D55:H55"/>
-    <mergeCell ref="D69:H69"/>
-    <mergeCell ref="D14:H14"/>
-    <mergeCell ref="D13:H13"/>
-    <mergeCell ref="D27:H27"/>
-    <mergeCell ref="D28:H28"/>
-    <mergeCell ref="D41:H41"/>
-    <mergeCell ref="D42:H42"/>
-    <mergeCell ref="D56:H56"/>
     <mergeCell ref="D83:H83"/>
     <mergeCell ref="D153:H153"/>
     <mergeCell ref="D168:H168"/>
@@ -8668,6 +8658,16 @@
     <mergeCell ref="D112:H112"/>
     <mergeCell ref="D154:H154"/>
     <mergeCell ref="D167:H167"/>
+    <mergeCell ref="D70:H70"/>
+    <mergeCell ref="D55:H55"/>
+    <mergeCell ref="D69:H69"/>
+    <mergeCell ref="D14:H14"/>
+    <mergeCell ref="D13:H13"/>
+    <mergeCell ref="D27:H27"/>
+    <mergeCell ref="D28:H28"/>
+    <mergeCell ref="D41:H41"/>
+    <mergeCell ref="D42:H42"/>
+    <mergeCell ref="D56:H56"/>
   </mergeCells>
   <phoneticPr fontId="3" type="noConversion"/>
   <conditionalFormatting sqref="B3:H3 B5:H5 B7:H7 B9:H9 B11:H11 B13:C13">
@@ -8779,16 +8779,16 @@
     <pageSetUpPr autoPageBreaks="0" fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:H168"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.77734375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.75" defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="2" customWidth="1"/>
-    <col min="2" max="2" width="18.21875" customWidth="1"/>
-    <col min="3" max="8" width="17.6640625" customWidth="1"/>
-    <col min="9" max="9" width="2.44140625" customWidth="1"/>
-    <col min="14" max="14" width="6.77734375" customWidth="1"/>
+    <col min="2" max="2" width="18.25" customWidth="1"/>
+    <col min="3" max="8" width="17.625" customWidth="1"/>
+    <col min="9" max="9" width="2.5" customWidth="1"/>
+    <col min="14" max="14" width="6.75" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="54" customHeight="1" x14ac:dyDescent="0.9">
+    <row r="1" spans="1:8" ht="54" customHeight="1" x14ac:dyDescent="0.7">
       <c r="A1" s="2"/>
       <c r="B1" s="1">
         <v>2020</v>
@@ -9045,12 +9045,12 @@
       <c r="B14" s="10"/>
       <c r="C14" s="10"/>
       <c r="D14" s="65"/>
-      <c r="E14" s="64"/>
-      <c r="F14" s="64"/>
-      <c r="G14" s="64"/>
-      <c r="H14" s="64"/>
-    </row>
-    <row r="15" spans="1:8" ht="54" customHeight="1" x14ac:dyDescent="0.9">
+      <c r="E14" s="62"/>
+      <c r="F14" s="62"/>
+      <c r="G14" s="62"/>
+      <c r="H14" s="62"/>
+    </row>
+    <row r="15" spans="1:8" ht="54" customHeight="1" x14ac:dyDescent="0.7">
       <c r="A15" s="2"/>
       <c r="B15" s="1">
         <f>YEAR(DATE(Calendario1Año,Calendario1MesOpción+1,1))</f>
@@ -9296,24 +9296,24 @@
       <c r="C27" s="4">
         <v>43893</v>
       </c>
-      <c r="D27" s="63" t="s">
+      <c r="D27" s="64" t="s">
         <v>1</v>
       </c>
-      <c r="E27" s="63"/>
-      <c r="F27" s="63"/>
-      <c r="G27" s="63"/>
-      <c r="H27" s="63"/>
+      <c r="E27" s="64"/>
+      <c r="F27" s="64"/>
+      <c r="G27" s="64"/>
+      <c r="H27" s="64"/>
     </row>
     <row r="28" spans="1:8" ht="63.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B28" s="10"/>
       <c r="C28" s="10"/>
-      <c r="D28" s="64"/>
-      <c r="E28" s="64"/>
-      <c r="F28" s="64"/>
-      <c r="G28" s="64"/>
-      <c r="H28" s="64"/>
-    </row>
-    <row r="29" spans="1:8" ht="54" customHeight="1" x14ac:dyDescent="0.9">
+      <c r="D28" s="62"/>
+      <c r="E28" s="62"/>
+      <c r="F28" s="62"/>
+      <c r="G28" s="62"/>
+      <c r="H28" s="62"/>
+    </row>
+    <row r="29" spans="1:8" ht="54" customHeight="1" x14ac:dyDescent="0.7">
       <c r="A29" s="2"/>
       <c r="B29" s="1">
         <f>YEAR(DATE(Calendario2Año,Calendario2MesOpción+1,1))</f>
@@ -9557,24 +9557,24 @@
       <c r="C41" s="4">
         <v>43921</v>
       </c>
-      <c r="D41" s="63" t="s">
+      <c r="D41" s="64" t="s">
         <v>1</v>
       </c>
-      <c r="E41" s="63"/>
-      <c r="F41" s="63"/>
-      <c r="G41" s="63"/>
-      <c r="H41" s="63"/>
+      <c r="E41" s="64"/>
+      <c r="F41" s="64"/>
+      <c r="G41" s="64"/>
+      <c r="H41" s="64"/>
     </row>
     <row r="42" spans="1:8" ht="63.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B42" s="10"/>
       <c r="C42" s="10"/>
-      <c r="D42" s="64"/>
-      <c r="E42" s="64"/>
-      <c r="F42" s="64"/>
-      <c r="G42" s="64"/>
-      <c r="H42" s="64"/>
-    </row>
-    <row r="43" spans="1:8" ht="54" customHeight="1" x14ac:dyDescent="0.9">
+      <c r="D42" s="62"/>
+      <c r="E42" s="62"/>
+      <c r="F42" s="62"/>
+      <c r="G42" s="62"/>
+      <c r="H42" s="62"/>
+    </row>
+    <row r="43" spans="1:8" ht="54" customHeight="1" x14ac:dyDescent="0.7">
       <c r="A43" s="2"/>
       <c r="B43" s="1">
         <f>YEAR(DATE(Calendario3Año,Calendario3MesOpción+1,1))</f>
@@ -9820,24 +9820,24 @@
       <c r="C55" s="4">
         <v>43956</v>
       </c>
-      <c r="D55" s="62" t="s">
+      <c r="D55" s="63" t="s">
         <v>1</v>
       </c>
-      <c r="E55" s="63"/>
-      <c r="F55" s="63"/>
-      <c r="G55" s="63"/>
-      <c r="H55" s="63"/>
+      <c r="E55" s="64"/>
+      <c r="F55" s="64"/>
+      <c r="G55" s="64"/>
+      <c r="H55" s="64"/>
     </row>
     <row r="56" spans="1:8" ht="63.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B56" s="10"/>
       <c r="C56" s="10"/>
-      <c r="D56" s="64"/>
-      <c r="E56" s="64"/>
-      <c r="F56" s="64"/>
-      <c r="G56" s="64"/>
-      <c r="H56" s="64"/>
-    </row>
-    <row r="57" spans="1:8" ht="54" customHeight="1" x14ac:dyDescent="0.9">
+      <c r="D56" s="62"/>
+      <c r="E56" s="62"/>
+      <c r="F56" s="62"/>
+      <c r="G56" s="62"/>
+      <c r="H56" s="62"/>
+    </row>
+    <row r="57" spans="1:8" ht="54" customHeight="1" x14ac:dyDescent="0.7">
       <c r="A57" s="2"/>
       <c r="B57" s="1">
         <f>YEAR(DATE(Calendario4Año,Calendario4MesOpción+1,1))</f>
@@ -10057,24 +10057,24 @@
       <c r="C69" s="4">
         <v>43984</v>
       </c>
-      <c r="D69" s="62" t="s">
+      <c r="D69" s="63" t="s">
         <v>1</v>
       </c>
-      <c r="E69" s="63"/>
-      <c r="F69" s="63"/>
-      <c r="G69" s="63"/>
-      <c r="H69" s="63"/>
+      <c r="E69" s="64"/>
+      <c r="F69" s="64"/>
+      <c r="G69" s="64"/>
+      <c r="H69" s="64"/>
     </row>
     <row r="70" spans="1:8" ht="63.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B70" s="10"/>
       <c r="C70" s="10"/>
-      <c r="D70" s="64"/>
-      <c r="E70" s="64"/>
-      <c r="F70" s="64"/>
-      <c r="G70" s="64"/>
-      <c r="H70" s="64"/>
-    </row>
-    <row r="71" spans="1:8" ht="54" customHeight="1" x14ac:dyDescent="0.9">
+      <c r="D70" s="62"/>
+      <c r="E70" s="62"/>
+      <c r="F70" s="62"/>
+      <c r="G70" s="62"/>
+      <c r="H70" s="62"/>
+    </row>
+    <row r="71" spans="1:8" ht="54" customHeight="1" x14ac:dyDescent="0.7">
       <c r="A71" s="2"/>
       <c r="B71" s="1">
         <f>YEAR(DATE(Calendario5Año,Calendario5MesOpción+1,1))</f>
@@ -10294,24 +10294,24 @@
       <c r="C83" s="4">
         <v>44019</v>
       </c>
-      <c r="D83" s="62" t="s">
+      <c r="D83" s="63" t="s">
         <v>1</v>
       </c>
-      <c r="E83" s="63"/>
-      <c r="F83" s="63"/>
-      <c r="G83" s="63"/>
-      <c r="H83" s="63"/>
+      <c r="E83" s="64"/>
+      <c r="F83" s="64"/>
+      <c r="G83" s="64"/>
+      <c r="H83" s="64"/>
     </row>
     <row r="84" spans="1:8" ht="63.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B84" s="10"/>
       <c r="C84" s="10"/>
-      <c r="D84" s="64"/>
-      <c r="E84" s="64"/>
-      <c r="F84" s="64"/>
-      <c r="G84" s="64"/>
-      <c r="H84" s="64"/>
-    </row>
-    <row r="85" spans="1:8" ht="54" customHeight="1" x14ac:dyDescent="0.9">
+      <c r="D84" s="62"/>
+      <c r="E84" s="62"/>
+      <c r="F84" s="62"/>
+      <c r="G84" s="62"/>
+      <c r="H84" s="62"/>
+    </row>
+    <row r="85" spans="1:8" ht="54" customHeight="1" x14ac:dyDescent="0.7">
       <c r="A85" s="2"/>
       <c r="B85" s="1">
         <f>YEAR(DATE(Calendario6Año,Calendario6MesOpción+1,1))</f>
@@ -10531,24 +10531,24 @@
       <c r="C97" s="4">
         <v>44047</v>
       </c>
-      <c r="D97" s="62" t="s">
+      <c r="D97" s="63" t="s">
         <v>1</v>
       </c>
-      <c r="E97" s="63"/>
-      <c r="F97" s="63"/>
-      <c r="G97" s="63"/>
-      <c r="H97" s="63"/>
+      <c r="E97" s="64"/>
+      <c r="F97" s="64"/>
+      <c r="G97" s="64"/>
+      <c r="H97" s="64"/>
     </row>
     <row r="98" spans="1:8" ht="63.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B98" s="10"/>
       <c r="C98" s="10"/>
-      <c r="D98" s="64"/>
-      <c r="E98" s="64"/>
-      <c r="F98" s="64"/>
-      <c r="G98" s="64"/>
-      <c r="H98" s="64"/>
-    </row>
-    <row r="99" spans="1:8" ht="54" customHeight="1" x14ac:dyDescent="0.9">
+      <c r="D98" s="62"/>
+      <c r="E98" s="62"/>
+      <c r="F98" s="62"/>
+      <c r="G98" s="62"/>
+      <c r="H98" s="62"/>
+    </row>
+    <row r="99" spans="1:8" ht="54" customHeight="1" x14ac:dyDescent="0.7">
       <c r="A99" s="2"/>
       <c r="B99" s="1">
         <f>YEAR(DATE(Calendario7Año,Calendario7MesOpción+1,1))</f>
@@ -10768,24 +10768,24 @@
       <c r="C111" s="4">
         <v>44075</v>
       </c>
-      <c r="D111" s="62" t="s">
+      <c r="D111" s="63" t="s">
         <v>1</v>
       </c>
-      <c r="E111" s="63"/>
-      <c r="F111" s="63"/>
-      <c r="G111" s="63"/>
-      <c r="H111" s="63"/>
+      <c r="E111" s="64"/>
+      <c r="F111" s="64"/>
+      <c r="G111" s="64"/>
+      <c r="H111" s="64"/>
     </row>
     <row r="112" spans="1:8" ht="63.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B112" s="10"/>
       <c r="C112" s="10"/>
-      <c r="D112" s="64"/>
-      <c r="E112" s="64"/>
-      <c r="F112" s="64"/>
-      <c r="G112" s="64"/>
-      <c r="H112" s="64"/>
-    </row>
-    <row r="113" spans="1:8" ht="54" customHeight="1" x14ac:dyDescent="0.9">
+      <c r="D112" s="62"/>
+      <c r="E112" s="62"/>
+      <c r="F112" s="62"/>
+      <c r="G112" s="62"/>
+      <c r="H112" s="62"/>
+    </row>
+    <row r="113" spans="1:8" ht="54" customHeight="1" x14ac:dyDescent="0.7">
       <c r="A113" s="2"/>
       <c r="B113" s="1">
         <f>YEAR(DATE(Calendario8Año,Calendario8MesOpción+1,1))</f>
@@ -11005,24 +11005,24 @@
       <c r="C125" s="4">
         <v>44110</v>
       </c>
-      <c r="D125" s="62" t="s">
+      <c r="D125" s="63" t="s">
         <v>1</v>
       </c>
-      <c r="E125" s="63"/>
-      <c r="F125" s="63"/>
-      <c r="G125" s="63"/>
-      <c r="H125" s="63"/>
+      <c r="E125" s="64"/>
+      <c r="F125" s="64"/>
+      <c r="G125" s="64"/>
+      <c r="H125" s="64"/>
     </row>
     <row r="126" spans="1:8" ht="63.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B126" s="10"/>
       <c r="C126" s="10"/>
-      <c r="D126" s="64"/>
-      <c r="E126" s="64"/>
-      <c r="F126" s="64"/>
-      <c r="G126" s="64"/>
-      <c r="H126" s="64"/>
-    </row>
-    <row r="127" spans="1:8" ht="54" customHeight="1" x14ac:dyDescent="0.9">
+      <c r="D126" s="62"/>
+      <c r="E126" s="62"/>
+      <c r="F126" s="62"/>
+      <c r="G126" s="62"/>
+      <c r="H126" s="62"/>
+    </row>
+    <row r="127" spans="1:8" ht="54" customHeight="1" x14ac:dyDescent="0.7">
       <c r="A127" s="2"/>
       <c r="B127" s="1">
         <f>YEAR(DATE(Calendario9Año,Calendario9MesOpción+1,1))</f>
@@ -11242,24 +11242,24 @@
       <c r="C139" s="4">
         <v>44138</v>
       </c>
-      <c r="D139" s="62" t="s">
+      <c r="D139" s="63" t="s">
         <v>1</v>
       </c>
-      <c r="E139" s="63"/>
-      <c r="F139" s="63"/>
-      <c r="G139" s="63"/>
-      <c r="H139" s="63"/>
+      <c r="E139" s="64"/>
+      <c r="F139" s="64"/>
+      <c r="G139" s="64"/>
+      <c r="H139" s="64"/>
     </row>
     <row r="140" spans="2:8" ht="63.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B140" s="10"/>
       <c r="C140" s="10"/>
-      <c r="D140" s="64"/>
-      <c r="E140" s="64"/>
-      <c r="F140" s="64"/>
-      <c r="G140" s="64"/>
-      <c r="H140" s="64"/>
-    </row>
-    <row r="141" spans="2:8" ht="54" customHeight="1" x14ac:dyDescent="0.9">
+      <c r="D140" s="62"/>
+      <c r="E140" s="62"/>
+      <c r="F140" s="62"/>
+      <c r="G140" s="62"/>
+      <c r="H140" s="62"/>
+    </row>
+    <row r="141" spans="2:8" ht="54" customHeight="1" x14ac:dyDescent="0.7">
       <c r="B141" s="1">
         <f>YEAR(DATE(Calendario10Año,Calendario10MesOpción+1,1))</f>
         <v>2020</v>
@@ -11477,24 +11477,24 @@
       <c r="C153" s="4">
         <v>44166</v>
       </c>
-      <c r="D153" s="62" t="s">
+      <c r="D153" s="63" t="s">
         <v>1</v>
       </c>
-      <c r="E153" s="63"/>
-      <c r="F153" s="63"/>
-      <c r="G153" s="63"/>
-      <c r="H153" s="63"/>
+      <c r="E153" s="64"/>
+      <c r="F153" s="64"/>
+      <c r="G153" s="64"/>
+      <c r="H153" s="64"/>
     </row>
     <row r="154" spans="2:8" ht="63.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B154" s="10"/>
       <c r="C154" s="10"/>
-      <c r="D154" s="64"/>
-      <c r="E154" s="64"/>
-      <c r="F154" s="64"/>
-      <c r="G154" s="64"/>
-      <c r="H154" s="64"/>
-    </row>
-    <row r="155" spans="2:8" ht="54" customHeight="1" x14ac:dyDescent="0.9">
+      <c r="D154" s="62"/>
+      <c r="E154" s="62"/>
+      <c r="F154" s="62"/>
+      <c r="G154" s="62"/>
+      <c r="H154" s="62"/>
+    </row>
+    <row r="155" spans="2:8" ht="54" customHeight="1" x14ac:dyDescent="0.7">
       <c r="B155" s="1">
         <f>YEAR(DATE(Calendario11Año,Calendario11MesOpción+1,1))</f>
         <v>2020</v>
@@ -11712,25 +11712,37 @@
       <c r="C167" s="4">
         <v>44201</v>
       </c>
-      <c r="D167" s="62" t="s">
+      <c r="D167" s="63" t="s">
         <v>1</v>
       </c>
-      <c r="E167" s="63"/>
-      <c r="F167" s="63"/>
-      <c r="G167" s="63"/>
-      <c r="H167" s="63"/>
+      <c r="E167" s="64"/>
+      <c r="F167" s="64"/>
+      <c r="G167" s="64"/>
+      <c r="H167" s="64"/>
     </row>
     <row r="168" spans="2:8" ht="63.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B168" s="10"/>
       <c r="C168" s="10"/>
-      <c r="D168" s="64"/>
-      <c r="E168" s="64"/>
-      <c r="F168" s="64"/>
-      <c r="G168" s="64"/>
-      <c r="H168" s="64"/>
+      <c r="D168" s="62"/>
+      <c r="E168" s="62"/>
+      <c r="F168" s="62"/>
+      <c r="G168" s="62"/>
+      <c r="H168" s="62"/>
     </row>
   </sheetData>
   <mergeCells count="24">
+    <mergeCell ref="D84:H84"/>
+    <mergeCell ref="D13:H13"/>
+    <mergeCell ref="D14:H14"/>
+    <mergeCell ref="D27:H27"/>
+    <mergeCell ref="D28:H28"/>
+    <mergeCell ref="D41:H41"/>
+    <mergeCell ref="D42:H42"/>
+    <mergeCell ref="D55:H55"/>
+    <mergeCell ref="D56:H56"/>
+    <mergeCell ref="D69:H69"/>
+    <mergeCell ref="D70:H70"/>
+    <mergeCell ref="D83:H83"/>
     <mergeCell ref="D168:H168"/>
     <mergeCell ref="D97:H97"/>
     <mergeCell ref="D98:H98"/>
@@ -11743,18 +11755,6 @@
     <mergeCell ref="D153:H153"/>
     <mergeCell ref="D154:H154"/>
     <mergeCell ref="D167:H167"/>
-    <mergeCell ref="D84:H84"/>
-    <mergeCell ref="D13:H13"/>
-    <mergeCell ref="D14:H14"/>
-    <mergeCell ref="D27:H27"/>
-    <mergeCell ref="D28:H28"/>
-    <mergeCell ref="D41:H41"/>
-    <mergeCell ref="D42:H42"/>
-    <mergeCell ref="D55:H55"/>
-    <mergeCell ref="D56:H56"/>
-    <mergeCell ref="D69:H69"/>
-    <mergeCell ref="D70:H70"/>
-    <mergeCell ref="D83:H83"/>
   </mergeCells>
   <conditionalFormatting sqref="B3:H3 B5:H5 B7:H7 B9:H9 B11:H11 B13:C13">
     <cfRule type="expression" dxfId="23" priority="12">
@@ -11860,16 +11860,16 @@
     <pageSetUpPr autoPageBreaks="0" fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:H168"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.77734375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.75" defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="2" customWidth="1"/>
-    <col min="2" max="2" width="18.21875" customWidth="1"/>
-    <col min="3" max="8" width="17.6640625" customWidth="1"/>
-    <col min="9" max="9" width="2.44140625" customWidth="1"/>
-    <col min="14" max="14" width="6.77734375" customWidth="1"/>
+    <col min="2" max="2" width="18.25" customWidth="1"/>
+    <col min="3" max="8" width="17.625" customWidth="1"/>
+    <col min="9" max="9" width="2.5" customWidth="1"/>
+    <col min="14" max="14" width="6.75" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="54" customHeight="1" x14ac:dyDescent="0.9">
+    <row r="1" spans="1:8" ht="54" customHeight="1" x14ac:dyDescent="0.7">
       <c r="A1" s="2"/>
       <c r="B1" s="1">
         <v>2026</v>
@@ -12098,12 +12098,12 @@
       <c r="B14" s="10"/>
       <c r="C14" s="10"/>
       <c r="D14" s="65"/>
-      <c r="E14" s="64"/>
-      <c r="F14" s="64"/>
-      <c r="G14" s="64"/>
-      <c r="H14" s="64"/>
-    </row>
-    <row r="15" spans="1:8" ht="54" customHeight="1" x14ac:dyDescent="0.9">
+      <c r="E14" s="62"/>
+      <c r="F14" s="62"/>
+      <c r="G14" s="62"/>
+      <c r="H14" s="62"/>
+    </row>
+    <row r="15" spans="1:8" ht="54" customHeight="1" x14ac:dyDescent="0.7">
       <c r="A15" s="2"/>
       <c r="B15" s="1">
         <f>YEAR(DATE(Calendario1Año,Calendario1MesOpción+1,1))</f>
@@ -12323,24 +12323,24 @@
       <c r="C27" s="4">
         <v>46084</v>
       </c>
-      <c r="D27" s="63" t="s">
+      <c r="D27" s="64" t="s">
         <v>1</v>
       </c>
-      <c r="E27" s="63"/>
-      <c r="F27" s="63"/>
-      <c r="G27" s="63"/>
-      <c r="H27" s="63"/>
+      <c r="E27" s="64"/>
+      <c r="F27" s="64"/>
+      <c r="G27" s="64"/>
+      <c r="H27" s="64"/>
     </row>
     <row r="28" spans="1:8" ht="63.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B28" s="10"/>
       <c r="C28" s="10"/>
-      <c r="D28" s="64"/>
-      <c r="E28" s="64"/>
-      <c r="F28" s="64"/>
-      <c r="G28" s="64"/>
-      <c r="H28" s="64"/>
-    </row>
-    <row r="29" spans="1:8" ht="54" customHeight="1" x14ac:dyDescent="0.9">
+      <c r="D28" s="62"/>
+      <c r="E28" s="62"/>
+      <c r="F28" s="62"/>
+      <c r="G28" s="62"/>
+      <c r="H28" s="62"/>
+    </row>
+    <row r="29" spans="1:8" ht="54" customHeight="1" x14ac:dyDescent="0.7">
       <c r="A29" s="2"/>
       <c r="B29" s="1">
         <f>YEAR(DATE(Calendario2Año,Calendario2MesOpción+1,1))</f>
@@ -12560,24 +12560,24 @@
       <c r="C41" s="4">
         <v>46112</v>
       </c>
-      <c r="D41" s="63" t="s">
+      <c r="D41" s="64" t="s">
         <v>1</v>
       </c>
-      <c r="E41" s="63"/>
-      <c r="F41" s="63"/>
-      <c r="G41" s="63"/>
-      <c r="H41" s="63"/>
+      <c r="E41" s="64"/>
+      <c r="F41" s="64"/>
+      <c r="G41" s="64"/>
+      <c r="H41" s="64"/>
     </row>
     <row r="42" spans="1:8" ht="63.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B42" s="10"/>
       <c r="C42" s="10"/>
-      <c r="D42" s="64"/>
-      <c r="E42" s="64"/>
-      <c r="F42" s="64"/>
-      <c r="G42" s="64"/>
-      <c r="H42" s="64"/>
-    </row>
-    <row r="43" spans="1:8" ht="54" customHeight="1" x14ac:dyDescent="0.9">
+      <c r="D42" s="62"/>
+      <c r="E42" s="62"/>
+      <c r="F42" s="62"/>
+      <c r="G42" s="62"/>
+      <c r="H42" s="62"/>
+    </row>
+    <row r="43" spans="1:8" ht="54" customHeight="1" x14ac:dyDescent="0.7">
       <c r="A43" s="2"/>
       <c r="B43" s="1">
         <f>YEAR(DATE(Calendario3Año,Calendario3MesOpción+1,1))</f>
@@ -12797,24 +12797,24 @@
       <c r="C55" s="4">
         <v>46147</v>
       </c>
-      <c r="D55" s="62" t="s">
+      <c r="D55" s="63" t="s">
         <v>1</v>
       </c>
-      <c r="E55" s="63"/>
-      <c r="F55" s="63"/>
-      <c r="G55" s="63"/>
-      <c r="H55" s="63"/>
+      <c r="E55" s="64"/>
+      <c r="F55" s="64"/>
+      <c r="G55" s="64"/>
+      <c r="H55" s="64"/>
     </row>
     <row r="56" spans="1:8" ht="63.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B56" s="10"/>
       <c r="C56" s="10"/>
-      <c r="D56" s="64"/>
-      <c r="E56" s="64"/>
-      <c r="F56" s="64"/>
-      <c r="G56" s="64"/>
-      <c r="H56" s="64"/>
-    </row>
-    <row r="57" spans="1:8" ht="54" customHeight="1" x14ac:dyDescent="0.9">
+      <c r="D56" s="62"/>
+      <c r="E56" s="62"/>
+      <c r="F56" s="62"/>
+      <c r="G56" s="62"/>
+      <c r="H56" s="62"/>
+    </row>
+    <row r="57" spans="1:8" ht="54" customHeight="1" x14ac:dyDescent="0.7">
       <c r="A57" s="2"/>
       <c r="B57" s="1">
         <f>YEAR(DATE(Calendario4Año,Calendario4MesOpción+1,1))</f>
@@ -13034,24 +13034,24 @@
       <c r="C69" s="4">
         <v>46175</v>
       </c>
-      <c r="D69" s="62" t="s">
+      <c r="D69" s="63" t="s">
         <v>1</v>
       </c>
-      <c r="E69" s="63"/>
-      <c r="F69" s="63"/>
-      <c r="G69" s="63"/>
-      <c r="H69" s="63"/>
+      <c r="E69" s="64"/>
+      <c r="F69" s="64"/>
+      <c r="G69" s="64"/>
+      <c r="H69" s="64"/>
     </row>
     <row r="70" spans="1:8" ht="63.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B70" s="13"/>
       <c r="C70" s="10"/>
-      <c r="D70" s="64"/>
-      <c r="E70" s="64"/>
-      <c r="F70" s="64"/>
-      <c r="G70" s="64"/>
-      <c r="H70" s="64"/>
-    </row>
-    <row r="71" spans="1:8" ht="54" customHeight="1" x14ac:dyDescent="0.9">
+      <c r="D70" s="62"/>
+      <c r="E70" s="62"/>
+      <c r="F70" s="62"/>
+      <c r="G70" s="62"/>
+      <c r="H70" s="62"/>
+    </row>
+    <row r="71" spans="1:8" ht="54" customHeight="1" x14ac:dyDescent="0.7">
       <c r="A71" s="2"/>
       <c r="B71" s="1">
         <f>YEAR(DATE(Calendario5Año,Calendario5MesOpción+1,1))</f>
@@ -13271,24 +13271,24 @@
       <c r="C83" s="4">
         <v>46210</v>
       </c>
-      <c r="D83" s="62" t="s">
+      <c r="D83" s="63" t="s">
         <v>1</v>
       </c>
-      <c r="E83" s="63"/>
-      <c r="F83" s="63"/>
-      <c r="G83" s="63"/>
-      <c r="H83" s="63"/>
+      <c r="E83" s="64"/>
+      <c r="F83" s="64"/>
+      <c r="G83" s="64"/>
+      <c r="H83" s="64"/>
     </row>
     <row r="84" spans="1:8" ht="63.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B84" s="10"/>
       <c r="C84" s="10"/>
-      <c r="D84" s="64"/>
-      <c r="E84" s="64"/>
-      <c r="F84" s="64"/>
-      <c r="G84" s="64"/>
-      <c r="H84" s="64"/>
-    </row>
-    <row r="85" spans="1:8" ht="54" customHeight="1" x14ac:dyDescent="0.9">
+      <c r="D84" s="62"/>
+      <c r="E84" s="62"/>
+      <c r="F84" s="62"/>
+      <c r="G84" s="62"/>
+      <c r="H84" s="62"/>
+    </row>
+    <row r="85" spans="1:8" ht="54" customHeight="1" x14ac:dyDescent="0.7">
       <c r="A85" s="2"/>
       <c r="B85" s="1">
         <f>YEAR(DATE(Calendario6Año,Calendario6MesOpción+1,1))</f>
@@ -13508,24 +13508,24 @@
       <c r="C97" s="4">
         <v>46238</v>
       </c>
-      <c r="D97" s="62" t="s">
+      <c r="D97" s="63" t="s">
         <v>1</v>
       </c>
-      <c r="E97" s="63"/>
-      <c r="F97" s="63"/>
-      <c r="G97" s="63"/>
-      <c r="H97" s="63"/>
+      <c r="E97" s="64"/>
+      <c r="F97" s="64"/>
+      <c r="G97" s="64"/>
+      <c r="H97" s="64"/>
     </row>
     <row r="98" spans="1:8" ht="63.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B98" s="10"/>
       <c r="C98" s="10"/>
-      <c r="D98" s="64"/>
-      <c r="E98" s="64"/>
-      <c r="F98" s="64"/>
-      <c r="G98" s="64"/>
-      <c r="H98" s="64"/>
-    </row>
-    <row r="99" spans="1:8" ht="54" customHeight="1" x14ac:dyDescent="0.9">
+      <c r="D98" s="62"/>
+      <c r="E98" s="62"/>
+      <c r="F98" s="62"/>
+      <c r="G98" s="62"/>
+      <c r="H98" s="62"/>
+    </row>
+    <row r="99" spans="1:8" ht="54" customHeight="1" x14ac:dyDescent="0.7">
       <c r="A99" s="2"/>
       <c r="B99" s="1">
         <f>YEAR(DATE(Calendario7Año,Calendario7MesOpción+1,1))</f>
@@ -13745,24 +13745,24 @@
       <c r="C111" s="4">
         <v>46266</v>
       </c>
-      <c r="D111" s="62" t="s">
+      <c r="D111" s="63" t="s">
         <v>1</v>
       </c>
-      <c r="E111" s="63"/>
-      <c r="F111" s="63"/>
-      <c r="G111" s="63"/>
-      <c r="H111" s="63"/>
+      <c r="E111" s="64"/>
+      <c r="F111" s="64"/>
+      <c r="G111" s="64"/>
+      <c r="H111" s="64"/>
     </row>
     <row r="112" spans="1:8" ht="63.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B112" s="13"/>
       <c r="C112" s="10"/>
-      <c r="D112" s="64"/>
-      <c r="E112" s="64"/>
-      <c r="F112" s="64"/>
-      <c r="G112" s="64"/>
-      <c r="H112" s="64"/>
-    </row>
-    <row r="113" spans="1:8" ht="54" customHeight="1" x14ac:dyDescent="0.9">
+      <c r="D112" s="62"/>
+      <c r="E112" s="62"/>
+      <c r="F112" s="62"/>
+      <c r="G112" s="62"/>
+      <c r="H112" s="62"/>
+    </row>
+    <row r="113" spans="1:8" ht="54" customHeight="1" x14ac:dyDescent="0.7">
       <c r="A113" s="2"/>
       <c r="B113" s="1">
         <f>YEAR(DATE(Calendario8Año,Calendario8MesOpción+1,1))</f>
@@ -13982,24 +13982,24 @@
       <c r="C125" s="4">
         <v>46301</v>
       </c>
-      <c r="D125" s="62" t="s">
+      <c r="D125" s="63" t="s">
         <v>1</v>
       </c>
-      <c r="E125" s="63"/>
-      <c r="F125" s="63"/>
-      <c r="G125" s="63"/>
-      <c r="H125" s="63"/>
+      <c r="E125" s="64"/>
+      <c r="F125" s="64"/>
+      <c r="G125" s="64"/>
+      <c r="H125" s="64"/>
     </row>
     <row r="126" spans="1:8" ht="63.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B126" s="10"/>
       <c r="C126" s="10"/>
-      <c r="D126" s="64"/>
-      <c r="E126" s="64"/>
-      <c r="F126" s="64"/>
-      <c r="G126" s="64"/>
-      <c r="H126" s="64"/>
-    </row>
-    <row r="127" spans="1:8" ht="54" customHeight="1" x14ac:dyDescent="0.9">
+      <c r="D126" s="62"/>
+      <c r="E126" s="62"/>
+      <c r="F126" s="62"/>
+      <c r="G126" s="62"/>
+      <c r="H126" s="62"/>
+    </row>
+    <row r="127" spans="1:8" ht="54" customHeight="1" x14ac:dyDescent="0.7">
       <c r="A127" s="2"/>
       <c r="B127" s="53">
         <f>YEAR(DATE(Calendario9Año,Calendario9MesOpción+1,1))</f>
@@ -14221,24 +14221,24 @@
       <c r="C139" s="4">
         <v>46329</v>
       </c>
-      <c r="D139" s="62" t="s">
+      <c r="D139" s="63" t="s">
         <v>1</v>
       </c>
-      <c r="E139" s="63"/>
-      <c r="F139" s="63"/>
-      <c r="G139" s="63"/>
-      <c r="H139" s="63"/>
+      <c r="E139" s="64"/>
+      <c r="F139" s="64"/>
+      <c r="G139" s="64"/>
+      <c r="H139" s="64"/>
     </row>
     <row r="140" spans="2:8" ht="63.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B140" s="10"/>
       <c r="C140" s="10"/>
-      <c r="D140" s="64"/>
-      <c r="E140" s="64"/>
-      <c r="F140" s="64"/>
-      <c r="G140" s="64"/>
-      <c r="H140" s="64"/>
-    </row>
-    <row r="141" spans="2:8" ht="54" customHeight="1" x14ac:dyDescent="0.9">
+      <c r="D140" s="62"/>
+      <c r="E140" s="62"/>
+      <c r="F140" s="62"/>
+      <c r="G140" s="62"/>
+      <c r="H140" s="62"/>
+    </row>
+    <row r="141" spans="2:8" ht="54" customHeight="1" x14ac:dyDescent="0.7">
       <c r="B141" s="53">
         <f>YEAR(DATE(Calendario10Año,Calendario10MesOpción+1,1))</f>
         <v>2026</v>
@@ -14460,24 +14460,24 @@
       <c r="C153" s="4">
         <v>46357</v>
       </c>
-      <c r="D153" s="62" t="s">
+      <c r="D153" s="63" t="s">
         <v>1</v>
       </c>
-      <c r="E153" s="63"/>
-      <c r="F153" s="63"/>
-      <c r="G153" s="63"/>
-      <c r="H153" s="63"/>
+      <c r="E153" s="64"/>
+      <c r="F153" s="64"/>
+      <c r="G153" s="64"/>
+      <c r="H153" s="64"/>
     </row>
     <row r="154" spans="2:8" ht="63.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B154" s="10"/>
       <c r="C154" s="10"/>
-      <c r="D154" s="64"/>
-      <c r="E154" s="64"/>
-      <c r="F154" s="64"/>
-      <c r="G154" s="64"/>
-      <c r="H154" s="64"/>
-    </row>
-    <row r="155" spans="2:8" ht="54" customHeight="1" x14ac:dyDescent="0.9">
+      <c r="D154" s="62"/>
+      <c r="E154" s="62"/>
+      <c r="F154" s="62"/>
+      <c r="G154" s="62"/>
+      <c r="H154" s="62"/>
+    </row>
+    <row r="155" spans="2:8" ht="54" customHeight="1" x14ac:dyDescent="0.7">
       <c r="B155" s="1">
         <f>YEAR(DATE(Calendario11Año,Calendario11MesOpción+1,1))</f>
         <v>2026</v>
@@ -14695,25 +14695,37 @@
       <c r="C167" s="4">
         <v>46392</v>
       </c>
-      <c r="D167" s="62" t="s">
+      <c r="D167" s="63" t="s">
         <v>1</v>
       </c>
-      <c r="E167" s="63"/>
-      <c r="F167" s="63"/>
-      <c r="G167" s="63"/>
-      <c r="H167" s="63"/>
+      <c r="E167" s="64"/>
+      <c r="F167" s="64"/>
+      <c r="G167" s="64"/>
+      <c r="H167" s="64"/>
     </row>
     <row r="168" spans="2:8" ht="63.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B168" s="10"/>
       <c r="C168" s="10"/>
-      <c r="D168" s="64"/>
-      <c r="E168" s="64"/>
-      <c r="F168" s="64"/>
-      <c r="G168" s="64"/>
-      <c r="H168" s="64"/>
+      <c r="D168" s="62"/>
+      <c r="E168" s="62"/>
+      <c r="F168" s="62"/>
+      <c r="G168" s="62"/>
+      <c r="H168" s="62"/>
     </row>
   </sheetData>
   <mergeCells count="27">
+    <mergeCell ref="D84:H84"/>
+    <mergeCell ref="D13:H13"/>
+    <mergeCell ref="D14:H14"/>
+    <mergeCell ref="D27:H27"/>
+    <mergeCell ref="D28:H28"/>
+    <mergeCell ref="D41:H41"/>
+    <mergeCell ref="D42:H42"/>
+    <mergeCell ref="D55:H55"/>
+    <mergeCell ref="D56:H56"/>
+    <mergeCell ref="D69:H69"/>
+    <mergeCell ref="D70:H70"/>
+    <mergeCell ref="D83:H83"/>
     <mergeCell ref="D168:H168"/>
     <mergeCell ref="D97:H97"/>
     <mergeCell ref="D98:H98"/>
@@ -14729,18 +14741,6 @@
     <mergeCell ref="D136:E136"/>
     <mergeCell ref="D150:E150"/>
     <mergeCell ref="D152:E152"/>
-    <mergeCell ref="D84:H84"/>
-    <mergeCell ref="D13:H13"/>
-    <mergeCell ref="D14:H14"/>
-    <mergeCell ref="D27:H27"/>
-    <mergeCell ref="D28:H28"/>
-    <mergeCell ref="D41:H41"/>
-    <mergeCell ref="D42:H42"/>
-    <mergeCell ref="D55:H55"/>
-    <mergeCell ref="D56:H56"/>
-    <mergeCell ref="D69:H69"/>
-    <mergeCell ref="D70:H70"/>
-    <mergeCell ref="D83:H83"/>
   </mergeCells>
   <conditionalFormatting sqref="B3:H3 B5:H5 B7:H7 B9:H9 B11:H11 B13:C13">
     <cfRule type="expression" dxfId="11" priority="12">

--- a/actividades MIR 2026/IPPI SDTI - Calendario Actividades.xlsx
+++ b/actividades MIR 2026/IPPI SDTI - Calendario Actividades.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\IPPI 11\Documents\GitHub\proyecto-ippi\actividades MIR 2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1713BF41-644D-47E1-BB56-44040801A22A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BB4EDD1A-B45D-49C0-869D-143131223A4D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="16440" tabRatio="788" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="788" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Calendario" sheetId="15" r:id="rId1"/>
@@ -166,7 +166,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1085" uniqueCount="59">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1086" uniqueCount="59">
   <si>
     <t>LUNES</t>
   </si>
@@ -1224,14 +1224,14 @@
     <xf numFmtId="0" fontId="11" fillId="13" borderId="3" xfId="11" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="10" borderId="0" xfId="13" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="13" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="14" xfId="13" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="10" borderId="0" xfId="13" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="9" borderId="0" xfId="13" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1239,14 +1239,14 @@
     <xf numFmtId="0" fontId="17" fillId="10" borderId="0" xfId="13" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="7" applyNumberFormat="1">
-      <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
-    </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="8" xfId="8" applyFont="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
     <xf numFmtId="164" fontId="12" fillId="0" borderId="8" xfId="8">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="7" applyNumberFormat="1">
+      <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="7" applyNumberFormat="1" applyBorder="1">
       <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
@@ -1808,30 +1808,30 @@
       <c r="F2" s="61"/>
       <c r="G2" s="61"/>
       <c r="H2" s="61"/>
-      <c r="K2" s="59" t="s">
+      <c r="K2" s="57" t="s">
         <v>5</v>
       </c>
-      <c r="L2" s="59"/>
-      <c r="M2" s="59"/>
-      <c r="N2" s="59"/>
-      <c r="O2" s="59"/>
-      <c r="P2" s="59"/>
-      <c r="S2" s="59" t="s">
+      <c r="L2" s="57"/>
+      <c r="M2" s="57"/>
+      <c r="N2" s="57"/>
+      <c r="O2" s="57"/>
+      <c r="P2" s="57"/>
+      <c r="S2" s="57" t="s">
         <v>6</v>
       </c>
-      <c r="T2" s="59"/>
-      <c r="U2" s="59"/>
-      <c r="V2" s="59"/>
-      <c r="W2" s="59"/>
-      <c r="X2" s="59"/>
-      <c r="AA2" s="59" t="s">
+      <c r="T2" s="57"/>
+      <c r="U2" s="57"/>
+      <c r="V2" s="57"/>
+      <c r="W2" s="57"/>
+      <c r="X2" s="57"/>
+      <c r="AA2" s="57" t="s">
         <v>7</v>
       </c>
-      <c r="AB2" s="59"/>
-      <c r="AC2" s="59"/>
-      <c r="AD2" s="59"/>
-      <c r="AE2" s="59"/>
-      <c r="AF2" s="59"/>
+      <c r="AB2" s="57"/>
+      <c r="AC2" s="57"/>
+      <c r="AD2" s="57"/>
+      <c r="AE2" s="57"/>
+      <c r="AF2" s="57"/>
     </row>
     <row r="3" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A3" s="60"/>
@@ -1923,7 +1923,7 @@
       </c>
     </row>
     <row r="5" spans="1:34" ht="15.75" customHeight="1" thickTop="1" x14ac:dyDescent="0.35">
-      <c r="A5" s="57" t="s">
+      <c r="A5" s="58" t="s">
         <v>16</v>
       </c>
       <c r="B5" s="17"/>
@@ -1933,7 +1933,7 @@
       <c r="F5" s="19"/>
       <c r="G5" s="19"/>
       <c r="H5" s="20"/>
-      <c r="J5" s="57" t="s">
+      <c r="J5" s="58" t="s">
         <v>16</v>
       </c>
       <c r="K5" s="18" t="s">
@@ -1954,7 +1954,7 @@
       <c r="P5" s="20" t="s">
         <v>17</v>
       </c>
-      <c r="R5" s="57" t="s">
+      <c r="R5" s="58" t="s">
         <v>16</v>
       </c>
       <c r="S5" s="18" t="s">
@@ -1975,7 +1975,7 @@
       <c r="X5" s="20" t="s">
         <v>17</v>
       </c>
-      <c r="Z5" s="57" t="s">
+      <c r="Z5" s="58" t="s">
         <v>16</v>
       </c>
       <c r="AA5" s="18" t="s">
@@ -1999,8 +1999,8 @@
       <c r="AH5" s="21"/>
     </row>
     <row r="6" spans="1:34" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A6" s="57"/>
-      <c r="B6" s="58" t="s">
+      <c r="A6" s="58"/>
+      <c r="B6" s="59" t="s">
         <v>18</v>
       </c>
       <c r="C6" s="33" t="s">
@@ -2015,7 +2015,7 @@
         <v>19</v>
       </c>
       <c r="H6" s="36"/>
-      <c r="J6" s="57"/>
+      <c r="J6" s="58"/>
       <c r="K6" s="22" t="s">
         <v>20</v>
       </c>
@@ -2034,7 +2034,7 @@
       <c r="P6" s="24" t="s">
         <v>21</v>
       </c>
-      <c r="R6" s="57"/>
+      <c r="R6" s="58"/>
       <c r="S6" s="22" t="s">
         <v>21</v>
       </c>
@@ -2053,7 +2053,7 @@
       <c r="X6" s="24" t="s">
         <v>21</v>
       </c>
-      <c r="Z6" s="57"/>
+      <c r="Z6" s="58"/>
       <c r="AA6" s="22" t="s">
         <v>20</v>
       </c>
@@ -2074,15 +2074,15 @@
       </c>
     </row>
     <row r="7" spans="1:34" ht="8.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A7" s="57"/>
-      <c r="B7" s="58"/>
+      <c r="A7" s="58"/>
+      <c r="B7" s="59"/>
       <c r="C7" s="39"/>
       <c r="D7" s="42"/>
       <c r="E7" s="39"/>
       <c r="F7" s="42"/>
       <c r="G7" s="39"/>
       <c r="H7" s="42"/>
-      <c r="J7" s="57"/>
+      <c r="J7" s="58"/>
       <c r="K7" s="22" t="s">
         <v>22</v>
       </c>
@@ -2101,7 +2101,7 @@
       <c r="P7" s="24" t="s">
         <v>23</v>
       </c>
-      <c r="R7" s="57"/>
+      <c r="R7" s="58"/>
       <c r="S7" s="22" t="s">
         <v>23</v>
       </c>
@@ -2120,7 +2120,7 @@
       <c r="X7" s="24" t="s">
         <v>23</v>
       </c>
-      <c r="Z7" s="57"/>
+      <c r="Z7" s="58"/>
       <c r="AA7" s="22" t="s">
         <v>21</v>
       </c>
@@ -2141,8 +2141,8 @@
       </c>
     </row>
     <row r="8" spans="1:34" ht="27.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A8" s="57"/>
-      <c r="B8" s="58"/>
+      <c r="A8" s="58"/>
+      <c r="B8" s="59"/>
       <c r="C8" s="35" t="s">
         <v>2</v>
       </c>
@@ -2155,7 +2155,7 @@
         <v>2</v>
       </c>
       <c r="H8" s="44"/>
-      <c r="J8" s="57"/>
+      <c r="J8" s="58"/>
       <c r="K8" s="22" t="s">
         <v>21</v>
       </c>
@@ -2174,7 +2174,7 @@
       <c r="P8" s="24" t="s">
         <v>24</v>
       </c>
-      <c r="R8" s="57"/>
+      <c r="R8" s="58"/>
       <c r="S8" s="22" t="s">
         <v>25</v>
       </c>
@@ -2193,7 +2193,7 @@
       <c r="X8" s="24" t="s">
         <v>24</v>
       </c>
-      <c r="Z8" s="57"/>
+      <c r="Z8" s="58"/>
       <c r="AA8" s="22" t="s">
         <v>23</v>
       </c>
@@ -2214,7 +2214,7 @@
       </c>
     </row>
     <row r="9" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A9" s="57"/>
+      <c r="A9" s="58"/>
       <c r="B9" s="16"/>
       <c r="C9" s="48"/>
       <c r="D9" s="37"/>
@@ -2222,21 +2222,21 @@
       <c r="F9" s="38"/>
       <c r="G9" s="48"/>
       <c r="H9" s="40"/>
-      <c r="J9" s="57"/>
+      <c r="J9" s="58"/>
       <c r="K9" s="22"/>
       <c r="L9" s="23"/>
       <c r="M9" s="23"/>
       <c r="N9" s="23"/>
       <c r="O9" s="23"/>
       <c r="P9" s="24"/>
-      <c r="R9" s="57"/>
+      <c r="R9" s="58"/>
       <c r="S9" s="22"/>
       <c r="T9" s="23"/>
       <c r="U9" s="23"/>
       <c r="V9" s="23"/>
       <c r="W9" s="23"/>
       <c r="X9" s="24"/>
-      <c r="Z9" s="57"/>
+      <c r="Z9" s="58"/>
       <c r="AA9" s="22"/>
       <c r="AB9" s="23"/>
       <c r="AC9" s="23"/>
@@ -2245,8 +2245,8 @@
       <c r="AF9" s="24"/>
     </row>
     <row r="10" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A10" s="57"/>
-      <c r="B10" s="58" t="s">
+      <c r="A10" s="58"/>
+      <c r="B10" s="59" t="s">
         <v>27</v>
       </c>
       <c r="C10" s="33" t="s">
@@ -2261,7 +2261,7 @@
         <v>19</v>
       </c>
       <c r="H10" s="36"/>
-      <c r="J10" s="57"/>
+      <c r="J10" s="58"/>
       <c r="K10" s="22" t="s">
         <v>24</v>
       </c>
@@ -2280,7 +2280,7 @@
       <c r="P10" s="24" t="s">
         <v>26</v>
       </c>
-      <c r="R10" s="57"/>
+      <c r="R10" s="58"/>
       <c r="S10" s="22" t="s">
         <v>28</v>
       </c>
@@ -2299,7 +2299,7 @@
       <c r="X10" s="24" t="s">
         <v>26</v>
       </c>
-      <c r="Z10" s="57"/>
+      <c r="Z10" s="58"/>
       <c r="AA10" s="22" t="s">
         <v>25</v>
       </c>
@@ -2320,15 +2320,15 @@
       </c>
     </row>
     <row r="11" spans="1:34" ht="6.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A11" s="57"/>
-      <c r="B11" s="58"/>
+      <c r="A11" s="58"/>
+      <c r="B11" s="59"/>
       <c r="C11" s="39"/>
       <c r="D11" s="42"/>
       <c r="E11" s="39"/>
       <c r="F11" s="42"/>
       <c r="G11" s="39"/>
       <c r="H11" s="42"/>
-      <c r="J11" s="57"/>
+      <c r="J11" s="58"/>
       <c r="K11" s="22" t="s">
         <v>25</v>
       </c>
@@ -2347,7 +2347,7 @@
       <c r="P11" s="24" t="s">
         <v>28</v>
       </c>
-      <c r="R11" s="57"/>
+      <c r="R11" s="58"/>
       <c r="S11" s="22" t="s">
         <v>30</v>
       </c>
@@ -2366,7 +2366,7 @@
       <c r="X11" s="24" t="s">
         <v>30</v>
       </c>
-      <c r="Z11" s="57"/>
+      <c r="Z11" s="58"/>
       <c r="AA11" s="22" t="s">
         <v>26</v>
       </c>
@@ -2387,8 +2387,8 @@
       </c>
     </row>
     <row r="12" spans="1:34" ht="24.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A12" s="57"/>
-      <c r="B12" s="58"/>
+      <c r="A12" s="58"/>
+      <c r="B12" s="59"/>
       <c r="C12" s="45" t="s">
         <v>2</v>
       </c>
@@ -2401,7 +2401,7 @@
         <v>2</v>
       </c>
       <c r="H12" s="44"/>
-      <c r="J12" s="57"/>
+      <c r="J12" s="58"/>
       <c r="K12" s="22" t="s">
         <v>26</v>
       </c>
@@ -2420,7 +2420,7 @@
       <c r="P12" s="24" t="s">
         <v>30</v>
       </c>
-      <c r="R12" s="57"/>
+      <c r="R12" s="58"/>
       <c r="S12" s="22" t="s">
         <v>33</v>
       </c>
@@ -2439,7 +2439,7 @@
       <c r="X12" s="24" t="s">
         <v>29</v>
       </c>
-      <c r="Z12" s="57"/>
+      <c r="Z12" s="58"/>
       <c r="AA12" s="22" t="s">
         <v>28</v>
       </c>
@@ -2460,7 +2460,7 @@
       </c>
     </row>
     <row r="13" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A13" s="57"/>
+      <c r="A13" s="58"/>
       <c r="B13" s="16"/>
       <c r="C13" s="48"/>
       <c r="D13" s="49"/>
@@ -2468,7 +2468,7 @@
       <c r="F13" s="49"/>
       <c r="G13" s="48"/>
       <c r="H13" s="50"/>
-      <c r="J13" s="57"/>
+      <c r="J13" s="58"/>
       <c r="K13" s="22" t="s">
         <v>28</v>
       </c>
@@ -2487,7 +2487,7 @@
       <c r="P13" s="24" t="s">
         <v>29</v>
       </c>
-      <c r="R13" s="57"/>
+      <c r="R13" s="58"/>
       <c r="S13" s="22" t="s">
         <v>36</v>
       </c>
@@ -2506,7 +2506,7 @@
       <c r="X13" s="24" t="s">
         <v>38</v>
       </c>
-      <c r="Z13" s="57"/>
+      <c r="Z13" s="58"/>
       <c r="AA13" s="22" t="s">
         <v>30</v>
       </c>
@@ -2527,8 +2527,8 @@
       </c>
     </row>
     <row r="14" spans="1:34" ht="18" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A14" s="57"/>
-      <c r="B14" s="58" t="s">
+      <c r="A14" s="58"/>
+      <c r="B14" s="59" t="s">
         <v>40</v>
       </c>
       <c r="C14" s="33" t="s">
@@ -2543,7 +2543,7 @@
         <v>19</v>
       </c>
       <c r="H14" s="36"/>
-      <c r="J14" s="57"/>
+      <c r="J14" s="58"/>
       <c r="K14" s="22" t="s">
         <v>30</v>
       </c>
@@ -2562,7 +2562,7 @@
       <c r="P14" s="24" t="s">
         <v>38</v>
       </c>
-      <c r="R14" s="57"/>
+      <c r="R14" s="58"/>
       <c r="S14" s="22" t="s">
         <v>39</v>
       </c>
@@ -2579,7 +2579,7 @@
       <c r="X14" s="24" t="s">
         <v>33</v>
       </c>
-      <c r="Z14" s="57"/>
+      <c r="Z14" s="58"/>
       <c r="AA14" s="22" t="s">
         <v>38</v>
       </c>
@@ -2600,15 +2600,15 @@
       </c>
     </row>
     <row r="15" spans="1:34" ht="8.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A15" s="57"/>
-      <c r="B15" s="58"/>
+      <c r="A15" s="58"/>
+      <c r="B15" s="59"/>
       <c r="C15" s="39"/>
       <c r="D15" s="42"/>
       <c r="E15" s="39"/>
       <c r="F15" s="42"/>
       <c r="G15" s="39"/>
       <c r="H15" s="42"/>
-      <c r="J15" s="57"/>
+      <c r="J15" s="58"/>
       <c r="K15" s="22" t="s">
         <v>38</v>
       </c>
@@ -2627,7 +2627,7 @@
       <c r="P15" s="24" t="s">
         <v>33</v>
       </c>
-      <c r="R15" s="57"/>
+      <c r="R15" s="58"/>
       <c r="S15" s="22" t="s">
         <v>42</v>
       </c>
@@ -2642,7 +2642,7 @@
       <c r="X15" s="24" t="s">
         <v>36</v>
       </c>
-      <c r="Z15" s="57"/>
+      <c r="Z15" s="58"/>
       <c r="AA15" s="22" t="s">
         <v>33</v>
       </c>
@@ -2663,8 +2663,8 @@
       </c>
     </row>
     <row r="16" spans="1:34" ht="23.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A16" s="57"/>
-      <c r="B16" s="58"/>
+      <c r="A16" s="58"/>
+      <c r="B16" s="59"/>
       <c r="C16" s="45" t="s">
         <v>2</v>
       </c>
@@ -2677,7 +2677,7 @@
         <v>2</v>
       </c>
       <c r="H16" s="44"/>
-      <c r="J16" s="57"/>
+      <c r="J16" s="58"/>
       <c r="K16" s="22" t="s">
         <v>33</v>
       </c>
@@ -2696,7 +2696,7 @@
       <c r="P16" s="24" t="s">
         <v>36</v>
       </c>
-      <c r="R16" s="57"/>
+      <c r="R16" s="58"/>
       <c r="S16" s="22"/>
       <c r="T16" s="23" t="s">
         <v>36</v>
@@ -2707,7 +2707,7 @@
       <c r="X16" s="24" t="s">
         <v>41</v>
       </c>
-      <c r="Z16" s="57"/>
+      <c r="Z16" s="58"/>
       <c r="AA16" s="22" t="s">
         <v>37</v>
       </c>
@@ -2724,7 +2724,7 @@
       </c>
     </row>
     <row r="17" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A17" s="57"/>
+      <c r="A17" s="58"/>
       <c r="B17" s="16"/>
       <c r="C17" s="48"/>
       <c r="D17" s="49"/>
@@ -2732,7 +2732,7 @@
       <c r="F17" s="49"/>
       <c r="G17" s="48"/>
       <c r="H17" s="50"/>
-      <c r="J17" s="57"/>
+      <c r="J17" s="58"/>
       <c r="K17" s="22" t="s">
         <v>37</v>
       </c>
@@ -2751,7 +2751,7 @@
       <c r="P17" s="24" t="s">
         <v>39</v>
       </c>
-      <c r="R17" s="57"/>
+      <c r="R17" s="58"/>
       <c r="S17" s="25"/>
       <c r="T17" s="26" t="s">
         <v>42</v>
@@ -2760,7 +2760,7 @@
       <c r="V17" s="26"/>
       <c r="W17" s="26"/>
       <c r="X17" s="27"/>
-      <c r="Z17" s="57"/>
+      <c r="Z17" s="58"/>
       <c r="AA17" s="22" t="s">
         <v>36</v>
       </c>
@@ -2775,8 +2775,8 @@
       <c r="AF17" s="24"/>
     </row>
     <row r="18" spans="1:32" ht="18" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A18" s="57"/>
-      <c r="B18" s="58" t="s">
+      <c r="A18" s="58"/>
+      <c r="B18" s="59" t="s">
         <v>43</v>
       </c>
       <c r="C18" s="33" t="s">
@@ -2791,7 +2791,7 @@
         <v>19</v>
       </c>
       <c r="H18" s="36"/>
-      <c r="J18" s="57"/>
+      <c r="J18" s="58"/>
       <c r="K18" s="22" t="s">
         <v>36</v>
       </c>
@@ -2815,7 +2815,7 @@
       <c r="V18" s="21"/>
       <c r="W18" s="21"/>
       <c r="X18" s="21"/>
-      <c r="Z18" s="57"/>
+      <c r="Z18" s="58"/>
       <c r="AA18" s="25" t="s">
         <v>39</v>
       </c>
@@ -2828,15 +2828,15 @@
       <c r="AF18" s="27"/>
     </row>
     <row r="19" spans="1:32" ht="6.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A19" s="57"/>
-      <c r="B19" s="58"/>
+      <c r="A19" s="58"/>
+      <c r="B19" s="59"/>
       <c r="C19" s="39"/>
       <c r="D19" s="42"/>
       <c r="E19" s="39"/>
       <c r="F19" s="42"/>
       <c r="G19" s="39"/>
       <c r="H19" s="42"/>
-      <c r="J19" s="57"/>
+      <c r="J19" s="58"/>
       <c r="K19" s="22" t="s">
         <v>39</v>
       </c>
@@ -2869,8 +2869,8 @@
       <c r="AF19" s="21"/>
     </row>
     <row r="20" spans="1:32" ht="28.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A20" s="57"/>
-      <c r="B20" s="58"/>
+      <c r="A20" s="58"/>
+      <c r="B20" s="59"/>
       <c r="C20" s="45" t="s">
         <v>2</v>
       </c>
@@ -2883,7 +2883,7 @@
         <v>2</v>
       </c>
       <c r="H20" s="47"/>
-      <c r="J20" s="57"/>
+      <c r="J20" s="58"/>
       <c r="K20" s="22" t="s">
         <v>42</v>
       </c>
@@ -2998,7 +2998,7 @@
       </c>
     </row>
     <row r="22" spans="1:32" ht="15.75" hidden="1" customHeight="1" thickTop="1" x14ac:dyDescent="0.35">
-      <c r="A22" s="57" t="s">
+      <c r="A22" s="58" t="s">
         <v>16</v>
       </c>
       <c r="B22" s="17"/>
@@ -3020,7 +3020,7 @@
       <c r="H22" s="20" t="s">
         <v>17</v>
       </c>
-      <c r="J22" s="57" t="s">
+      <c r="J22" s="58" t="s">
         <v>16</v>
       </c>
       <c r="K22" s="18" t="s">
@@ -3041,7 +3041,7 @@
       <c r="P22" s="20" t="s">
         <v>20</v>
       </c>
-      <c r="R22" s="57" t="s">
+      <c r="R22" s="58" t="s">
         <v>16</v>
       </c>
       <c r="S22" s="18" t="s">
@@ -3062,7 +3062,7 @@
       <c r="X22" s="20" t="s">
         <v>20</v>
       </c>
-      <c r="Z22" s="57" t="s">
+      <c r="Z22" s="58" t="s">
         <v>16</v>
       </c>
       <c r="AA22" s="29" t="s">
@@ -3075,7 +3075,7 @@
       <c r="AF22" s="21"/>
     </row>
     <row r="23" spans="1:32" ht="17.25" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A23" s="57"/>
+      <c r="A23" s="58"/>
       <c r="B23" s="17"/>
       <c r="C23" s="22" t="s">
         <v>21</v>
@@ -3095,7 +3095,7 @@
       <c r="H23" s="24" t="s">
         <v>20</v>
       </c>
-      <c r="J23" s="57"/>
+      <c r="J23" s="58"/>
       <c r="K23" s="22" t="s">
         <v>20</v>
       </c>
@@ -3114,7 +3114,7 @@
       <c r="P23" s="24" t="s">
         <v>24</v>
       </c>
-      <c r="R23" s="57"/>
+      <c r="R23" s="58"/>
       <c r="S23" s="22" t="s">
         <v>22</v>
       </c>
@@ -3133,7 +3133,7 @@
       <c r="X23" s="24" t="s">
         <v>24</v>
       </c>
-      <c r="Z23" s="57"/>
+      <c r="Z23" s="58"/>
       <c r="AA23" s="30" t="s">
         <v>25</v>
       </c>
@@ -3144,7 +3144,7 @@
       <c r="AF23" s="21"/>
     </row>
     <row r="24" spans="1:32" ht="17.25" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A24" s="57"/>
+      <c r="A24" s="58"/>
       <c r="B24" s="17"/>
       <c r="C24" s="22" t="s">
         <v>23</v>
@@ -3164,7 +3164,7 @@
       <c r="H24" s="24" t="s">
         <v>21</v>
       </c>
-      <c r="J24" s="57"/>
+      <c r="J24" s="58"/>
       <c r="K24" s="22" t="s">
         <v>23</v>
       </c>
@@ -3183,7 +3183,7 @@
       <c r="P24" s="24" t="s">
         <v>25</v>
       </c>
-      <c r="R24" s="57"/>
+      <c r="R24" s="58"/>
       <c r="S24" s="22" t="s">
         <v>23</v>
       </c>
@@ -3202,7 +3202,7 @@
       <c r="X24" s="24" t="s">
         <v>25</v>
       </c>
-      <c r="Z24" s="57"/>
+      <c r="Z24" s="58"/>
       <c r="AA24" s="30" t="s">
         <v>26</v>
       </c>
@@ -3213,7 +3213,7 @@
       <c r="AF24" s="21"/>
     </row>
     <row r="25" spans="1:32" ht="17.25" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A25" s="57"/>
+      <c r="A25" s="58"/>
       <c r="B25" s="17"/>
       <c r="C25" s="22" t="s">
         <v>25</v>
@@ -3233,7 +3233,7 @@
       <c r="H25" s="24" t="s">
         <v>48</v>
       </c>
-      <c r="J25" s="57"/>
+      <c r="J25" s="58"/>
       <c r="K25" s="22" t="s">
         <v>24</v>
       </c>
@@ -3252,7 +3252,7 @@
       <c r="P25" s="24" t="s">
         <v>26</v>
       </c>
-      <c r="R25" s="57"/>
+      <c r="R25" s="58"/>
       <c r="S25" s="22" t="s">
         <v>25</v>
       </c>
@@ -3271,7 +3271,7 @@
       <c r="X25" s="24" t="s">
         <v>26</v>
       </c>
-      <c r="Z25" s="57"/>
+      <c r="Z25" s="58"/>
       <c r="AA25" s="30" t="s">
         <v>30</v>
       </c>
@@ -3282,7 +3282,7 @@
       <c r="AF25" s="21"/>
     </row>
     <row r="26" spans="1:32" ht="17.25" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A26" s="57"/>
+      <c r="A26" s="58"/>
       <c r="B26" s="17"/>
       <c r="C26" s="22" t="s">
         <v>26</v>
@@ -3302,7 +3302,7 @@
       <c r="H26" s="24" t="s">
         <v>24</v>
       </c>
-      <c r="J26" s="57"/>
+      <c r="J26" s="58"/>
       <c r="K26" s="22" t="s">
         <v>25</v>
       </c>
@@ -3321,7 +3321,7 @@
       <c r="P26" s="24" t="s">
         <v>32</v>
       </c>
-      <c r="R26" s="57"/>
+      <c r="R26" s="58"/>
       <c r="S26" s="22" t="s">
         <v>26</v>
       </c>
@@ -3340,7 +3340,7 @@
       <c r="X26" s="24" t="s">
         <v>28</v>
       </c>
-      <c r="Z26" s="57"/>
+      <c r="Z26" s="58"/>
       <c r="AA26" s="30" t="s">
         <v>29</v>
       </c>
@@ -3351,7 +3351,7 @@
       <c r="AF26" s="21"/>
     </row>
     <row r="27" spans="1:32" ht="17.25" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A27" s="57"/>
+      <c r="A27" s="58"/>
       <c r="B27" s="17"/>
       <c r="C27" s="22" t="s">
         <v>49</v>
@@ -3371,7 +3371,7 @@
       <c r="H27" s="24" t="s">
         <v>25</v>
       </c>
-      <c r="J27" s="57"/>
+      <c r="J27" s="58"/>
       <c r="K27" s="22" t="s">
         <v>26</v>
       </c>
@@ -3390,7 +3390,7 @@
       <c r="P27" s="24" t="s">
         <v>33</v>
       </c>
-      <c r="R27" s="57"/>
+      <c r="R27" s="58"/>
       <c r="S27" s="22" t="s">
         <v>32</v>
       </c>
@@ -3409,7 +3409,7 @@
       <c r="X27" s="24" t="s">
         <v>32</v>
       </c>
-      <c r="Z27" s="57"/>
+      <c r="Z27" s="58"/>
       <c r="AA27" s="30" t="s">
         <v>36</v>
       </c>
@@ -3420,7 +3420,7 @@
       <c r="AF27" s="21"/>
     </row>
     <row r="28" spans="1:32" ht="17.25" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A28" s="57"/>
+      <c r="A28" s="58"/>
       <c r="B28" s="17"/>
       <c r="C28" s="22" t="s">
         <v>31</v>
@@ -3440,7 +3440,7 @@
       <c r="H28" s="24" t="s">
         <v>26</v>
       </c>
-      <c r="J28" s="57"/>
+      <c r="J28" s="58"/>
       <c r="K28" s="22" t="s">
         <v>32</v>
       </c>
@@ -3459,7 +3459,7 @@
       <c r="P28" s="24" t="s">
         <v>36</v>
       </c>
-      <c r="R28" s="57"/>
+      <c r="R28" s="58"/>
       <c r="S28" s="22" t="s">
         <v>31</v>
       </c>
@@ -3478,7 +3478,7 @@
       <c r="X28" s="24" t="s">
         <v>33</v>
       </c>
-      <c r="Z28" s="57"/>
+      <c r="Z28" s="58"/>
       <c r="AA28" s="31" t="s">
         <v>39</v>
       </c>
@@ -3489,7 +3489,7 @@
       <c r="AF28" s="21"/>
     </row>
     <row r="29" spans="1:32" ht="17.25" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A29" s="57"/>
+      <c r="A29" s="58"/>
       <c r="B29" s="17"/>
       <c r="C29" s="22" t="s">
         <v>30</v>
@@ -3509,7 +3509,7 @@
       <c r="H29" s="24" t="s">
         <v>28</v>
       </c>
-      <c r="J29" s="57"/>
+      <c r="J29" s="58"/>
       <c r="K29" s="22" t="s">
         <v>31</v>
       </c>
@@ -3528,7 +3528,7 @@
       <c r="P29" s="24" t="s">
         <v>39</v>
       </c>
-      <c r="R29" s="57"/>
+      <c r="R29" s="58"/>
       <c r="S29" s="22" t="s">
         <v>30</v>
       </c>
@@ -3556,7 +3556,7 @@
       <c r="AF29" s="21"/>
     </row>
     <row r="30" spans="1:32" ht="17.25" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A30" s="57"/>
+      <c r="A30" s="58"/>
       <c r="B30" s="17"/>
       <c r="C30" s="22" t="s">
         <v>33</v>
@@ -3576,7 +3576,7 @@
       <c r="H30" s="24" t="s">
         <v>32</v>
       </c>
-      <c r="J30" s="57"/>
+      <c r="J30" s="58"/>
       <c r="K30" s="22" t="s">
         <v>30</v>
       </c>
@@ -3591,7 +3591,7 @@
         <v>37</v>
       </c>
       <c r="P30" s="24"/>
-      <c r="R30" s="57"/>
+      <c r="R30" s="58"/>
       <c r="S30" s="22" t="s">
         <v>33</v>
       </c>
@@ -3613,7 +3613,7 @@
       <c r="AF30" s="21"/>
     </row>
     <row r="31" spans="1:32" ht="17.25" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A31" s="57"/>
+      <c r="A31" s="58"/>
       <c r="B31" s="17"/>
       <c r="C31" s="22" t="s">
         <v>37</v>
@@ -3633,7 +3633,7 @@
       <c r="H31" s="24" t="s">
         <v>29</v>
       </c>
-      <c r="J31" s="57"/>
+      <c r="J31" s="58"/>
       <c r="K31" s="22" t="s">
         <v>33</v>
       </c>
@@ -3648,7 +3648,7 @@
         <v>36</v>
       </c>
       <c r="P31" s="24"/>
-      <c r="R31" s="57"/>
+      <c r="R31" s="58"/>
       <c r="S31" s="22" t="s">
         <v>36</v>
       </c>
@@ -3668,7 +3668,7 @@
       <c r="AF31" s="21"/>
     </row>
     <row r="32" spans="1:32" ht="17.25" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A32" s="57"/>
+      <c r="A32" s="58"/>
       <c r="B32" s="17"/>
       <c r="C32" s="22" t="s">
         <v>36</v>
@@ -3688,7 +3688,7 @@
       <c r="H32" s="24" t="s">
         <v>33</v>
       </c>
-      <c r="J32" s="57"/>
+      <c r="J32" s="58"/>
       <c r="K32" s="22" t="s">
         <v>37</v>
       </c>
@@ -3699,7 +3699,7 @@
       <c r="N32" s="23"/>
       <c r="O32" s="23"/>
       <c r="P32" s="24"/>
-      <c r="R32" s="57"/>
+      <c r="R32" s="58"/>
       <c r="S32" s="22" t="s">
         <v>39</v>
       </c>
@@ -3717,7 +3717,7 @@
       <c r="AF32" s="21"/>
     </row>
     <row r="33" spans="1:32" ht="17.25" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A33" s="57"/>
+      <c r="A33" s="58"/>
       <c r="B33" s="17"/>
       <c r="C33" s="22" t="s">
         <v>39</v>
@@ -3737,7 +3737,7 @@
       <c r="H33" s="24" t="s">
         <v>37</v>
       </c>
-      <c r="J33" s="57"/>
+      <c r="J33" s="58"/>
       <c r="K33" s="22" t="s">
         <v>36</v>
       </c>
@@ -3748,7 +3748,7 @@
       <c r="N33" s="23"/>
       <c r="O33" s="23"/>
       <c r="P33" s="24"/>
-      <c r="R33" s="57"/>
+      <c r="R33" s="58"/>
       <c r="S33" s="25" t="s">
         <v>42</v>
       </c>
@@ -3766,7 +3766,7 @@
       <c r="AF33" s="21"/>
     </row>
     <row r="34" spans="1:32" ht="17.25" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A34" s="57"/>
+      <c r="A34" s="58"/>
       <c r="B34" s="17"/>
       <c r="C34" s="22"/>
       <c r="D34" s="23" t="s">
@@ -3784,7 +3784,7 @@
       <c r="H34" s="24" t="s">
         <v>36</v>
       </c>
-      <c r="J34" s="57"/>
+      <c r="J34" s="58"/>
       <c r="K34" s="25" t="s">
         <v>39</v>
       </c>
@@ -3809,7 +3809,7 @@
       <c r="AF34" s="21"/>
     </row>
     <row r="35" spans="1:32" ht="17.25" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A35" s="57"/>
+      <c r="A35" s="58"/>
       <c r="B35" s="17"/>
       <c r="C35" s="22"/>
       <c r="D35" s="23" t="s">
@@ -3848,7 +3848,7 @@
       <c r="AF35" s="21"/>
     </row>
     <row r="36" spans="1:32" ht="17.25" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A36" s="57"/>
+      <c r="A36" s="58"/>
       <c r="B36" s="17"/>
       <c r="C36" s="22"/>
       <c r="D36" s="23"/>
@@ -3885,7 +3885,7 @@
       <c r="AF36" s="21"/>
     </row>
     <row r="37" spans="1:32" ht="17.25" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A37" s="57"/>
+      <c r="A37" s="58"/>
       <c r="B37" s="17"/>
       <c r="C37" s="25"/>
       <c r="D37" s="26"/>
@@ -4009,7 +4009,7 @@
       </c>
     </row>
     <row r="40" spans="1:32" ht="15.75" hidden="1" customHeight="1" thickTop="1" x14ac:dyDescent="0.35">
-      <c r="A40" s="57" t="s">
+      <c r="A40" s="58" t="s">
         <v>16</v>
       </c>
       <c r="B40" s="17"/>
@@ -4031,7 +4031,7 @@
       <c r="H40" s="20" t="s">
         <v>17</v>
       </c>
-      <c r="J40" s="57" t="s">
+      <c r="J40" s="58" t="s">
         <v>16</v>
       </c>
       <c r="K40" s="18" t="s">
@@ -4052,7 +4052,7 @@
       <c r="P40" s="20" t="s">
         <v>20</v>
       </c>
-      <c r="R40" s="57" t="s">
+      <c r="R40" s="58" t="s">
         <v>16</v>
       </c>
       <c r="S40" s="18" t="s">
@@ -4076,7 +4076,7 @@
       <c r="Z40" s="32"/>
     </row>
     <row r="41" spans="1:32" ht="17.25" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A41" s="57"/>
+      <c r="A41" s="58"/>
       <c r="B41" s="17"/>
       <c r="C41" s="22" t="s">
         <v>20</v>
@@ -4096,7 +4096,7 @@
       <c r="H41" s="24" t="s">
         <v>20</v>
       </c>
-      <c r="J41" s="57"/>
+      <c r="J41" s="58"/>
       <c r="K41" s="22" t="s">
         <v>20</v>
       </c>
@@ -4115,7 +4115,7 @@
       <c r="P41" s="24" t="s">
         <v>22</v>
       </c>
-      <c r="R41" s="57"/>
+      <c r="R41" s="58"/>
       <c r="S41" s="22" t="s">
         <v>20</v>
       </c>
@@ -4137,7 +4137,7 @@
       <c r="Z41" s="32"/>
     </row>
     <row r="42" spans="1:32" ht="17.25" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A42" s="57"/>
+      <c r="A42" s="58"/>
       <c r="B42" s="17"/>
       <c r="C42" s="22" t="s">
         <v>21</v>
@@ -4157,7 +4157,7 @@
       <c r="H42" s="24" t="s">
         <v>22</v>
       </c>
-      <c r="J42" s="57"/>
+      <c r="J42" s="58"/>
       <c r="K42" s="22" t="s">
         <v>21</v>
       </c>
@@ -4176,7 +4176,7 @@
       <c r="P42" s="24" t="s">
         <v>25</v>
       </c>
-      <c r="R42" s="57"/>
+      <c r="R42" s="58"/>
       <c r="S42" s="22" t="s">
         <v>22</v>
       </c>
@@ -4198,7 +4198,7 @@
       <c r="Z42" s="32"/>
     </row>
     <row r="43" spans="1:32" ht="17.25" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A43" s="57"/>
+      <c r="A43" s="58"/>
       <c r="B43" s="17"/>
       <c r="C43" s="22" t="s">
         <v>23</v>
@@ -4218,7 +4218,7 @@
       <c r="H43" s="24" t="s">
         <v>48</v>
       </c>
-      <c r="J43" s="57"/>
+      <c r="J43" s="58"/>
       <c r="K43" s="22" t="s">
         <v>23</v>
       </c>
@@ -4237,7 +4237,7 @@
       <c r="P43" s="24" t="s">
         <v>26</v>
       </c>
-      <c r="R43" s="57"/>
+      <c r="R43" s="58"/>
       <c r="S43" s="22" t="s">
         <v>21</v>
       </c>
@@ -4259,7 +4259,7 @@
       <c r="Z43" s="32"/>
     </row>
     <row r="44" spans="1:32" ht="17.25" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A44" s="57"/>
+      <c r="A44" s="58"/>
       <c r="B44" s="17"/>
       <c r="C44" s="22" t="s">
         <v>48</v>
@@ -4279,7 +4279,7 @@
       <c r="H44" s="24" t="s">
         <v>24</v>
       </c>
-      <c r="J44" s="57"/>
+      <c r="J44" s="58"/>
       <c r="K44" s="22" t="s">
         <v>25</v>
       </c>
@@ -4298,7 +4298,7 @@
       <c r="P44" s="24" t="s">
         <v>38</v>
       </c>
-      <c r="R44" s="57"/>
+      <c r="R44" s="58"/>
       <c r="S44" s="22" t="s">
         <v>23</v>
       </c>
@@ -4320,7 +4320,7 @@
       <c r="Z44" s="32"/>
     </row>
     <row r="45" spans="1:32" ht="17.25" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A45" s="57"/>
+      <c r="A45" s="58"/>
       <c r="B45" s="17"/>
       <c r="C45" s="22" t="s">
         <v>24</v>
@@ -4340,7 +4340,7 @@
       <c r="H45" s="24" t="s">
         <v>25</v>
       </c>
-      <c r="J45" s="57"/>
+      <c r="J45" s="58"/>
       <c r="K45" s="22" t="s">
         <v>26</v>
       </c>
@@ -4359,7 +4359,7 @@
       <c r="P45" s="24" t="s">
         <v>33</v>
       </c>
-      <c r="R45" s="57"/>
+      <c r="R45" s="58"/>
       <c r="S45" s="22" t="s">
         <v>24</v>
       </c>
@@ -4381,7 +4381,7 @@
       <c r="Z45" s="32"/>
     </row>
     <row r="46" spans="1:32" ht="17.25" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A46" s="57"/>
+      <c r="A46" s="58"/>
       <c r="B46" s="17"/>
       <c r="C46" s="22" t="s">
         <v>25</v>
@@ -4401,7 +4401,7 @@
       <c r="H46" s="24" t="s">
         <v>26</v>
       </c>
-      <c r="J46" s="57"/>
+      <c r="J46" s="58"/>
       <c r="K46" s="22" t="s">
         <v>33</v>
       </c>
@@ -4420,7 +4420,7 @@
       <c r="P46" s="24" t="s">
         <v>36</v>
       </c>
-      <c r="R46" s="57"/>
+      <c r="R46" s="58"/>
       <c r="S46" s="22" t="s">
         <v>25</v>
       </c>
@@ -4442,7 +4442,7 @@
       <c r="Z46" s="32"/>
     </row>
     <row r="47" spans="1:32" ht="17.25" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A47" s="57"/>
+      <c r="A47" s="58"/>
       <c r="B47" s="17"/>
       <c r="C47" s="22" t="s">
         <v>26</v>
@@ -4462,7 +4462,7 @@
       <c r="H47" s="24" t="s">
         <v>28</v>
       </c>
-      <c r="J47" s="57"/>
+      <c r="J47" s="58"/>
       <c r="K47" s="22" t="s">
         <v>36</v>
       </c>
@@ -4477,7 +4477,7 @@
         <v>33</v>
       </c>
       <c r="P47" s="24"/>
-      <c r="R47" s="57"/>
+      <c r="R47" s="58"/>
       <c r="S47" s="22" t="s">
         <v>26</v>
       </c>
@@ -4499,7 +4499,7 @@
       <c r="Z47" s="32"/>
     </row>
     <row r="48" spans="1:32" ht="17.25" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A48" s="57"/>
+      <c r="A48" s="58"/>
       <c r="B48" s="17"/>
       <c r="C48" s="22" t="s">
         <v>28</v>
@@ -4519,7 +4519,7 @@
       <c r="H48" s="24" t="s">
         <v>32</v>
       </c>
-      <c r="J48" s="57"/>
+      <c r="J48" s="58"/>
       <c r="K48" s="22" t="s">
         <v>39</v>
       </c>
@@ -4530,7 +4530,7 @@
         <v>37</v>
       </c>
       <c r="P48" s="24"/>
-      <c r="R48" s="57"/>
+      <c r="R48" s="58"/>
       <c r="S48" s="22" t="s">
         <v>28</v>
       </c>
@@ -4550,7 +4550,7 @@
       <c r="Z48" s="32"/>
     </row>
     <row r="49" spans="1:26" ht="17.25" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A49" s="57"/>
+      <c r="A49" s="58"/>
       <c r="B49" s="17"/>
       <c r="C49" s="22" t="s">
         <v>31</v>
@@ -4570,7 +4570,7 @@
       <c r="H49" s="24" t="s">
         <v>38</v>
       </c>
-      <c r="J49" s="57"/>
+      <c r="J49" s="58"/>
       <c r="K49" s="22"/>
       <c r="L49" s="23"/>
       <c r="M49" s="23"/>
@@ -4579,7 +4579,7 @@
         <v>36</v>
       </c>
       <c r="P49" s="24"/>
-      <c r="R49" s="57"/>
+      <c r="R49" s="58"/>
       <c r="S49" s="22" t="s">
         <v>30</v>
       </c>
@@ -4597,7 +4597,7 @@
       <c r="Z49" s="32"/>
     </row>
     <row r="50" spans="1:26" ht="17.25" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A50" s="57"/>
+      <c r="A50" s="58"/>
       <c r="B50" s="17"/>
       <c r="C50" s="22" t="s">
         <v>29</v>
@@ -4617,7 +4617,7 @@
       <c r="H50" s="24" t="s">
         <v>33</v>
       </c>
-      <c r="J50" s="57"/>
+      <c r="J50" s="58"/>
       <c r="K50" s="25"/>
       <c r="L50" s="26"/>
       <c r="M50" s="26"/>
@@ -4626,7 +4626,7 @@
         <v>42</v>
       </c>
       <c r="P50" s="27"/>
-      <c r="R50" s="57"/>
+      <c r="R50" s="58"/>
       <c r="S50" s="22" t="s">
         <v>33</v>
       </c>
@@ -4642,7 +4642,7 @@
       <c r="Z50" s="32"/>
     </row>
     <row r="51" spans="1:26" ht="17.25" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A51" s="57"/>
+      <c r="A51" s="58"/>
       <c r="B51" s="17"/>
       <c r="C51" s="22" t="s">
         <v>38</v>
@@ -4669,7 +4669,7 @@
       <c r="N51" s="21"/>
       <c r="O51" s="21"/>
       <c r="P51" s="21"/>
-      <c r="R51" s="57"/>
+      <c r="R51" s="58"/>
       <c r="S51" s="22" t="s">
         <v>36</v>
       </c>
@@ -4684,7 +4684,7 @@
       </c>
     </row>
     <row r="52" spans="1:26" ht="17.25" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A52" s="57"/>
+      <c r="A52" s="58"/>
       <c r="B52" s="17"/>
       <c r="C52" s="22" t="s">
         <v>33</v>
@@ -4711,7 +4711,7 @@
       <c r="N52" s="21"/>
       <c r="O52" s="21"/>
       <c r="P52" s="21"/>
-      <c r="R52" s="57"/>
+      <c r="R52" s="58"/>
       <c r="S52" s="25" t="s">
         <v>39</v>
       </c>
@@ -4724,7 +4724,7 @@
       <c r="X52" s="27"/>
     </row>
     <row r="53" spans="1:26" ht="17.25" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A53" s="57"/>
+      <c r="A53" s="58"/>
       <c r="B53" s="17"/>
       <c r="C53" s="22" t="s">
         <v>36</v>
@@ -4756,7 +4756,7 @@
       <c r="X53" s="21"/>
     </row>
     <row r="54" spans="1:26" ht="17.25" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A54" s="57"/>
+      <c r="A54" s="58"/>
       <c r="B54" s="17"/>
       <c r="C54" s="22" t="s">
         <v>39</v>
@@ -4786,7 +4786,7 @@
       <c r="X54" s="21"/>
     </row>
     <row r="55" spans="1:26" ht="17.25" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A55" s="57"/>
+      <c r="A55" s="58"/>
       <c r="B55" s="17"/>
       <c r="C55" s="25" t="s">
         <v>42</v>
@@ -4897,7 +4897,7 @@
       </c>
     </row>
     <row r="58" spans="1:26" ht="15" hidden="1" customHeight="1" thickTop="1" x14ac:dyDescent="0.35">
-      <c r="A58" s="57" t="s">
+      <c r="A58" s="58" t="s">
         <v>16</v>
       </c>
       <c r="B58" s="17"/>
@@ -4919,7 +4919,7 @@
       <c r="H58" s="20" t="s">
         <v>17</v>
       </c>
-      <c r="J58" s="57" t="s">
+      <c r="J58" s="58" t="s">
         <v>16</v>
       </c>
       <c r="K58" s="18" t="s">
@@ -4940,7 +4940,7 @@
       <c r="P58" s="20" t="s">
         <v>20</v>
       </c>
-      <c r="R58" s="57" t="s">
+      <c r="R58" s="58" t="s">
         <v>16</v>
       </c>
       <c r="S58" s="18" t="s">
@@ -4964,7 +4964,7 @@
       <c r="Z58" s="28"/>
     </row>
     <row r="59" spans="1:26" ht="17.25" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A59" s="57"/>
+      <c r="A59" s="58"/>
       <c r="B59" s="17"/>
       <c r="C59" s="22" t="s">
         <v>23</v>
@@ -4984,7 +4984,7 @@
       <c r="H59" s="24" t="s">
         <v>20</v>
       </c>
-      <c r="J59" s="57"/>
+      <c r="J59" s="58"/>
       <c r="K59" s="22" t="s">
         <v>23</v>
       </c>
@@ -5003,7 +5003,7 @@
       <c r="P59" s="24" t="s">
         <v>24</v>
       </c>
-      <c r="R59" s="57"/>
+      <c r="R59" s="58"/>
       <c r="S59" s="22" t="s">
         <v>25</v>
       </c>
@@ -5025,7 +5025,7 @@
       <c r="Z59" s="28"/>
     </row>
     <row r="60" spans="1:26" ht="17.25" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A60" s="57"/>
+      <c r="A60" s="58"/>
       <c r="B60" s="17"/>
       <c r="C60" s="22" t="s">
         <v>24</v>
@@ -5045,7 +5045,7 @@
       <c r="H60" s="24" t="s">
         <v>21</v>
       </c>
-      <c r="J60" s="57"/>
+      <c r="J60" s="58"/>
       <c r="K60" s="22" t="s">
         <v>25</v>
       </c>
@@ -5064,7 +5064,7 @@
       <c r="P60" s="24" t="s">
         <v>25</v>
       </c>
-      <c r="R60" s="57"/>
+      <c r="R60" s="58"/>
       <c r="S60" s="22" t="s">
         <v>26</v>
       </c>
@@ -5086,7 +5086,7 @@
       <c r="Z60" s="28"/>
     </row>
     <row r="61" spans="1:26" ht="17.25" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A61" s="57"/>
+      <c r="A61" s="58"/>
       <c r="B61" s="17"/>
       <c r="C61" s="22" t="s">
         <v>25</v>
@@ -5106,7 +5106,7 @@
       <c r="H61" s="24" t="s">
         <v>24</v>
       </c>
-      <c r="J61" s="57"/>
+      <c r="J61" s="58"/>
       <c r="K61" s="22" t="s">
         <v>26</v>
       </c>
@@ -5125,7 +5125,7 @@
       <c r="P61" s="24" t="s">
         <v>26</v>
       </c>
-      <c r="R61" s="57"/>
+      <c r="R61" s="58"/>
       <c r="S61" s="22" t="s">
         <v>32</v>
       </c>
@@ -5147,7 +5147,7 @@
       <c r="Z61" s="28"/>
     </row>
     <row r="62" spans="1:26" ht="17.25" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A62" s="57"/>
+      <c r="A62" s="58"/>
       <c r="B62" s="17"/>
       <c r="C62" s="22" t="s">
         <v>26</v>
@@ -5167,7 +5167,7 @@
       <c r="H62" s="24" t="s">
         <v>25</v>
       </c>
-      <c r="J62" s="57"/>
+      <c r="J62" s="58"/>
       <c r="K62" s="22" t="s">
         <v>32</v>
       </c>
@@ -5186,7 +5186,7 @@
       <c r="P62" s="24" t="s">
         <v>32</v>
       </c>
-      <c r="R62" s="57"/>
+      <c r="R62" s="58"/>
       <c r="S62" s="22" t="s">
         <v>38</v>
       </c>
@@ -5208,7 +5208,7 @@
       <c r="Z62" s="28"/>
     </row>
     <row r="63" spans="1:26" ht="17.25" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A63" s="57"/>
+      <c r="A63" s="58"/>
       <c r="B63" s="17"/>
       <c r="C63" s="22" t="s">
         <v>32</v>
@@ -5228,7 +5228,7 @@
       <c r="H63" s="24" t="s">
         <v>26</v>
       </c>
-      <c r="J63" s="57"/>
+      <c r="J63" s="58"/>
       <c r="K63" s="22" t="s">
         <v>38</v>
       </c>
@@ -5247,7 +5247,7 @@
       <c r="P63" s="24" t="s">
         <v>37</v>
       </c>
-      <c r="R63" s="57"/>
+      <c r="R63" s="58"/>
       <c r="S63" s="22" t="s">
         <v>33</v>
       </c>
@@ -5269,7 +5269,7 @@
       <c r="Z63" s="28"/>
     </row>
     <row r="64" spans="1:26" ht="17.25" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A64" s="57"/>
+      <c r="A64" s="58"/>
       <c r="B64" s="17"/>
       <c r="C64" s="22" t="s">
         <v>30</v>
@@ -5289,7 +5289,7 @@
       <c r="H64" s="24" t="s">
         <v>32</v>
       </c>
-      <c r="J64" s="57"/>
+      <c r="J64" s="58"/>
       <c r="K64" s="22" t="s">
         <v>33</v>
       </c>
@@ -5308,7 +5308,7 @@
       <c r="P64" s="24" t="s">
         <v>36</v>
       </c>
-      <c r="R64" s="57"/>
+      <c r="R64" s="58"/>
       <c r="S64" s="22" t="s">
         <v>36</v>
       </c>
@@ -5328,7 +5328,7 @@
       <c r="Z64" s="28"/>
     </row>
     <row r="65" spans="1:26" ht="17.25" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A65" s="57"/>
+      <c r="A65" s="58"/>
       <c r="B65" s="17"/>
       <c r="C65" s="22" t="s">
         <v>38</v>
@@ -5348,7 +5348,7 @@
       <c r="H65" s="24" t="s">
         <v>30</v>
       </c>
-      <c r="J65" s="57"/>
+      <c r="J65" s="58"/>
       <c r="K65" s="22" t="s">
         <v>36</v>
       </c>
@@ -5361,7 +5361,7 @@
       <c r="N65" s="23"/>
       <c r="O65" s="23"/>
       <c r="P65" s="24"/>
-      <c r="R65" s="57"/>
+      <c r="R65" s="58"/>
       <c r="S65" s="22"/>
       <c r="T65" s="23" t="s">
         <v>36</v>
@@ -5377,7 +5377,7 @@
       <c r="Z65" s="28"/>
     </row>
     <row r="66" spans="1:26" ht="17.25" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A66" s="57"/>
+      <c r="A66" s="58"/>
       <c r="B66" s="17"/>
       <c r="C66" s="22" t="s">
         <v>33</v>
@@ -5397,7 +5397,7 @@
       <c r="H66" s="24" t="s">
         <v>29</v>
       </c>
-      <c r="J66" s="57"/>
+      <c r="J66" s="58"/>
       <c r="K66" s="22"/>
       <c r="L66" s="23"/>
       <c r="M66" s="23" t="s">
@@ -5406,7 +5406,7 @@
       <c r="N66" s="23"/>
       <c r="O66" s="23"/>
       <c r="P66" s="24"/>
-      <c r="R66" s="57"/>
+      <c r="R66" s="58"/>
       <c r="S66" s="22"/>
       <c r="T66" s="23" t="s">
         <v>39</v>
@@ -5422,7 +5422,7 @@
       <c r="Z66" s="28"/>
     </row>
     <row r="67" spans="1:26" ht="17.25" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A67" s="57"/>
+      <c r="A67" s="58"/>
       <c r="B67" s="17"/>
       <c r="C67" s="22" t="s">
         <v>36</v>
@@ -5442,7 +5442,7 @@
       <c r="H67" s="24" t="s">
         <v>33</v>
       </c>
-      <c r="J67" s="57"/>
+      <c r="J67" s="58"/>
       <c r="K67" s="25"/>
       <c r="L67" s="26"/>
       <c r="M67" s="26" t="s">
@@ -5451,7 +5451,7 @@
       <c r="N67" s="26"/>
       <c r="O67" s="26"/>
       <c r="P67" s="27"/>
-      <c r="R67" s="57"/>
+      <c r="R67" s="58"/>
       <c r="S67" s="25"/>
       <c r="T67" s="26"/>
       <c r="U67" s="26" t="s">
@@ -5465,7 +5465,7 @@
       <c r="Z67" s="28"/>
     </row>
     <row r="68" spans="1:26" ht="17.25" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A68" s="57"/>
+      <c r="A68" s="58"/>
       <c r="B68" s="17"/>
       <c r="C68" s="22" t="s">
         <v>39</v>
@@ -5502,7 +5502,7 @@
       <c r="Z68" s="28"/>
     </row>
     <row r="69" spans="1:26" ht="17.25" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A69" s="57"/>
+      <c r="A69" s="58"/>
       <c r="B69" s="17"/>
       <c r="C69" s="22"/>
       <c r="D69" s="23"/>
@@ -5534,7 +5534,7 @@
       <c r="X69" s="21"/>
     </row>
     <row r="70" spans="1:26" ht="17.25" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A70" s="57"/>
+      <c r="A70" s="58"/>
       <c r="B70" s="17"/>
       <c r="C70" s="22"/>
       <c r="D70" s="23"/>
@@ -5562,7 +5562,7 @@
       <c r="X70" s="21"/>
     </row>
     <row r="71" spans="1:26" ht="17.25" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A71" s="57"/>
+      <c r="A71" s="58"/>
       <c r="B71" s="17"/>
       <c r="C71" s="25"/>
       <c r="D71" s="26"/>
@@ -5656,20 +5656,6 @@
     </row>
   </sheetData>
   <mergeCells count="23">
-    <mergeCell ref="K2:P2"/>
-    <mergeCell ref="A5:A20"/>
-    <mergeCell ref="S2:X2"/>
-    <mergeCell ref="AA2:AF2"/>
-    <mergeCell ref="B10:B12"/>
-    <mergeCell ref="A2:B4"/>
-    <mergeCell ref="C2:H2"/>
-    <mergeCell ref="Z22:Z28"/>
-    <mergeCell ref="Z5:Z18"/>
-    <mergeCell ref="J5:J20"/>
-    <mergeCell ref="R5:R17"/>
-    <mergeCell ref="B6:B8"/>
-    <mergeCell ref="B18:B20"/>
-    <mergeCell ref="B14:B16"/>
     <mergeCell ref="A58:A71"/>
     <mergeCell ref="J58:J67"/>
     <mergeCell ref="R58:R67"/>
@@ -5679,6 +5665,20 @@
     <mergeCell ref="A40:A55"/>
     <mergeCell ref="J40:J50"/>
     <mergeCell ref="R40:R52"/>
+    <mergeCell ref="Z22:Z28"/>
+    <mergeCell ref="Z5:Z18"/>
+    <mergeCell ref="J5:J20"/>
+    <mergeCell ref="R5:R17"/>
+    <mergeCell ref="B6:B8"/>
+    <mergeCell ref="B18:B20"/>
+    <mergeCell ref="B14:B16"/>
+    <mergeCell ref="K2:P2"/>
+    <mergeCell ref="A5:A20"/>
+    <mergeCell ref="S2:X2"/>
+    <mergeCell ref="AA2:AF2"/>
+    <mergeCell ref="B10:B12"/>
+    <mergeCell ref="A2:B4"/>
+    <mergeCell ref="C2:H2"/>
   </mergeCells>
   <pageMargins left="0.39370078740157483" right="0.39370078740157483" top="0.47244094488188981" bottom="0.39370078740157483" header="0.31496062992125984" footer="0.31496062992125984"/>
   <pageSetup scale="142" orientation="landscape" r:id="rId1"/>
@@ -5958,10 +5958,10 @@
       <c r="B14" s="10"/>
       <c r="C14" s="10"/>
       <c r="D14" s="65"/>
-      <c r="E14" s="62"/>
-      <c r="F14" s="62"/>
-      <c r="G14" s="62"/>
-      <c r="H14" s="62"/>
+      <c r="E14" s="64"/>
+      <c r="F14" s="64"/>
+      <c r="G14" s="64"/>
+      <c r="H14" s="64"/>
     </row>
     <row r="15" spans="1:8" ht="54" customHeight="1" x14ac:dyDescent="0.7">
       <c r="A15" s="2"/>
@@ -6209,22 +6209,22 @@
       <c r="C27" s="4">
         <v>43529</v>
       </c>
-      <c r="D27" s="64" t="s">
+      <c r="D27" s="63" t="s">
         <v>1</v>
       </c>
-      <c r="E27" s="64"/>
-      <c r="F27" s="64"/>
-      <c r="G27" s="64"/>
-      <c r="H27" s="64"/>
+      <c r="E27" s="63"/>
+      <c r="F27" s="63"/>
+      <c r="G27" s="63"/>
+      <c r="H27" s="63"/>
     </row>
     <row r="28" spans="1:8" ht="63.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B28" s="10"/>
       <c r="C28" s="10"/>
-      <c r="D28" s="62"/>
-      <c r="E28" s="62"/>
-      <c r="F28" s="62"/>
-      <c r="G28" s="62"/>
-      <c r="H28" s="62"/>
+      <c r="D28" s="64"/>
+      <c r="E28" s="64"/>
+      <c r="F28" s="64"/>
+      <c r="G28" s="64"/>
+      <c r="H28" s="64"/>
     </row>
     <row r="29" spans="1:8" ht="54" customHeight="1" x14ac:dyDescent="0.7">
       <c r="A29" s="2"/>
@@ -6470,22 +6470,22 @@
       <c r="C41" s="4">
         <v>43557</v>
       </c>
-      <c r="D41" s="64" t="s">
+      <c r="D41" s="63" t="s">
         <v>1</v>
       </c>
-      <c r="E41" s="64"/>
-      <c r="F41" s="64"/>
-      <c r="G41" s="64"/>
-      <c r="H41" s="64"/>
+      <c r="E41" s="63"/>
+      <c r="F41" s="63"/>
+      <c r="G41" s="63"/>
+      <c r="H41" s="63"/>
     </row>
     <row r="42" spans="1:8" ht="63.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B42" s="10"/>
       <c r="C42" s="10"/>
-      <c r="D42" s="62"/>
-      <c r="E42" s="62"/>
-      <c r="F42" s="62"/>
-      <c r="G42" s="62"/>
-      <c r="H42" s="62"/>
+      <c r="D42" s="64"/>
+      <c r="E42" s="64"/>
+      <c r="F42" s="64"/>
+      <c r="G42" s="64"/>
+      <c r="H42" s="64"/>
     </row>
     <row r="43" spans="1:8" ht="54" customHeight="1" x14ac:dyDescent="0.7">
       <c r="A43" s="2"/>
@@ -6733,22 +6733,22 @@
       <c r="C55" s="4">
         <v>43592</v>
       </c>
-      <c r="D55" s="63" t="s">
+      <c r="D55" s="62" t="s">
         <v>1</v>
       </c>
-      <c r="E55" s="64"/>
-      <c r="F55" s="64"/>
-      <c r="G55" s="64"/>
-      <c r="H55" s="64"/>
+      <c r="E55" s="63"/>
+      <c r="F55" s="63"/>
+      <c r="G55" s="63"/>
+      <c r="H55" s="63"/>
     </row>
     <row r="56" spans="1:8" ht="63.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B56" s="10"/>
       <c r="C56" s="10"/>
-      <c r="D56" s="62"/>
-      <c r="E56" s="62"/>
-      <c r="F56" s="62"/>
-      <c r="G56" s="62"/>
-      <c r="H56" s="62"/>
+      <c r="D56" s="64"/>
+      <c r="E56" s="64"/>
+      <c r="F56" s="64"/>
+      <c r="G56" s="64"/>
+      <c r="H56" s="64"/>
     </row>
     <row r="57" spans="1:8" ht="54" customHeight="1" x14ac:dyDescent="0.7">
       <c r="A57" s="2"/>
@@ -6970,22 +6970,22 @@
       <c r="C69" s="4">
         <v>43620</v>
       </c>
-      <c r="D69" s="63" t="s">
+      <c r="D69" s="62" t="s">
         <v>1</v>
       </c>
-      <c r="E69" s="64"/>
-      <c r="F69" s="64"/>
-      <c r="G69" s="64"/>
-      <c r="H69" s="64"/>
+      <c r="E69" s="63"/>
+      <c r="F69" s="63"/>
+      <c r="G69" s="63"/>
+      <c r="H69" s="63"/>
     </row>
     <row r="70" spans="1:8" ht="63.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B70" s="10"/>
       <c r="C70" s="10"/>
-      <c r="D70" s="62"/>
-      <c r="E70" s="62"/>
-      <c r="F70" s="62"/>
-      <c r="G70" s="62"/>
-      <c r="H70" s="62"/>
+      <c r="D70" s="64"/>
+      <c r="E70" s="64"/>
+      <c r="F70" s="64"/>
+      <c r="G70" s="64"/>
+      <c r="H70" s="64"/>
     </row>
     <row r="71" spans="1:8" ht="54" customHeight="1" x14ac:dyDescent="0.7">
       <c r="A71" s="2"/>
@@ -7207,22 +7207,22 @@
       <c r="C83" s="4">
         <v>43648</v>
       </c>
-      <c r="D83" s="63" t="s">
+      <c r="D83" s="62" t="s">
         <v>1</v>
       </c>
-      <c r="E83" s="64"/>
-      <c r="F83" s="64"/>
-      <c r="G83" s="64"/>
-      <c r="H83" s="64"/>
+      <c r="E83" s="63"/>
+      <c r="F83" s="63"/>
+      <c r="G83" s="63"/>
+      <c r="H83" s="63"/>
     </row>
     <row r="84" spans="1:8" ht="63.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B84" s="10"/>
       <c r="C84" s="10"/>
-      <c r="D84" s="62"/>
-      <c r="E84" s="62"/>
-      <c r="F84" s="62"/>
-      <c r="G84" s="62"/>
-      <c r="H84" s="62"/>
+      <c r="D84" s="64"/>
+      <c r="E84" s="64"/>
+      <c r="F84" s="64"/>
+      <c r="G84" s="64"/>
+      <c r="H84" s="64"/>
     </row>
     <row r="85" spans="1:8" ht="54" customHeight="1" x14ac:dyDescent="0.7">
       <c r="A85" s="2"/>
@@ -7444,22 +7444,22 @@
       <c r="C97" s="4">
         <v>43683</v>
       </c>
-      <c r="D97" s="63" t="s">
+      <c r="D97" s="62" t="s">
         <v>1</v>
       </c>
-      <c r="E97" s="64"/>
-      <c r="F97" s="64"/>
-      <c r="G97" s="64"/>
-      <c r="H97" s="64"/>
+      <c r="E97" s="63"/>
+      <c r="F97" s="63"/>
+      <c r="G97" s="63"/>
+      <c r="H97" s="63"/>
     </row>
     <row r="98" spans="1:8" ht="63.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B98" s="10"/>
       <c r="C98" s="10"/>
-      <c r="D98" s="62"/>
-      <c r="E98" s="62"/>
-      <c r="F98" s="62"/>
-      <c r="G98" s="62"/>
-      <c r="H98" s="62"/>
+      <c r="D98" s="64"/>
+      <c r="E98" s="64"/>
+      <c r="F98" s="64"/>
+      <c r="G98" s="64"/>
+      <c r="H98" s="64"/>
     </row>
     <row r="99" spans="1:8" ht="54" customHeight="1" x14ac:dyDescent="0.7">
       <c r="A99" s="2"/>
@@ -7681,22 +7681,22 @@
       <c r="C111" s="4">
         <v>43711</v>
       </c>
-      <c r="D111" s="63" t="s">
+      <c r="D111" s="62" t="s">
         <v>1</v>
       </c>
-      <c r="E111" s="64"/>
-      <c r="F111" s="64"/>
-      <c r="G111" s="64"/>
-      <c r="H111" s="64"/>
+      <c r="E111" s="63"/>
+      <c r="F111" s="63"/>
+      <c r="G111" s="63"/>
+      <c r="H111" s="63"/>
     </row>
     <row r="112" spans="1:8" ht="63.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B112" s="10"/>
       <c r="C112" s="10"/>
-      <c r="D112" s="62"/>
-      <c r="E112" s="62"/>
-      <c r="F112" s="62"/>
-      <c r="G112" s="62"/>
-      <c r="H112" s="62"/>
+      <c r="D112" s="64"/>
+      <c r="E112" s="64"/>
+      <c r="F112" s="64"/>
+      <c r="G112" s="64"/>
+      <c r="H112" s="64"/>
     </row>
     <row r="113" spans="1:8" ht="54" customHeight="1" x14ac:dyDescent="0.7">
       <c r="A113" s="2"/>
@@ -7918,22 +7918,22 @@
       <c r="C125" s="4">
         <v>43739</v>
       </c>
-      <c r="D125" s="63" t="s">
+      <c r="D125" s="62" t="s">
         <v>1</v>
       </c>
-      <c r="E125" s="64"/>
-      <c r="F125" s="64"/>
-      <c r="G125" s="64"/>
-      <c r="H125" s="64"/>
+      <c r="E125" s="63"/>
+      <c r="F125" s="63"/>
+      <c r="G125" s="63"/>
+      <c r="H125" s="63"/>
     </row>
     <row r="126" spans="1:8" ht="63.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B126" s="10"/>
       <c r="C126" s="10"/>
-      <c r="D126" s="62"/>
-      <c r="E126" s="62"/>
-      <c r="F126" s="62"/>
-      <c r="G126" s="62"/>
-      <c r="H126" s="62"/>
+      <c r="D126" s="64"/>
+      <c r="E126" s="64"/>
+      <c r="F126" s="64"/>
+      <c r="G126" s="64"/>
+      <c r="H126" s="64"/>
     </row>
     <row r="127" spans="1:8" ht="54" customHeight="1" x14ac:dyDescent="0.7">
       <c r="A127" s="2"/>
@@ -8155,22 +8155,22 @@
       <c r="C139" s="4">
         <v>43774</v>
       </c>
-      <c r="D139" s="63" t="s">
+      <c r="D139" s="62" t="s">
         <v>1</v>
       </c>
-      <c r="E139" s="64"/>
-      <c r="F139" s="64"/>
-      <c r="G139" s="64"/>
-      <c r="H139" s="64"/>
+      <c r="E139" s="63"/>
+      <c r="F139" s="63"/>
+      <c r="G139" s="63"/>
+      <c r="H139" s="63"/>
     </row>
     <row r="140" spans="2:8" ht="63.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B140" s="10"/>
       <c r="C140" s="10"/>
-      <c r="D140" s="62"/>
-      <c r="E140" s="62"/>
-      <c r="F140" s="62"/>
-      <c r="G140" s="62"/>
-      <c r="H140" s="62"/>
+      <c r="D140" s="64"/>
+      <c r="E140" s="64"/>
+      <c r="F140" s="64"/>
+      <c r="G140" s="64"/>
+      <c r="H140" s="64"/>
     </row>
     <row r="141" spans="2:8" ht="54" customHeight="1" x14ac:dyDescent="0.7">
       <c r="B141" s="1">
@@ -8390,22 +8390,22 @@
       <c r="C153" s="4">
         <v>43802</v>
       </c>
-      <c r="D153" s="63" t="s">
+      <c r="D153" s="62" t="s">
         <v>1</v>
       </c>
-      <c r="E153" s="64"/>
-      <c r="F153" s="64"/>
-      <c r="G153" s="64"/>
-      <c r="H153" s="64"/>
+      <c r="E153" s="63"/>
+      <c r="F153" s="63"/>
+      <c r="G153" s="63"/>
+      <c r="H153" s="63"/>
     </row>
     <row r="154" spans="2:8" ht="63.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B154" s="10"/>
       <c r="C154" s="10"/>
-      <c r="D154" s="62"/>
-      <c r="E154" s="62"/>
-      <c r="F154" s="62"/>
-      <c r="G154" s="62"/>
-      <c r="H154" s="62"/>
+      <c r="D154" s="64"/>
+      <c r="E154" s="64"/>
+      <c r="F154" s="64"/>
+      <c r="G154" s="64"/>
+      <c r="H154" s="64"/>
     </row>
     <row r="155" spans="2:8" ht="54" customHeight="1" x14ac:dyDescent="0.7">
       <c r="B155" s="1">
@@ -8625,25 +8625,35 @@
       <c r="C167" s="4">
         <v>43830</v>
       </c>
-      <c r="D167" s="63" t="s">
+      <c r="D167" s="62" t="s">
         <v>1</v>
       </c>
-      <c r="E167" s="64"/>
-      <c r="F167" s="64"/>
-      <c r="G167" s="64"/>
-      <c r="H167" s="64"/>
+      <c r="E167" s="63"/>
+      <c r="F167" s="63"/>
+      <c r="G167" s="63"/>
+      <c r="H167" s="63"/>
     </row>
     <row r="168" spans="2:8" ht="63.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B168" s="10"/>
       <c r="C168" s="10"/>
-      <c r="D168" s="62"/>
-      <c r="E168" s="62"/>
-      <c r="F168" s="62"/>
-      <c r="G168" s="62"/>
-      <c r="H168" s="62"/>
+      <c r="D168" s="64"/>
+      <c r="E168" s="64"/>
+      <c r="F168" s="64"/>
+      <c r="G168" s="64"/>
+      <c r="H168" s="64"/>
     </row>
   </sheetData>
   <mergeCells count="24">
+    <mergeCell ref="D70:H70"/>
+    <mergeCell ref="D55:H55"/>
+    <mergeCell ref="D69:H69"/>
+    <mergeCell ref="D14:H14"/>
+    <mergeCell ref="D13:H13"/>
+    <mergeCell ref="D27:H27"/>
+    <mergeCell ref="D28:H28"/>
+    <mergeCell ref="D41:H41"/>
+    <mergeCell ref="D42:H42"/>
+    <mergeCell ref="D56:H56"/>
     <mergeCell ref="D83:H83"/>
     <mergeCell ref="D153:H153"/>
     <mergeCell ref="D168:H168"/>
@@ -8658,16 +8668,6 @@
     <mergeCell ref="D112:H112"/>
     <mergeCell ref="D154:H154"/>
     <mergeCell ref="D167:H167"/>
-    <mergeCell ref="D70:H70"/>
-    <mergeCell ref="D55:H55"/>
-    <mergeCell ref="D69:H69"/>
-    <mergeCell ref="D14:H14"/>
-    <mergeCell ref="D13:H13"/>
-    <mergeCell ref="D27:H27"/>
-    <mergeCell ref="D28:H28"/>
-    <mergeCell ref="D41:H41"/>
-    <mergeCell ref="D42:H42"/>
-    <mergeCell ref="D56:H56"/>
   </mergeCells>
   <phoneticPr fontId="3" type="noConversion"/>
   <conditionalFormatting sqref="B3:H3 B5:H5 B7:H7 B9:H9 B11:H11 B13:C13">
@@ -9045,10 +9045,10 @@
       <c r="B14" s="10"/>
       <c r="C14" s="10"/>
       <c r="D14" s="65"/>
-      <c r="E14" s="62"/>
-      <c r="F14" s="62"/>
-      <c r="G14" s="62"/>
-      <c r="H14" s="62"/>
+      <c r="E14" s="64"/>
+      <c r="F14" s="64"/>
+      <c r="G14" s="64"/>
+      <c r="H14" s="64"/>
     </row>
     <row r="15" spans="1:8" ht="54" customHeight="1" x14ac:dyDescent="0.7">
       <c r="A15" s="2"/>
@@ -9296,22 +9296,22 @@
       <c r="C27" s="4">
         <v>43893</v>
       </c>
-      <c r="D27" s="64" t="s">
+      <c r="D27" s="63" t="s">
         <v>1</v>
       </c>
-      <c r="E27" s="64"/>
-      <c r="F27" s="64"/>
-      <c r="G27" s="64"/>
-      <c r="H27" s="64"/>
+      <c r="E27" s="63"/>
+      <c r="F27" s="63"/>
+      <c r="G27" s="63"/>
+      <c r="H27" s="63"/>
     </row>
     <row r="28" spans="1:8" ht="63.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B28" s="10"/>
       <c r="C28" s="10"/>
-      <c r="D28" s="62"/>
-      <c r="E28" s="62"/>
-      <c r="F28" s="62"/>
-      <c r="G28" s="62"/>
-      <c r="H28" s="62"/>
+      <c r="D28" s="64"/>
+      <c r="E28" s="64"/>
+      <c r="F28" s="64"/>
+      <c r="G28" s="64"/>
+      <c r="H28" s="64"/>
     </row>
     <row r="29" spans="1:8" ht="54" customHeight="1" x14ac:dyDescent="0.7">
       <c r="A29" s="2"/>
@@ -9557,22 +9557,22 @@
       <c r="C41" s="4">
         <v>43921</v>
       </c>
-      <c r="D41" s="64" t="s">
+      <c r="D41" s="63" t="s">
         <v>1</v>
       </c>
-      <c r="E41" s="64"/>
-      <c r="F41" s="64"/>
-      <c r="G41" s="64"/>
-      <c r="H41" s="64"/>
+      <c r="E41" s="63"/>
+      <c r="F41" s="63"/>
+      <c r="G41" s="63"/>
+      <c r="H41" s="63"/>
     </row>
     <row r="42" spans="1:8" ht="63.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B42" s="10"/>
       <c r="C42" s="10"/>
-      <c r="D42" s="62"/>
-      <c r="E42" s="62"/>
-      <c r="F42" s="62"/>
-      <c r="G42" s="62"/>
-      <c r="H42" s="62"/>
+      <c r="D42" s="64"/>
+      <c r="E42" s="64"/>
+      <c r="F42" s="64"/>
+      <c r="G42" s="64"/>
+      <c r="H42" s="64"/>
     </row>
     <row r="43" spans="1:8" ht="54" customHeight="1" x14ac:dyDescent="0.7">
       <c r="A43" s="2"/>
@@ -9820,22 +9820,22 @@
       <c r="C55" s="4">
         <v>43956</v>
       </c>
-      <c r="D55" s="63" t="s">
+      <c r="D55" s="62" t="s">
         <v>1</v>
       </c>
-      <c r="E55" s="64"/>
-      <c r="F55" s="64"/>
-      <c r="G55" s="64"/>
-      <c r="H55" s="64"/>
+      <c r="E55" s="63"/>
+      <c r="F55" s="63"/>
+      <c r="G55" s="63"/>
+      <c r="H55" s="63"/>
     </row>
     <row r="56" spans="1:8" ht="63.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B56" s="10"/>
       <c r="C56" s="10"/>
-      <c r="D56" s="62"/>
-      <c r="E56" s="62"/>
-      <c r="F56" s="62"/>
-      <c r="G56" s="62"/>
-      <c r="H56" s="62"/>
+      <c r="D56" s="64"/>
+      <c r="E56" s="64"/>
+      <c r="F56" s="64"/>
+      <c r="G56" s="64"/>
+      <c r="H56" s="64"/>
     </row>
     <row r="57" spans="1:8" ht="54" customHeight="1" x14ac:dyDescent="0.7">
       <c r="A57" s="2"/>
@@ -10057,22 +10057,22 @@
       <c r="C69" s="4">
         <v>43984</v>
       </c>
-      <c r="D69" s="63" t="s">
+      <c r="D69" s="62" t="s">
         <v>1</v>
       </c>
-      <c r="E69" s="64"/>
-      <c r="F69" s="64"/>
-      <c r="G69" s="64"/>
-      <c r="H69" s="64"/>
+      <c r="E69" s="63"/>
+      <c r="F69" s="63"/>
+      <c r="G69" s="63"/>
+      <c r="H69" s="63"/>
     </row>
     <row r="70" spans="1:8" ht="63.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B70" s="10"/>
       <c r="C70" s="10"/>
-      <c r="D70" s="62"/>
-      <c r="E70" s="62"/>
-      <c r="F70" s="62"/>
-      <c r="G70" s="62"/>
-      <c r="H70" s="62"/>
+      <c r="D70" s="64"/>
+      <c r="E70" s="64"/>
+      <c r="F70" s="64"/>
+      <c r="G70" s="64"/>
+      <c r="H70" s="64"/>
     </row>
     <row r="71" spans="1:8" ht="54" customHeight="1" x14ac:dyDescent="0.7">
       <c r="A71" s="2"/>
@@ -10294,22 +10294,22 @@
       <c r="C83" s="4">
         <v>44019</v>
       </c>
-      <c r="D83" s="63" t="s">
+      <c r="D83" s="62" t="s">
         <v>1</v>
       </c>
-      <c r="E83" s="64"/>
-      <c r="F83" s="64"/>
-      <c r="G83" s="64"/>
-      <c r="H83" s="64"/>
+      <c r="E83" s="63"/>
+      <c r="F83" s="63"/>
+      <c r="G83" s="63"/>
+      <c r="H83" s="63"/>
     </row>
     <row r="84" spans="1:8" ht="63.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B84" s="10"/>
       <c r="C84" s="10"/>
-      <c r="D84" s="62"/>
-      <c r="E84" s="62"/>
-      <c r="F84" s="62"/>
-      <c r="G84" s="62"/>
-      <c r="H84" s="62"/>
+      <c r="D84" s="64"/>
+      <c r="E84" s="64"/>
+      <c r="F84" s="64"/>
+      <c r="G84" s="64"/>
+      <c r="H84" s="64"/>
     </row>
     <row r="85" spans="1:8" ht="54" customHeight="1" x14ac:dyDescent="0.7">
       <c r="A85" s="2"/>
@@ -10531,22 +10531,22 @@
       <c r="C97" s="4">
         <v>44047</v>
       </c>
-      <c r="D97" s="63" t="s">
+      <c r="D97" s="62" t="s">
         <v>1</v>
       </c>
-      <c r="E97" s="64"/>
-      <c r="F97" s="64"/>
-      <c r="G97" s="64"/>
-      <c r="H97" s="64"/>
+      <c r="E97" s="63"/>
+      <c r="F97" s="63"/>
+      <c r="G97" s="63"/>
+      <c r="H97" s="63"/>
     </row>
     <row r="98" spans="1:8" ht="63.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B98" s="10"/>
       <c r="C98" s="10"/>
-      <c r="D98" s="62"/>
-      <c r="E98" s="62"/>
-      <c r="F98" s="62"/>
-      <c r="G98" s="62"/>
-      <c r="H98" s="62"/>
+      <c r="D98" s="64"/>
+      <c r="E98" s="64"/>
+      <c r="F98" s="64"/>
+      <c r="G98" s="64"/>
+      <c r="H98" s="64"/>
     </row>
     <row r="99" spans="1:8" ht="54" customHeight="1" x14ac:dyDescent="0.7">
       <c r="A99" s="2"/>
@@ -10768,22 +10768,22 @@
       <c r="C111" s="4">
         <v>44075</v>
       </c>
-      <c r="D111" s="63" t="s">
+      <c r="D111" s="62" t="s">
         <v>1</v>
       </c>
-      <c r="E111" s="64"/>
-      <c r="F111" s="64"/>
-      <c r="G111" s="64"/>
-      <c r="H111" s="64"/>
+      <c r="E111" s="63"/>
+      <c r="F111" s="63"/>
+      <c r="G111" s="63"/>
+      <c r="H111" s="63"/>
     </row>
     <row r="112" spans="1:8" ht="63.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B112" s="10"/>
       <c r="C112" s="10"/>
-      <c r="D112" s="62"/>
-      <c r="E112" s="62"/>
-      <c r="F112" s="62"/>
-      <c r="G112" s="62"/>
-      <c r="H112" s="62"/>
+      <c r="D112" s="64"/>
+      <c r="E112" s="64"/>
+      <c r="F112" s="64"/>
+      <c r="G112" s="64"/>
+      <c r="H112" s="64"/>
     </row>
     <row r="113" spans="1:8" ht="54" customHeight="1" x14ac:dyDescent="0.7">
       <c r="A113" s="2"/>
@@ -11005,22 +11005,22 @@
       <c r="C125" s="4">
         <v>44110</v>
       </c>
-      <c r="D125" s="63" t="s">
+      <c r="D125" s="62" t="s">
         <v>1</v>
       </c>
-      <c r="E125" s="64"/>
-      <c r="F125" s="64"/>
-      <c r="G125" s="64"/>
-      <c r="H125" s="64"/>
+      <c r="E125" s="63"/>
+      <c r="F125" s="63"/>
+      <c r="G125" s="63"/>
+      <c r="H125" s="63"/>
     </row>
     <row r="126" spans="1:8" ht="63.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B126" s="10"/>
       <c r="C126" s="10"/>
-      <c r="D126" s="62"/>
-      <c r="E126" s="62"/>
-      <c r="F126" s="62"/>
-      <c r="G126" s="62"/>
-      <c r="H126" s="62"/>
+      <c r="D126" s="64"/>
+      <c r="E126" s="64"/>
+      <c r="F126" s="64"/>
+      <c r="G126" s="64"/>
+      <c r="H126" s="64"/>
     </row>
     <row r="127" spans="1:8" ht="54" customHeight="1" x14ac:dyDescent="0.7">
       <c r="A127" s="2"/>
@@ -11242,22 +11242,22 @@
       <c r="C139" s="4">
         <v>44138</v>
       </c>
-      <c r="D139" s="63" t="s">
+      <c r="D139" s="62" t="s">
         <v>1</v>
       </c>
-      <c r="E139" s="64"/>
-      <c r="F139" s="64"/>
-      <c r="G139" s="64"/>
-      <c r="H139" s="64"/>
+      <c r="E139" s="63"/>
+      <c r="F139" s="63"/>
+      <c r="G139" s="63"/>
+      <c r="H139" s="63"/>
     </row>
     <row r="140" spans="2:8" ht="63.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B140" s="10"/>
       <c r="C140" s="10"/>
-      <c r="D140" s="62"/>
-      <c r="E140" s="62"/>
-      <c r="F140" s="62"/>
-      <c r="G140" s="62"/>
-      <c r="H140" s="62"/>
+      <c r="D140" s="64"/>
+      <c r="E140" s="64"/>
+      <c r="F140" s="64"/>
+      <c r="G140" s="64"/>
+      <c r="H140" s="64"/>
     </row>
     <row r="141" spans="2:8" ht="54" customHeight="1" x14ac:dyDescent="0.7">
       <c r="B141" s="1">
@@ -11477,22 +11477,22 @@
       <c r="C153" s="4">
         <v>44166</v>
       </c>
-      <c r="D153" s="63" t="s">
+      <c r="D153" s="62" t="s">
         <v>1</v>
       </c>
-      <c r="E153" s="64"/>
-      <c r="F153" s="64"/>
-      <c r="G153" s="64"/>
-      <c r="H153" s="64"/>
+      <c r="E153" s="63"/>
+      <c r="F153" s="63"/>
+      <c r="G153" s="63"/>
+      <c r="H153" s="63"/>
     </row>
     <row r="154" spans="2:8" ht="63.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B154" s="10"/>
       <c r="C154" s="10"/>
-      <c r="D154" s="62"/>
-      <c r="E154" s="62"/>
-      <c r="F154" s="62"/>
-      <c r="G154" s="62"/>
-      <c r="H154" s="62"/>
+      <c r="D154" s="64"/>
+      <c r="E154" s="64"/>
+      <c r="F154" s="64"/>
+      <c r="G154" s="64"/>
+      <c r="H154" s="64"/>
     </row>
     <row r="155" spans="2:8" ht="54" customHeight="1" x14ac:dyDescent="0.7">
       <c r="B155" s="1">
@@ -11712,25 +11712,37 @@
       <c r="C167" s="4">
         <v>44201</v>
       </c>
-      <c r="D167" s="63" t="s">
+      <c r="D167" s="62" t="s">
         <v>1</v>
       </c>
-      <c r="E167" s="64"/>
-      <c r="F167" s="64"/>
-      <c r="G167" s="64"/>
-      <c r="H167" s="64"/>
+      <c r="E167" s="63"/>
+      <c r="F167" s="63"/>
+      <c r="G167" s="63"/>
+      <c r="H167" s="63"/>
     </row>
     <row r="168" spans="2:8" ht="63.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B168" s="10"/>
       <c r="C168" s="10"/>
-      <c r="D168" s="62"/>
-      <c r="E168" s="62"/>
-      <c r="F168" s="62"/>
-      <c r="G168" s="62"/>
-      <c r="H168" s="62"/>
+      <c r="D168" s="64"/>
+      <c r="E168" s="64"/>
+      <c r="F168" s="64"/>
+      <c r="G168" s="64"/>
+      <c r="H168" s="64"/>
     </row>
   </sheetData>
   <mergeCells count="24">
+    <mergeCell ref="D168:H168"/>
+    <mergeCell ref="D97:H97"/>
+    <mergeCell ref="D98:H98"/>
+    <mergeCell ref="D111:H111"/>
+    <mergeCell ref="D112:H112"/>
+    <mergeCell ref="D125:H125"/>
+    <mergeCell ref="D126:H126"/>
+    <mergeCell ref="D139:H139"/>
+    <mergeCell ref="D140:H140"/>
+    <mergeCell ref="D153:H153"/>
+    <mergeCell ref="D154:H154"/>
+    <mergeCell ref="D167:H167"/>
     <mergeCell ref="D84:H84"/>
     <mergeCell ref="D13:H13"/>
     <mergeCell ref="D14:H14"/>
@@ -11743,18 +11755,6 @@
     <mergeCell ref="D69:H69"/>
     <mergeCell ref="D70:H70"/>
     <mergeCell ref="D83:H83"/>
-    <mergeCell ref="D168:H168"/>
-    <mergeCell ref="D97:H97"/>
-    <mergeCell ref="D98:H98"/>
-    <mergeCell ref="D111:H111"/>
-    <mergeCell ref="D112:H112"/>
-    <mergeCell ref="D125:H125"/>
-    <mergeCell ref="D126:H126"/>
-    <mergeCell ref="D139:H139"/>
-    <mergeCell ref="D140:H140"/>
-    <mergeCell ref="D153:H153"/>
-    <mergeCell ref="D154:H154"/>
-    <mergeCell ref="D167:H167"/>
   </mergeCells>
   <conditionalFormatting sqref="B3:H3 B5:H5 B7:H7 B9:H9 B11:H11 B13:C13">
     <cfRule type="expression" dxfId="23" priority="12">
@@ -12098,10 +12098,10 @@
       <c r="B14" s="10"/>
       <c r="C14" s="10"/>
       <c r="D14" s="65"/>
-      <c r="E14" s="62"/>
-      <c r="F14" s="62"/>
-      <c r="G14" s="62"/>
-      <c r="H14" s="62"/>
+      <c r="E14" s="64"/>
+      <c r="F14" s="64"/>
+      <c r="G14" s="64"/>
+      <c r="H14" s="64"/>
     </row>
     <row r="15" spans="1:8" ht="54" customHeight="1" x14ac:dyDescent="0.7">
       <c r="A15" s="2"/>
@@ -12323,22 +12323,22 @@
       <c r="C27" s="4">
         <v>46084</v>
       </c>
-      <c r="D27" s="64" t="s">
+      <c r="D27" s="63" t="s">
         <v>1</v>
       </c>
-      <c r="E27" s="64"/>
-      <c r="F27" s="64"/>
-      <c r="G27" s="64"/>
-      <c r="H27" s="64"/>
+      <c r="E27" s="63"/>
+      <c r="F27" s="63"/>
+      <c r="G27" s="63"/>
+      <c r="H27" s="63"/>
     </row>
     <row r="28" spans="1:8" ht="63.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B28" s="10"/>
       <c r="C28" s="10"/>
-      <c r="D28" s="62"/>
-      <c r="E28" s="62"/>
-      <c r="F28" s="62"/>
-      <c r="G28" s="62"/>
-      <c r="H28" s="62"/>
+      <c r="D28" s="64"/>
+      <c r="E28" s="64"/>
+      <c r="F28" s="64"/>
+      <c r="G28" s="64"/>
+      <c r="H28" s="64"/>
     </row>
     <row r="29" spans="1:8" ht="54" customHeight="1" x14ac:dyDescent="0.7">
       <c r="A29" s="2"/>
@@ -12560,22 +12560,22 @@
       <c r="C41" s="4">
         <v>46112</v>
       </c>
-      <c r="D41" s="64" t="s">
+      <c r="D41" s="63" t="s">
         <v>1</v>
       </c>
-      <c r="E41" s="64"/>
-      <c r="F41" s="64"/>
-      <c r="G41" s="64"/>
-      <c r="H41" s="64"/>
+      <c r="E41" s="63"/>
+      <c r="F41" s="63"/>
+      <c r="G41" s="63"/>
+      <c r="H41" s="63"/>
     </row>
     <row r="42" spans="1:8" ht="63.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B42" s="10"/>
       <c r="C42" s="10"/>
-      <c r="D42" s="62"/>
-      <c r="E42" s="62"/>
-      <c r="F42" s="62"/>
-      <c r="G42" s="62"/>
-      <c r="H42" s="62"/>
+      <c r="D42" s="64"/>
+      <c r="E42" s="64"/>
+      <c r="F42" s="64"/>
+      <c r="G42" s="64"/>
+      <c r="H42" s="64"/>
     </row>
     <row r="43" spans="1:8" ht="54" customHeight="1" x14ac:dyDescent="0.7">
       <c r="A43" s="2"/>
@@ -12797,22 +12797,22 @@
       <c r="C55" s="4">
         <v>46147</v>
       </c>
-      <c r="D55" s="63" t="s">
+      <c r="D55" s="62" t="s">
         <v>1</v>
       </c>
-      <c r="E55" s="64"/>
-      <c r="F55" s="64"/>
-      <c r="G55" s="64"/>
-      <c r="H55" s="64"/>
+      <c r="E55" s="63"/>
+      <c r="F55" s="63"/>
+      <c r="G55" s="63"/>
+      <c r="H55" s="63"/>
     </row>
     <row r="56" spans="1:8" ht="63.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B56" s="10"/>
       <c r="C56" s="10"/>
-      <c r="D56" s="62"/>
-      <c r="E56" s="62"/>
-      <c r="F56" s="62"/>
-      <c r="G56" s="62"/>
-      <c r="H56" s="62"/>
+      <c r="D56" s="64"/>
+      <c r="E56" s="64"/>
+      <c r="F56" s="64"/>
+      <c r="G56" s="64"/>
+      <c r="H56" s="64"/>
     </row>
     <row r="57" spans="1:8" ht="54" customHeight="1" x14ac:dyDescent="0.7">
       <c r="A57" s="2"/>
@@ -13034,22 +13034,22 @@
       <c r="C69" s="4">
         <v>46175</v>
       </c>
-      <c r="D69" s="63" t="s">
+      <c r="D69" s="62" t="s">
         <v>1</v>
       </c>
-      <c r="E69" s="64"/>
-      <c r="F69" s="64"/>
-      <c r="G69" s="64"/>
-      <c r="H69" s="64"/>
+      <c r="E69" s="63"/>
+      <c r="F69" s="63"/>
+      <c r="G69" s="63"/>
+      <c r="H69" s="63"/>
     </row>
     <row r="70" spans="1:8" ht="63.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B70" s="13"/>
       <c r="C70" s="10"/>
-      <c r="D70" s="62"/>
-      <c r="E70" s="62"/>
-      <c r="F70" s="62"/>
-      <c r="G70" s="62"/>
-      <c r="H70" s="62"/>
+      <c r="D70" s="64"/>
+      <c r="E70" s="64"/>
+      <c r="F70" s="64"/>
+      <c r="G70" s="64"/>
+      <c r="H70" s="64"/>
     </row>
     <row r="71" spans="1:8" ht="54" customHeight="1" x14ac:dyDescent="0.7">
       <c r="A71" s="2"/>
@@ -13271,22 +13271,22 @@
       <c r="C83" s="4">
         <v>46210</v>
       </c>
-      <c r="D83" s="63" t="s">
+      <c r="D83" s="62" t="s">
         <v>1</v>
       </c>
-      <c r="E83" s="64"/>
-      <c r="F83" s="64"/>
-      <c r="G83" s="64"/>
-      <c r="H83" s="64"/>
+      <c r="E83" s="63"/>
+      <c r="F83" s="63"/>
+      <c r="G83" s="63"/>
+      <c r="H83" s="63"/>
     </row>
     <row r="84" spans="1:8" ht="63.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B84" s="10"/>
       <c r="C84" s="10"/>
-      <c r="D84" s="62"/>
-      <c r="E84" s="62"/>
-      <c r="F84" s="62"/>
-      <c r="G84" s="62"/>
-      <c r="H84" s="62"/>
+      <c r="D84" s="64"/>
+      <c r="E84" s="64"/>
+      <c r="F84" s="64"/>
+      <c r="G84" s="64"/>
+      <c r="H84" s="64"/>
     </row>
     <row r="85" spans="1:8" ht="54" customHeight="1" x14ac:dyDescent="0.7">
       <c r="A85" s="2"/>
@@ -13508,22 +13508,22 @@
       <c r="C97" s="4">
         <v>46238</v>
       </c>
-      <c r="D97" s="63" t="s">
+      <c r="D97" s="62" t="s">
         <v>1</v>
       </c>
-      <c r="E97" s="64"/>
-      <c r="F97" s="64"/>
-      <c r="G97" s="64"/>
-      <c r="H97" s="64"/>
+      <c r="E97" s="63"/>
+      <c r="F97" s="63"/>
+      <c r="G97" s="63"/>
+      <c r="H97" s="63"/>
     </row>
     <row r="98" spans="1:8" ht="63.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B98" s="10"/>
       <c r="C98" s="10"/>
-      <c r="D98" s="62"/>
-      <c r="E98" s="62"/>
-      <c r="F98" s="62"/>
-      <c r="G98" s="62"/>
-      <c r="H98" s="62"/>
+      <c r="D98" s="64"/>
+      <c r="E98" s="64"/>
+      <c r="F98" s="64"/>
+      <c r="G98" s="64"/>
+      <c r="H98" s="64"/>
     </row>
     <row r="99" spans="1:8" ht="54" customHeight="1" x14ac:dyDescent="0.7">
       <c r="A99" s="2"/>
@@ -13745,22 +13745,22 @@
       <c r="C111" s="4">
         <v>46266</v>
       </c>
-      <c r="D111" s="63" t="s">
+      <c r="D111" s="62" t="s">
         <v>1</v>
       </c>
-      <c r="E111" s="64"/>
-      <c r="F111" s="64"/>
-      <c r="G111" s="64"/>
-      <c r="H111" s="64"/>
+      <c r="E111" s="63"/>
+      <c r="F111" s="63"/>
+      <c r="G111" s="63"/>
+      <c r="H111" s="63"/>
     </row>
     <row r="112" spans="1:8" ht="63.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B112" s="13"/>
       <c r="C112" s="10"/>
-      <c r="D112" s="62"/>
-      <c r="E112" s="62"/>
-      <c r="F112" s="62"/>
-      <c r="G112" s="62"/>
-      <c r="H112" s="62"/>
+      <c r="D112" s="64"/>
+      <c r="E112" s="64"/>
+      <c r="F112" s="64"/>
+      <c r="G112" s="64"/>
+      <c r="H112" s="64"/>
     </row>
     <row r="113" spans="1:8" ht="54" customHeight="1" x14ac:dyDescent="0.7">
       <c r="A113" s="2"/>
@@ -13982,22 +13982,22 @@
       <c r="C125" s="4">
         <v>46301</v>
       </c>
-      <c r="D125" s="63" t="s">
+      <c r="D125" s="62" t="s">
         <v>1</v>
       </c>
-      <c r="E125" s="64"/>
-      <c r="F125" s="64"/>
-      <c r="G125" s="64"/>
-      <c r="H125" s="64"/>
+      <c r="E125" s="63"/>
+      <c r="F125" s="63"/>
+      <c r="G125" s="63"/>
+      <c r="H125" s="63"/>
     </row>
     <row r="126" spans="1:8" ht="63.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B126" s="10"/>
       <c r="C126" s="10"/>
-      <c r="D126" s="62"/>
-      <c r="E126" s="62"/>
-      <c r="F126" s="62"/>
-      <c r="G126" s="62"/>
-      <c r="H126" s="62"/>
+      <c r="D126" s="64"/>
+      <c r="E126" s="64"/>
+      <c r="F126" s="64"/>
+      <c r="G126" s="64"/>
+      <c r="H126" s="64"/>
     </row>
     <row r="127" spans="1:8" ht="54" customHeight="1" x14ac:dyDescent="0.7">
       <c r="A127" s="2"/>
@@ -14206,8 +14206,10 @@
     </row>
     <row r="138" spans="2:8" ht="57" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B138" s="52"/>
-      <c r="C138" s="10"/>
-      <c r="D138" s="52"/>
+      <c r="C138" s="68" t="s">
+        <v>56</v>
+      </c>
+      <c r="D138" s="69"/>
       <c r="E138" s="10"/>
       <c r="F138" s="52"/>
       <c r="G138" s="10"/>
@@ -14221,22 +14223,22 @@
       <c r="C139" s="4">
         <v>46329</v>
       </c>
-      <c r="D139" s="63" t="s">
+      <c r="D139" s="62" t="s">
         <v>1</v>
       </c>
-      <c r="E139" s="64"/>
-      <c r="F139" s="64"/>
-      <c r="G139" s="64"/>
-      <c r="H139" s="64"/>
+      <c r="E139" s="63"/>
+      <c r="F139" s="63"/>
+      <c r="G139" s="63"/>
+      <c r="H139" s="63"/>
     </row>
     <row r="140" spans="2:8" ht="63.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B140" s="10"/>
       <c r="C140" s="10"/>
-      <c r="D140" s="62"/>
-      <c r="E140" s="62"/>
-      <c r="F140" s="62"/>
-      <c r="G140" s="62"/>
-      <c r="H140" s="62"/>
+      <c r="D140" s="64"/>
+      <c r="E140" s="64"/>
+      <c r="F140" s="64"/>
+      <c r="G140" s="64"/>
+      <c r="H140" s="64"/>
     </row>
     <row r="141" spans="2:8" ht="54" customHeight="1" x14ac:dyDescent="0.7">
       <c r="B141" s="53">
@@ -14460,22 +14462,22 @@
       <c r="C153" s="4">
         <v>46357</v>
       </c>
-      <c r="D153" s="63" t="s">
+      <c r="D153" s="62" t="s">
         <v>1</v>
       </c>
-      <c r="E153" s="64"/>
-      <c r="F153" s="64"/>
-      <c r="G153" s="64"/>
-      <c r="H153" s="64"/>
+      <c r="E153" s="63"/>
+      <c r="F153" s="63"/>
+      <c r="G153" s="63"/>
+      <c r="H153" s="63"/>
     </row>
     <row r="154" spans="2:8" ht="63.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B154" s="10"/>
       <c r="C154" s="10"/>
-      <c r="D154" s="62"/>
-      <c r="E154" s="62"/>
-      <c r="F154" s="62"/>
-      <c r="G154" s="62"/>
-      <c r="H154" s="62"/>
+      <c r="D154" s="64"/>
+      <c r="E154" s="64"/>
+      <c r="F154" s="64"/>
+      <c r="G154" s="64"/>
+      <c r="H154" s="64"/>
     </row>
     <row r="155" spans="2:8" ht="54" customHeight="1" x14ac:dyDescent="0.7">
       <c r="B155" s="1">
@@ -14695,37 +14697,25 @@
       <c r="C167" s="4">
         <v>46392</v>
       </c>
-      <c r="D167" s="63" t="s">
+      <c r="D167" s="62" t="s">
         <v>1</v>
       </c>
-      <c r="E167" s="64"/>
-      <c r="F167" s="64"/>
-      <c r="G167" s="64"/>
-      <c r="H167" s="64"/>
+      <c r="E167" s="63"/>
+      <c r="F167" s="63"/>
+      <c r="G167" s="63"/>
+      <c r="H167" s="63"/>
     </row>
     <row r="168" spans="2:8" ht="63.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B168" s="10"/>
       <c r="C168" s="10"/>
-      <c r="D168" s="62"/>
-      <c r="E168" s="62"/>
-      <c r="F168" s="62"/>
-      <c r="G168" s="62"/>
-      <c r="H168" s="62"/>
+      <c r="D168" s="64"/>
+      <c r="E168" s="64"/>
+      <c r="F168" s="64"/>
+      <c r="G168" s="64"/>
+      <c r="H168" s="64"/>
     </row>
   </sheetData>
-  <mergeCells count="27">
-    <mergeCell ref="D84:H84"/>
-    <mergeCell ref="D13:H13"/>
-    <mergeCell ref="D14:H14"/>
-    <mergeCell ref="D27:H27"/>
-    <mergeCell ref="D28:H28"/>
-    <mergeCell ref="D41:H41"/>
-    <mergeCell ref="D42:H42"/>
-    <mergeCell ref="D55:H55"/>
-    <mergeCell ref="D56:H56"/>
-    <mergeCell ref="D69:H69"/>
-    <mergeCell ref="D70:H70"/>
-    <mergeCell ref="D83:H83"/>
+  <mergeCells count="28">
     <mergeCell ref="D168:H168"/>
     <mergeCell ref="D97:H97"/>
     <mergeCell ref="D98:H98"/>
@@ -14741,6 +14731,19 @@
     <mergeCell ref="D136:E136"/>
     <mergeCell ref="D150:E150"/>
     <mergeCell ref="D152:E152"/>
+    <mergeCell ref="C138:D138"/>
+    <mergeCell ref="D84:H84"/>
+    <mergeCell ref="D13:H13"/>
+    <mergeCell ref="D14:H14"/>
+    <mergeCell ref="D27:H27"/>
+    <mergeCell ref="D28:H28"/>
+    <mergeCell ref="D41:H41"/>
+    <mergeCell ref="D42:H42"/>
+    <mergeCell ref="D55:H55"/>
+    <mergeCell ref="D56:H56"/>
+    <mergeCell ref="D69:H69"/>
+    <mergeCell ref="D70:H70"/>
+    <mergeCell ref="D83:H83"/>
   </mergeCells>
   <conditionalFormatting sqref="B3:H3 B5:H5 B7:H7 B9:H9 B11:H11 B13:C13">
     <cfRule type="expression" dxfId="11" priority="12">
